--- a/MAPA-DRIVE_Indice-de-Links.xlsx
+++ b/MAPA-DRIVE_Indice-de-Links.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mapa de Links Drive" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapa de Links Drive'!$A$1:$D$406</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapa de Links Drive'!$A$1:$D$410</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D406"/>
+  <dimension ref="A1:D410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1602,12 +1602,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>01_apoio</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AVA-CAP-001_Avaliacao-Processo-Padrao-Geral.docx</t>
+          <t>REGMED001_RepositorioOrganizacionaldeMedicao.docx</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1L0MK80X6mMOf0oDMYQtBVmYKD-LLuB6O/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1FOAiyoGlyqXioyDAXV4gCyqsJZvaJ1aB/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1629,17 +1629,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AVA-CAP-001_Avaliacao-Processo-Padrao-Geral.md</t>
+          <t>AVA-CAP-001_Avaliacao-Processo-Padrao-Geral.docx</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11rB7oDMvWo0GvcL1GhUM824bC85cmAOj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1L0MK80X6mMOf0oDMYQtBVmYKD-LLuB6O/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1651,17 +1651,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AVA-CAP-002_Avaliacao-GPR.docx</t>
+          <t>AVA-CAP-001_Avaliacao-Processo-Padrao-Geral.md</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13zYWvkkv4II08CrmYt3n0cmDwTCC3AeP/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11rB7oDMvWo0GvcL1GhUM824bC85cmAOj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1673,17 +1673,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AVA-CAP-002_Avaliacao-GPR.md</t>
+          <t>AVA-CAP-002_Avaliacao-GPR.docx</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13DugViGDC7m2Xqk-fBxWN2IqvwpSwQnc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13zYWvkkv4II08CrmYt3n0cmDwTCC3AeP/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AVA-CAP-003_Avaliacao-Tecnico-REQ-PCP-VV.docx</t>
+          <t>AVA-CAP-002_Avaliacao-GPR.md</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ihIG6DY8eq0B3qpLdXJMixozPhWv-bwT/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13DugViGDC7m2Xqk-fBxWN2IqvwpSwQnc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1717,17 +1717,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AVA-CAP-003_Avaliacao-Tecnico-REQ-PCP-VV.md</t>
+          <t>AVA-CAP-003_Avaliacao-Tecnico-REQ-PCP-VV.docx</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nskpt_7NeBQU76v1SecFt3shK616OHdU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ihIG6DY8eq0B3qpLdXJMixozPhWv-bwT/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1739,17 +1739,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AVA-CAP-004_Avaliacao-GCO-ITP.docx</t>
+          <t>AVA-CAP-003_Avaliacao-Tecnico-REQ-PCP-VV.md</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HR8kPCFtn1YeCpdGSKCsvjEVsTpKdvoZ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nskpt_7NeBQU76v1SecFt3shK616OHdU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1761,17 +1761,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AVA-CAP-004_Avaliacao-GCO-ITP.md</t>
+          <t>AVA-CAP-004_Avaliacao-GCO-ITP.docx</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JbcegYCdahfdayymHIawCep5N8sEbCqF/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1HR8kPCFtn1YeCpdGSKCsvjEVsTpKdvoZ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1783,17 +1783,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AVA-CAP-005_Avaliacao-GPC-MED-CAP.docx</t>
+          <t>AVA-CAP-004_Avaliacao-GCO-ITP.md</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1KMJLMsB9KciEhNQxSNieI3A9O1d7wTsL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JbcegYCdahfdayymHIawCep5N8sEbCqF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AVA-CAP-005_Avaliacao-GPC-MED-CAP.md</t>
+          <t>AVA-CAP-005_Avaliacao-GPC-MED-CAP.docx</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1f4ODSbjmha6LhJjT7d86A1HOEnf4Pq0T/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1KMJLMsB9KciEhNQxSNieI3A9O1d7wTsL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GUIA-CAP-001_MiniManual-GPR.docx</t>
+          <t>AVA-CAP-005_Avaliacao-GPC-MED-CAP.md</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1rS4OTxRrRrbua89Qg2Br9jrmOrjabfEu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1f4ODSbjmha6LhJjT7d86A1HOEnf4Pq0T/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1849,17 +1849,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GUIA-CAP-001_MiniManual-GPR.md</t>
+          <t>GUIA-CAP-001_MiniManual-GPR.docx</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1obKGUSvsgBmoAzGF1j5sAjUYz72erOCV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1rS4OTxRrRrbua89Qg2Br9jrmOrjabfEu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1871,17 +1871,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GUIA-CAP-002_MiniManual-REQ.docx</t>
+          <t>GUIA-CAP-001_MiniManual-GPR.md</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1wy0aD3f_ffoR5L742FgEMWqlKSj1gt1_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1obKGUSvsgBmoAzGF1j5sAjUYz72erOCV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1893,17 +1893,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GUIA-CAP-002_MiniManual-REQ.md</t>
+          <t>GUIA-CAP-002_MiniManual-REQ.docx</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1oVcmJVt3NVuN5MfJL80bJfdXJA7FL_hc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1wy0aD3f_ffoR5L742FgEMWqlKSj1gt1_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1915,17 +1915,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GUIA-CAP-003_MiniManual-PCP.docx</t>
+          <t>GUIA-CAP-002_MiniManual-REQ.md</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DCGLP9f5Pho42AMAjWzZn4A73E45bHBH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1oVcmJVt3NVuN5MfJL80bJfdXJA7FL_hc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1937,17 +1937,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GUIA-CAP-003_MiniManual-PCP.md</t>
+          <t>GUIA-CAP-003_MiniManual-PCP.docx</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1APDWRdjS_qW3Zq5bDTRFOVjC3h4DXSZ7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1DCGLP9f5Pho42AMAjWzZn4A73E45bHBH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1959,17 +1959,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GUIA-CAP-004_MiniManual-VV.docx</t>
+          <t>GUIA-CAP-003_MiniManual-PCP.md</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10OrGMaay8ZyWKQQtlPWAIStN2EArM2lX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1APDWRdjS_qW3Zq5bDTRFOVjC3h4DXSZ7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1981,17 +1981,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GUIA-CAP-004_MiniManual-VV.md</t>
+          <t>GUIA-CAP-004_MiniManual-VV.docx</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1l5pgpbqAvQlIEz6MGdE7qmLi8kJ15eVU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/10OrGMaay8ZyWKQQtlPWAIStN2EArM2lX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2003,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GUIA-CAP-005_MiniManual-GCO.docx</t>
+          <t>GUIA-CAP-004_MiniManual-VV.md</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Ehp57xo1dNee43TBPc6l8McdEHqBIusA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1l5pgpbqAvQlIEz6MGdE7qmLi8kJ15eVU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2025,17 +2025,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GUIA-CAP-005_MiniManual-GCO.md</t>
+          <t>GUIA-CAP-005_MiniManual-GCO.docx</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1amNy8d4c3vZV__wkBMaIzOeky16bLvcn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Ehp57xo1dNee43TBPc6l8McdEHqBIusA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2047,17 +2047,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GUIA-CAP-006_MiniManual-ITP.docx</t>
+          <t>GUIA-CAP-005_MiniManual-GCO.md</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dbKffWaDaaHkSpQ6wAuqyJujuyQ7Dkyy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1amNy8d4c3vZV__wkBMaIzOeky16bLvcn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2069,17 +2069,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GUIA-CAP-006_MiniManual-ITP.md</t>
+          <t>GUIA-CAP-006_MiniManual-ITP.docx</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gAPICKSawMohY7R2radBCHl6OyRZ-oA8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dbKffWaDaaHkSpQ6wAuqyJujuyQ7Dkyy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2091,17 +2091,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GUIA-CAP-007_MiniManual-GDE.docx</t>
+          <t>GUIA-CAP-006_MiniManual-ITP.md</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MgTl2w9fZz3aHeHW0ZSdEKN9TmEHt7eY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1gAPICKSawMohY7R2radBCHl6OyRZ-oA8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GUIA-CAP-007_MiniManual-GDE.md</t>
+          <t>GUIA-CAP-007_MiniManual-GDE.docx</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1csGF1cCc8vi1dA5OlfKCh9q-g3FoMRg5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1MgTl2w9fZz3aHeHW0ZSdEKN9TmEHt7eY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2135,17 +2135,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GUIA-CAP-008_MiniManual-MED.docx</t>
+          <t>GUIA-CAP-007_MiniManual-GDE.md</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15dXPTmal-yqg9B2vQyoSZEUX8OxZksFr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1csGF1cCc8vi1dA5OlfKCh9q-g3FoMRg5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GUIA-CAP-008_MiniManual-MED.md</t>
+          <t>GUIA-CAP-008_MiniManual-MED.docx</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MJf9WWhQQUdXuXW8VKazxIUzmFVSButZ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15dXPTmal-yqg9B2vQyoSZEUX8OxZksFr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2179,17 +2179,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GUIA-CAP-009_MiniManual-GPC.docx</t>
+          <t>GUIA-CAP-008_MiniManual-MED.md</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1kNivoZ1Wr4QXbjReNplUIfqigeOtJ8_o/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1MJf9WWhQQUdXuXW8VKazxIUzmFVSButZ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2201,17 +2201,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GUIA-CAP-009_MiniManual-GPC.md</t>
+          <t>GUIA-CAP-009_MiniManual-GPC.docx</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15s8hqDo_2kh_qrkEqvbBSzSXvOVJa-hI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1kNivoZ1Wr4QXbjReNplUIfqigeOtJ8_o/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2223,17 +2223,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GUIA-CAP-010_MiniManual-OSW.docx</t>
+          <t>GUIA-CAP-009_MiniManual-GPC.md</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12S8LyYhsEzQv4A0D6qDZRLgC30S0nqmK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15s8hqDo_2kh_qrkEqvbBSzSXvOVJa-hI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2245,17 +2245,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GUIA-CAP-010_MiniManual-OSW.md</t>
+          <t>GUIA-CAP-010_MiniManual-OSW.docx</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15XAGw1n2P_mXvbGIEvHRGmnJKgbNgKBR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/12S8LyYhsEzQv4A0D6qDZRLgC30S0nqmK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2267,17 +2267,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GUIA-CAP-011_MiniManual-CAP.docx</t>
+          <t>GUIA-CAP-010_MiniManual-OSW.md</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TMwHMbbq0D8I17CWr-cPGP7TzW-GJms0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15XAGw1n2P_mXvbGIEvHRGmnJKgbNgKBR/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2289,17 +2289,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GUIA-CAP-011_MiniManual-CAP.md</t>
+          <t>GUIA-CAP-011_MiniManual-CAP.docx</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17ZZI8mUkEkCoRTmXrJe_mY8Qj0kol-N1/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TMwHMbbq0D8I17CWr-cPGP7TzW-GJms0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2311,17 +2311,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GUIA-CAP-012_MiniManual-AQU.docx</t>
+          <t>GUIA-CAP-011_MiniManual-CAP.md</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1xT56t0Yfh7YnSZ1TPx8TYla_9D9w7Xc4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17ZZI8mUkEkCoRTmXrJe_mY8Qj0kol-N1/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2333,17 +2333,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GUIA-CAP-012_MiniManual-AQU.md</t>
+          <t>GUIA-CAP-012_MiniManual-AQU.docx</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1aS7ue400NH7RXhsiAch-o_IBnooTKg6b/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1xT56t0Yfh7YnSZ1TPx8TYla_9D9w7Xc4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2355,17 +2355,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MAT-CAP-013_Trilha-COO-Portfolio.docx</t>
+          <t>GUIA-CAP-012_MiniManual-AQU.md</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13YO3MTQBznbYFOc_akFM-UwWdsobodLj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1aS7ue400NH7RXhsiAch-o_IBnooTKg6b/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2377,17 +2377,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MAT-CAP-013_Trilha-COO-Portfolio.md</t>
+          <t>MAT-CAP-013_Trilha-COO-Portfolio.docx</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ifOoba9-maD6zF6_4fqVJBohKkJFBfIc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13YO3MTQBznbYFOc_akFM-UwWdsobodLj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2399,17 +2399,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MAT-CAP-014_Trilha-Time-Melhoria-SEPG.docx</t>
+          <t>MAT-CAP-013_Trilha-COO-Portfolio.md</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RkTsNavdx3osAAgqlgFzkTLFIGwkMTBi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ifOoba9-maD6zF6_4fqVJBohKkJFBfIc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2421,17 +2421,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MAT-CAP-014_Trilha-Time-Melhoria-SEPG.md</t>
+          <t>MAT-CAP-014_Trilha-Time-Melhoria-SEPG.docx</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TTaEJ-gZEKxjrSZ4XVrBQgqrRjnoTBeL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RkTsNavdx3osAAgqlgFzkTLFIGwkMTBi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2443,17 +2443,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MAT-CAP-015_Trilha-RH-Pessoas.docx</t>
+          <t>MAT-CAP-014_Trilha-Time-Melhoria-SEPG.md</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1apnEAcH2MS8RsyDsvl5Hqfnz5xkrCXpe/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TTaEJ-gZEKxjrSZ4XVrBQgqrRjnoTBeL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2465,17 +2465,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MAT-CAP-015_Trilha-RH-Pessoas.md</t>
+          <t>MAT-CAP-015_Trilha-RH-Pessoas.docx</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SgEIYvz-cRVmg2aEiwKHdYPJixBAT5fk/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1apnEAcH2MS8RsyDsvl5Hqfnz5xkrCXpe/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2487,17 +2487,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MAT-CAP-016_Trilha-Tech-Lead-Arquiteto.docx</t>
+          <t>MAT-CAP-015_Trilha-RH-Pessoas.md</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JS4_FKAPYHzz1B65YTGL8uVkSAo0-ad-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SgEIYvz-cRVmg2aEiwKHdYPJixBAT5fk/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2509,17 +2509,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MAT-CAP-016_Trilha-Tech-Lead-Arquiteto.md</t>
+          <t>MAT-CAP-016_Trilha-Tech-Lead-Arquiteto.docx</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12tV94PVD8CSJO7GBtuiV_wkAX8uhxZQD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JS4_FKAPYHzz1B65YTGL8uVkSAo0-ad-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2531,17 +2531,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MAT-CAP-017_Trilha-PO-PM.docx</t>
+          <t>MAT-CAP-016_Trilha-Tech-Lead-Arquiteto.md</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Nk9RNKlXzfJwijqhfm-wJysHm8et6cBG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/12tV94PVD8CSJO7GBtuiV_wkAX8uhxZQD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MAT-CAP-017_Trilha-PO-PM.md</t>
+          <t>MAT-CAP-017_Trilha-PO-PM.docx</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1a8ORfbTfL6Ic6l8ECE1SiYTM8YUwaszg/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Nk9RNKlXzfJwijqhfm-wJysHm8et6cBG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2575,17 +2575,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MAT-CAP-018_Trilha-Devs.docx</t>
+          <t>MAT-CAP-017_Trilha-PO-PM.md</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cYBe6kG7LK67kpPVPQj-jfolwxk57Z-S/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1a8ORfbTfL6Ic6l8ECE1SiYTM8YUwaszg/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2597,17 +2597,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MAT-CAP-018_Trilha-Devs.md</t>
+          <t>MAT-CAP-018_Trilha-Devs.docx</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Agyekcmbs8jKVYHF930x3mGtdS1b-l0w/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1cYBe6kG7LK67kpPVPQj-jfolwxk57Z-S/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2619,17 +2619,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MAT-CAP-019_Trilha-DevOps.docx</t>
+          <t>MAT-CAP-018_Trilha-Devs.md</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1om6pDV7QThxnwkx52889J2_3pOrWACKm/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Agyekcmbs8jKVYHF930x3mGtdS1b-l0w/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2641,17 +2641,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MAT-CAP-019_Trilha-DevOps.md</t>
+          <t>MAT-CAP-019_Trilha-DevOps.docx</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13xgrU-0Pthp_6P6woHdUfiDyHwpVmb_g/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1om6pDV7QThxnwkx52889J2_3pOrWACKm/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2663,17 +2663,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MAT-CAP-020_Trilha-QA.docx</t>
+          <t>MAT-CAP-019_Trilha-DevOps.md</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1KUq-32kGvzsKicpUN_Kxy0aRMPu0Y_oi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13xgrU-0Pthp_6P6woHdUfiDyHwpVmb_g/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MAT-CAP-020_Trilha-QA.md</t>
+          <t>MAT-CAP-020_Trilha-QA.docx</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13k32H05H8n7d1ZA3BoOeoL1NyXsHKGva/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1KUq-32kGvzsKicpUN_Kxy0aRMPu0Y_oi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2707,17 +2707,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MAT-CAP-021_Trilha-GCO-Baseline.docx</t>
+          <t>MAT-CAP-020_Trilha-QA.md</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1xG7FbLTcLVNY9Tf75MM3Ttu_t3ZRjTix/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13k32H05H8n7d1ZA3BoOeoL1NyXsHKGva/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2729,17 +2729,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MAT-CAP-021_Trilha-GCO-Baseline.md</t>
+          <t>MAT-CAP-021_Trilha-GCO-Baseline.docx</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dJ_MTeu8qbYjaw50Wbh0c8Eh-ZKGZ-48/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1xG7FbLTcLVNY9Tf75MM3Ttu_t3ZRjTix/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2751,17 +2751,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MAT-CAP-022_Trilha-Responsavel-Medicao.docx</t>
+          <t>MAT-CAP-021_Trilha-GCO-Baseline.md</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1VRdJxBk4wlBQ_-jq7Ue_4DhHQ3PbKjsC/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dJ_MTeu8qbYjaw50Wbh0c8Eh-ZKGZ-48/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2773,17 +2773,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MAT-CAP-022_Trilha-Responsavel-Medicao.md</t>
+          <t>MAT-CAP-022_Trilha-Responsavel-Medicao.docx</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1vL14qqXbQD_Tse191WLvePN5uB2ewpcG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1VRdJxBk4wlBQ_-jq7Ue_4DhHQ3PbKjsC/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2795,17 +2795,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MAT-CAP-023_Trilha-Tecnica-Onboarding.docx</t>
+          <t>MAT-CAP-022_Trilha-Responsavel-Medicao.md</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1sKQLlANRH_jIB6WIy0v6ko5XemKojdC-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1vL14qqXbQD_Tse191WLvePN5uB2ewpcG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2817,17 +2817,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MAT-CAP-023_Trilha-Tecnica-Onboarding.md</t>
+          <t>MAT-CAP-023_Trilha-Tecnica-Onboarding.docx</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1oHF_OtwhrXzCkBYJnrTDkTjNhey3vmk_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1sKQLlANRH_jIB6WIy0v6ko5XemKojdC-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2839,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>REG-CAP-001B_Sessao-Reforco-Jan2025.docx</t>
+          <t>MAT-CAP-023_Trilha-Tecnica-Onboarding.md</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1O-P9xpYwaW_vd1xmsRiwgyP9FQ3j7nCp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1oHF_OtwhrXzCkBYJnrTDkTjNhey3vmk_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2861,17 +2861,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>REG-CAP-001B_Sessao-Reforco-Jan2025.md</t>
+          <t>REG-CAP-001B_Sessao-Reforco-Jan2025.docx</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ABAnRyZSxwoJObVCP84fEt-N4fXR1bxQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1O-P9xpYwaW_vd1xmsRiwgyP9FQ3j7nCp/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>REG-CAP-001_Sessao-Treinamento-Dez2024.docx</t>
+          <t>REG-CAP-001B_Sessao-Reforco-Jan2025.md</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nO1WhH6T77KWemD0dxO2ZTXuzXbJU8at/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ABAnRyZSxwoJObVCP84fEt-N4fXR1bxQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2905,17 +2905,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>REG-CAP-001_Sessao-Treinamento-Dez2024.md</t>
+          <t>REG-CAP-001_Sessao-Treinamento-Dez2024.docx</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1enrf4ZAUhttkVPDlVmCyLdbwOwHgJXKy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nO1WhH6T77KWemD0dxO2ZTXuzXbJU8at/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2927,17 +2927,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>REG-CAP-002B_Sessao-Reforco-Set2025.docx</t>
+          <t>REG-CAP-001_Sessao-Treinamento-Dez2024.md</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1lOL9e-11IVGVyS4TvsF21Ht325Nl0NAS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1enrf4ZAUhttkVPDlVmCyLdbwOwHgJXKy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2949,17 +2949,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>REG-CAP-002B_Sessao-Reforco-Set2025.md</t>
+          <t>REG-CAP-002B_Sessao-Reforco-Set2025.docx</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Ljd3g8eppyULGODYbJzt1962L0O-VoSp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1lOL9e-11IVGVyS4TvsF21Ht325Nl0NAS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2971,17 +2971,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>REG-CAP-002_Sessao-Treinamento-Mar2025.docx</t>
+          <t>REG-CAP-002B_Sessao-Reforco-Set2025.md</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1S4KO93SuNshpOxu3g41TjnZW3HajFBNw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Ljd3g8eppyULGODYbJzt1962L0O-VoSp/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>REG-CAP-002_Sessao-Treinamento-Mar2025.md</t>
+          <t>REG-CAP-002_Sessao-Treinamento-Mar2025.docx</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NbodP8vj_SS999XcRiCu4aslfdXw9FAP/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1S4KO93SuNshpOxu3g41TjnZW3HajFBNw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3015,17 +3015,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>REG-CAP-003_Sessao-Treinamento-Ago2025.docx</t>
+          <t>REG-CAP-002_Sessao-Treinamento-Mar2025.md</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1x2iX2AevFRS44IkePAvaC9BF1t8i5mup/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NbodP8vj_SS999XcRiCu4aslfdXw9FAP/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3037,17 +3037,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>REG-CAP-003_Sessao-Treinamento-Ago2025.md</t>
+          <t>REG-CAP-003_Sessao-Treinamento-Ago2025.docx</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZKJFrUa_v0JpLre9LLNPti6sLE-qt-sI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1x2iX2AevFRS44IkePAvaC9BF1t8i5mup/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3059,17 +3059,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>REG-CAP-004_Sessao-Treinamento-Jan2026.docx</t>
+          <t>REG-CAP-003_Sessao-Treinamento-Ago2025.md</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jJ7Gjeu_ds4huXMAF7e564NeJBgICJDz/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZKJFrUa_v0JpLre9LLNPti6sLE-qt-sI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3081,17 +3081,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>REG-CAP-004_Sessao-Treinamento-Jan2026.md</t>
+          <t>REG-CAP-004_Sessao-Treinamento-Jan2026.docx</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15qmHgk5_9u0ep5Je0R1femPBgim9Wvsw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jJ7Gjeu_ds4huXMAF7e564NeJBgICJDz/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3103,17 +3103,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>REG-CAP-005_Sessao-Treinamento-Mai2026.docx</t>
+          <t>REG-CAP-004_Sessao-Treinamento-Jan2026.md</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1wGWK2W15Bws7fpOpta5AaqqvTpBMe7s5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15qmHgk5_9u0ep5Je0R1femPBgim9Wvsw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3125,17 +3125,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>REG-CAP-005_Sessao-Treinamento-Mai2026.md</t>
+          <t>REG-CAP-005_Sessao-Treinamento-Mai2026.docx</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11POQMlFp5psX9W4oAWk5J842VZvU83hY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1wGWK2W15Bws7fpOpta5AaqqvTpBMe7s5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3147,17 +3147,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>REG-CAP-006_Sessao-Gestao-Out2025.docx</t>
+          <t>REG-CAP-005_Sessao-Treinamento-Mai2026.md</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11Nd6v2QxAipLc6gR1WDvH81DS2FfMKox/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11POQMlFp5psX9W4oAWk5J842VZvU83hY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3169,17 +3169,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>REG-CAP-006_Sessao-Gestao-Out2025.md</t>
+          <t>REG-CAP-006_Sessao-Gestao-Out2025.docx</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10jW0RgPOO_YOPYdh0MiDkP1r6oAkPiS1/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11Nd6v2QxAipLc6gR1WDvH81DS2FfMKox/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3191,17 +3191,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>REG-CAP-007_Sessao-Tecnico-Jan2026.docx</t>
+          <t>REG-CAP-006_Sessao-Gestao-Out2025.md</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16Lpc4ZfSV0HGifzpJwfeEjIgidwCo2pR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/10jW0RgPOO_YOPYdh0MiDkP1r6oAkPiS1/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3213,17 +3213,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>REG-CAP-007_Sessao-Tecnico-Jan2026.md</t>
+          <t>REG-CAP-007_Sessao-Tecnico-Jan2026.docx</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SthU41muR1B9KQ-AjTzdPy7C7zjAx6St/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/16Lpc4ZfSV0HGifzpJwfeEjIgidwCo2pR/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3235,17 +3235,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>REG-CAP-008_Sessao-Tecnico-Fev2026.docx</t>
+          <t>REG-CAP-007_Sessao-Tecnico-Jan2026.md</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UYtCRfbMeXCdL_aXzAz-wpCs8bTC-sR1/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SthU41muR1B9KQ-AjTzdPy7C7zjAx6St/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3257,17 +3257,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>REG-CAP-008_Sessao-Tecnico-Fev2026.md</t>
+          <t>REG-CAP-008_Sessao-Tecnico-Fev2026.docx</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FCa5wLWvxiOHu1GJfKqXrdYfvC8mg7MG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1UYtCRfbMeXCdL_aXzAz-wpCs8bTC-sR1/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3279,17 +3279,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>REG-CAP-009_Reciclagem-Mar2026.docx</t>
+          <t>REG-CAP-008_Sessao-Tecnico-Fev2026.md</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1xgHZsTCrfuBCgwvVfWaSTZGsS3GZ7xiR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1FCa5wLWvxiOHu1GJfKqXrdYfvC8mg7MG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3301,17 +3301,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>REG-CAP-009_Reciclagem-Mar2026.md</t>
+          <t>REG-CAP-009_Reciclagem-Mar2026.docx</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1X5pxMU4f1oCgfCn65m8SE8bQkPUiYnl8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1xgHZsTCrfuBCgwvVfWaSTZGsS3GZ7xiR/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3323,17 +3323,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>REG-CAP-010_Onboarding-Tecnico-Jan2026.docx</t>
+          <t>REG-CAP-009_Reciclagem-Mar2026.md</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pWjwFRZgCCd2D4MIN9AEhMIX176WACAg/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1X5pxMU4f1oCgfCn65m8SE8bQkPUiYnl8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3345,17 +3345,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>REG-CAP-010_Onboarding-Tecnico-Jan2026.md</t>
+          <t>REG-CAP-010_Onboarding-Tecnico-Jan2026.docx</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jt5GFjbCsNurYrDdCoW-Pjmdr5BanLwK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pWjwFRZgCCd2D4MIN9AEhMIX176WACAg/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3367,17 +3367,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>REG-CAP-011_Workshop-Azure-APIM-Mar2026.docx</t>
+          <t>REG-CAP-010_Onboarding-Tecnico-Jan2026.md</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11KTzVFyJCNcVZHItsY2HZwL8YX2CHk7r/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jt5GFjbCsNurYrDdCoW-Pjmdr5BanLwK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3389,17 +3389,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>REG-CAP-011_Workshop-Azure-APIM-Mar2026.md</t>
+          <t>REG-CAP-011_Workshop-Azure-APIM-Mar2026.docx</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1qu5roDPPeKIxp3C-DCMHOtkuavzA6DX_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11KTzVFyJCNcVZHItsY2HZwL8YX2CHk7r/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3411,17 +3411,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>REG-CAP-012_Workshop-Automacao-Testes-Fev2026.docx</t>
+          <t>REG-CAP-011_Workshop-Azure-APIM-Mar2026.md</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10RHw3_QQb3-yF4aCqLMMk7vNzROKhbXH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1qu5roDPPeKIxp3C-DCMHOtkuavzA6DX_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3433,17 +3433,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>REG-CAP-012_Workshop-Automacao-Testes-Fev2026.md</t>
+          <t>REG-CAP-012_Workshop-Automacao-Testes-Fev2026.docx</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13aw-J5V35sDlLWbE4MMCvt06qA8p-InU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/10RHw3_QQb3-yF4aCqLMMk7vNzROKhbXH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3455,17 +3455,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>REG-CAP-013_Consultoria-Desenho-Processos-Jun2025.docx</t>
+          <t>REG-CAP-012_Workshop-Automacao-Testes-Fev2026.md</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FpzpCSb3W1th24HWN5iUTN_O17YSW1NZ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13aw-J5V35sDlLWbE4MMCvt06qA8p-InU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3477,17 +3477,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>REG-CAP-013_Consultoria-Desenho-Processos-Jun2025.md</t>
+          <t>REG-CAP-013_Consultoria-Desenho-Processos-Jun2025.docx</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1sgqmkafBuD0gJ_EPNluW16VXUquFp24v/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1FpzpCSb3W1th24HWN5iUTN_O17YSW1NZ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3499,17 +3499,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>REG-CAP-CV-001_Indice-de-Curriculos.docx</t>
+          <t>REG-CAP-013_Consultoria-Desenho-Processos-Jun2025.md</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1K0cu6iTTt70jGgGBXDo9pRWwPj3sGva4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1sgqmkafBuD0gJ_EPNluW16VXUquFp24v/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3521,17 +3521,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>REG-CAP-CV-001_Indice-de-Curriculos.md</t>
+          <t>REG-CAP-CV-001_Indice-de-Curriculos.docx</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14INGstsvVIz7rsXaOxlfArjNflLSFd5x/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1K0cu6iTTt70jGgGBXDo9pRWwPj3sGva4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3543,17 +3543,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>REL-CAP-001_Relatorio-de-Eficacia-2025.docx</t>
+          <t>REG-CAP-CV-001_Indice-de-Curriculos.md</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gXdIOCwtTvOW-QrBf8UYFEv2YEH8q6A3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14INGstsvVIz7rsXaOxlfArjNflLSFd5x/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3565,17 +3565,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>REL-CAP-001_Relatorio-de-Eficacia-2025.md</t>
+          <t>REL-CAP-001_Relatorio-de-Eficacia-2025.docx</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bEjNu5MAK6AZSURmLyDRxn2jegRay09J/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1gXdIOCwtTvOW-QrBf8UYFEv2YEH8q6A3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TPL-CAP-001_Registro-de-Sessao-de-Treinamento.docx</t>
+          <t>REL-CAP-001_Relatorio-de-Eficacia-2025.md</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CVkEt9LrB9ClXXPqYteGC9NnEgYKoXFe/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bEjNu5MAK6AZSURmLyDRxn2jegRay09J/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3609,17 +3609,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TPL-CAP-001_Registro-de-Sessao-de-Treinamento.md</t>
+          <t>TPL-CAP-001_Registro-de-Sessao-de-Treinamento.docx</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1V6nwWP49ThNknbf0gvVkK19GFRQMZC4l/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CVkEt9LrB9ClXXPqYteGC9NnEgYKoXFe/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3631,17 +3631,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TPL-CAP-002_Relatorio-de-Eficacia-de-Treinamento.docx</t>
+          <t>TPL-CAP-001_Registro-de-Sessao-de-Treinamento.md</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1m3HpIJ0JgLVQM9LaEDxMUgidJhkg6RJO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1V6nwWP49ThNknbf0gvVkK19GFRQMZC4l/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3653,39 +3653,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TPL-CAP-002_Relatorio-de-Eficacia-de-Treinamento.md</t>
+          <t>TPL-CAP-002_Relatorio-de-Eficacia-de-Treinamento.docx</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1GHbjdOCqWlo0_K4rnKN-kgJDs-A9aNAI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1m3HpIJ0JgLVQM9LaEDxMUgidJhkg6RJO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>01_apoio/cap/curriculos</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CV-Caroline-Jenifer_QA.pdf</t>
+          <t>TPL-CAP-002_Relatorio-de-Eficacia-de-Treinamento.md</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1C7vxxTRerQM1J7J344iub0tfSV86ozhc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1GHbjdOCqWlo0_K4rnKN-kgJDs-A9aNAI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CV-Cezar-Velazquez_TechLead.pdf</t>
+          <t>CV-Caroline-Jenifer_QA.pdf</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Wj_kGQvhXViFApjmjJDfvzUvbSuyqqV3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1C7vxxTRerQM1J7J344iub0tfSV86ozhc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CV-Flavio-Fernandes_GQA-Arquitetura.pdf</t>
+          <t>CV-Cezar-Velazquez_TechLead.pdf</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1GSQQ2yS_E7-HnE2BFPsf1A-hkq2AVjPd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Wj_kGQvhXViFApjmjJDfvzUvbSuyqqV3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CV-Karen-Wada_Consultora-Processos.pdf</t>
+          <t>CV-Flavio-Fernandes_GQA-Arquitetura.pdf</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jX6ax9IDMALDHpoTCrcMMerF_nGIGpCr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1GSQQ2yS_E7-HnE2BFPsf1A-hkq2AVjPd/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CV-Silvio-Baroni_SEPG-GPC.pdf</t>
+          <t>CV-Karen-Wada_Consultora-Processos.pdf</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1rC4NvQveAUCAWQOkNiU8VvlVX2AkTN6i/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jX6ax9IDMALDHpoTCrcMMerF_nGIGpCr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CV-Wilson-Yamada_Sponsor-Portfolio.pdf</t>
+          <t>CV-Silvio-Baroni_SEPG-GPC.pdf</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3795,29 +3795,29 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11gRQH_6m7Eq1ojWkfu6hRK_AqTqY65ak/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1rC4NvQveAUCAWQOkNiU8VvlVX2AkTN6i/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>01_apoio/cap/curriculos</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GUIA-GPR-001_Roteiro-de-Kickoff.docx</t>
+          <t>CV-Wilson-Yamada_Sponsor-Portfolio.pdf</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1icahhXdwUOXQA3txofLbVmOaFKnbaCxu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11gRQH_6m7Eq1ojWkfu6hRK_AqTqY65ak/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3829,17 +3829,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GUIA-GPR-001_Roteiro-de-Kickoff.md</t>
+          <t>GUIA-GPR-001_Roteiro-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1N1YGy0ljWuoaq603HAmFjpJwrF1Yw-Ac/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1icahhXdwUOXQA3txofLbVmOaFKnbaCxu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3851,17 +3851,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PRO-GPR-001_Processo-de-Gerencia-de-Projetos.docx</t>
+          <t>GUIA-GPR-001_Roteiro-de-Kickoff.md</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1k8QAAFCQmb8sJAMKlrR-Pnv6MZqD1Xcy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1N1YGy0ljWuoaq603HAmFjpJwrF1Yw-Ac/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3873,17 +3873,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PRO-GPR-001_Processo-de-Gerencia-de-Projetos.md</t>
+          <t>PRO-GPR-001_Processo-de-Gerencia-de-Projetos.docx</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tuaDp9oFw0sAVv4qe0BgsSPNKD_JgoMn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1k8QAAFCQmb8sJAMKlrR-Pnv6MZqD1Xcy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3895,17 +3895,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PRO-ITP-001_Processo-de-Integracao-do-Produto.docx</t>
+          <t>PRO-GPR-001_Processo-de-Gerencia-de-Projetos.md</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Ua11xIFEHx4QTKpoKXZd3pFLXrES7OXW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tuaDp9oFw0sAVv4qe0BgsSPNKD_JgoMn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3917,17 +3917,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PRO-ITP-001_Processo-de-Integracao-do-Produto.md</t>
+          <t>PRO-ITP-001_Processo-de-Integracao-do-Produto.docx</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1QdieFmzpCLXLGRwy_9QwjFuzKPM_-_03/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Ua11xIFEHx4QTKpoKXZd3pFLXrES7OXW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3939,17 +3939,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PRO-PCP-001_Processo-de-Projeto-e-Construcao-do-Produto.docx</t>
+          <t>PRO-ITP-001_Processo-de-Integracao-do-Produto.md</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1PFGeQPHNKcUFMFNIO9lT1CkO9RyUe0CD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1QdieFmzpCLXLGRwy_9QwjFuzKPM_-_03/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3961,17 +3961,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PRO-PCP-001_Processo-de-Projeto-e-Construcao-do-Produto.md</t>
+          <t>PRO-PCP-001_Processo-de-Projeto-e-Construcao-do-Produto.docx</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D9wE8bol3nzsW802mrEujCEmqDJcaG3K/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1PFGeQPHNKcUFMFNIO9lT1CkO9RyUe0CD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3983,17 +3983,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PRO-REQ-001_Processo-de-Engenharia-de-Requisitos.docx</t>
+          <t>PRO-PCP-001_Processo-de-Projeto-e-Construcao-do-Produto.md</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FE8Ytpu1fUrggTPn7A1hAI2rut4oeRV2/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D9wE8bol3nzsW802mrEujCEmqDJcaG3K/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4005,17 +4005,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PRO-REQ-001_Processo-de-Engenharia-de-Requisitos.md</t>
+          <t>PRO-REQ-001_Processo-de-Engenharia-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1mEmw_8na4H8-Wysz_K51-hNyfMGq7B25/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1FE8Ytpu1fUrggTPn7A1hAI2rut4oeRV2/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4027,17 +4027,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PRO-VV-001_Processo-de-Verificacao-e-Validacao.docx</t>
+          <t>PRO-REQ-001_Processo-de-Engenharia-de-Requisitos.md</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UloaOSeholVwPG1uQTnwaYMCDd_Eqgu7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1mEmw_8na4H8-Wysz_K51-hNyfMGq7B25/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4049,29 +4049,29 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PRO-VV-001_Processo-de-Verificacao-e-Validacao.md</t>
+          <t>PRO-VV-001_Processo-de-Verificacao-e-Validacao.docx</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1QFnmCgrpXpIPNqirQS9EwAVR38zDCJE3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1UloaOSeholVwPG1uQTnwaYMCDd_Eqgu7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>02_projeto</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EXEMPLO-GPR-005_Status-Report-Exemplo-Preenchido.md</t>
+          <t>PRO-VV-001_Processo-de-Verificacao-e-Validacao.md</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tk09ctAQgOW2xowJIjnVQX9lx_DFpMvi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1QFnmCgrpXpIPNqirQS9EwAVR38zDCJE3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4093,17 +4093,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TPL-GDE-001_Template-Registro-de-Analise-de-Decisao.docx</t>
+          <t>EXEMPLO-GPR-005_Status-Report-Exemplo-Preenchido.md</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1V2VwWHjezpUNsDIy0eNM31mo0ydqiHa8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tk09ctAQgOW2xowJIjnVQX9lx_DFpMvi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4115,17 +4115,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TPL-GDE-001_Template-Registro-de-Analise-de-Decisao.md</t>
+          <t>EXEMPLOGPR005_StatusReportExemploPreenchido.docx</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1xqVF8ueYmwaKzDsDypX6n0YLy7Qq-6jU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1xdb1hYORBdN9jrAxuuqEunXIoDzptTBH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TPL-GPC-001_Template-Registro-de-Verificacao-de-GQA.docx</t>
+          <t>TPL-GDE-001_Template-Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1vklwYMZeJFJ_hsULzyPPQfHSIBH2sPCG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1V2VwWHjezpUNsDIy0eNM31mo0ydqiHa8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TPL-GPC-001_Template-Registro-de-Verificacao-de-GQA.md</t>
+          <t>TPL-GDE-001_Template-Registro-de-Analise-de-Decisao.md</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TFVY8JIrsAd9K-a52ymx0PvhlA4yUgbE/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1xqVF8ueYmwaKzDsDypX6n0YLy7Qq-6jU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TPL-GPR-001_Template-Plano-de-Projeto.docx</t>
+          <t>TPL-GPC-001_Template-Registro-de-Verificacao-de-GQA.docx</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JG7_Er7Cq5FfiS44dfcZlg0dKUwzWetA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1vklwYMZeJFJ_hsULzyPPQfHSIBH2sPCG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TPL-GPR-001_Template-Plano-de-Projeto.md</t>
+          <t>TPL-GPC-001_Template-Registro-de-Verificacao-de-GQA.md</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s74PRIyXyCSuRPi2_yCL3GsYk_N9pR0k/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TFVY8JIrsAd9K-a52ymx0PvhlA4yUgbE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TPL-GPR-002_Template-Termo-de-Abertura.docx</t>
+          <t>TPL-GPR-001_Template-Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fw6vq92uHpUuJoVNuHbDPbVFC3gxVEm8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JG7_Er7Cq5FfiS44dfcZlg0dKUwzWetA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TPL-GPR-002_Template-Termo-de-Abertura.md</t>
+          <t>TPL-GPR-001_Template-Plano-de-Projeto.md</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pvb4FoBeV8cBmdEE7OLmIntCAmxNMD4A/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1s74PRIyXyCSuRPi2_yCL3GsYk_N9pR0k/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TPL-GPR-003_Template-Registro-de-Adaptacao.docx</t>
+          <t>TPL-GPR-002_Template-Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17Q9cPXicAvMqAXYPz8ljpb5S2i0NePx_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fw6vq92uHpUuJoVNuHbDPbVFC3gxVEm8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TPL-GPR-003_Template-Registro-de-Adaptacao.md</t>
+          <t>TPL-GPR-002_Template-Termo-de-Abertura.md</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/131xkb1wj3ZoJbRgkuNefU8bmLwACM3VD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pvb4FoBeV8cBmdEE7OLmIntCAmxNMD4A/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TPL-GPR-004_Template-Termo-de-Encerramento.docx</t>
+          <t>TPL-GPR-003_Template-Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LFj2UMUcCD7ewIGlkRdshUo-HmJUMmad/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17Q9cPXicAvMqAXYPz8ljpb5S2i0NePx_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TPL-GPR-004_Template-Termo-de-Encerramento.md</t>
+          <t>TPL-GPR-003_Template-Registro-de-Adaptacao.md</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/133uiwTw2s2O63F5E-DBBeCh1MmFvOCS9/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/131xkb1wj3ZoJbRgkuNefU8bmLwACM3VD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TPL-GPR-005_Template-Relatorio-de-Acompanhamento.docx</t>
+          <t>TPL-GPR-004_Template-Termo-de-Encerramento.docx</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1U4pFEFtk7OwhzNix2RDuOcvWNT55XJQo/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LFj2UMUcCD7ewIGlkRdshUo-HmJUMmad/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TPL-GPR-005_Template-Relatorio-de-Acompanhamento.md</t>
+          <t>TPL-GPR-004_Template-Termo-de-Encerramento.md</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HUSg5x0hlen1UY4RjPAiWh1a_ETf1RCu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/133uiwTw2s2O63F5E-DBBeCh1MmFvOCS9/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TPL-GPR-006_Template-Change-Request.docx</t>
+          <t>TPL-GPR-005_Template-Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1p400uzBBwZpSWLeGNzJlFy_so7UoDURu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1U4pFEFtk7OwhzNix2RDuOcvWNT55XJQo/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>TPL-GPR-006_Template-Change-Request.md</t>
+          <t>TPL-GPR-005_Template-Relatorio-de-Acompanhamento.md</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HwSihP8liBxJcEfLsgiHgwJZFgulkd_y/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1HUSg5x0hlen1UY4RjPAiWh1a_ETf1RCu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TPL-ITP-001_Template-Estrategia-de-Integracao.docx</t>
+          <t>TPL-GPR-006_Template-Change-Request.docx</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1n3gUvRn54vsEAgZWQeXLxfbAoDoQRzEO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1p400uzBBwZpSWLeGNzJlFy_so7UoDURu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TPL-ITP-001_Template-Estrategia-de-Integracao.md</t>
+          <t>TPL-GPR-006_Template-Change-Request.md</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gTeyMOv_qhfqWZf8J7Se4O9kxJiJDrZO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1HwSihP8liBxJcEfLsgiHgwJZFgulkd_y/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TPL-ORG-001_Template-Ata-de-Reuniao.docx</t>
+          <t>TPL-ITP-001_Template-Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bdb2aarUtu2uLyhgCFVtS3FiyiKb7CF5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1n3gUvRn54vsEAgZWQeXLxfbAoDoQRzEO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>TPL-ORG-001_Template-Ata-de-Reuniao.md</t>
+          <t>TPL-ITP-001_Template-Estrategia-de-Integracao.md</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Cufw51GxH3TRru8xL9vDGHiYi8Mmjk6D/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1gTeyMOv_qhfqWZf8J7Se4O9kxJiJDrZO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TPL-PCP-001_Template-Documento-de-Design.docx</t>
+          <t>TPL-ORG-001_Template-Ata-de-Reuniao.docx</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MzCnCw8RflPBrznE_xSEWci1LAaCoVLl/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bdb2aarUtu2uLyhgCFVtS3FiyiKb7CF5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>TPL-PCP-001_Template-Documento-de-Design.md</t>
+          <t>TPL-ORG-001_Template-Ata-de-Reuniao.md</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1vGR1UiffaWOvicnoU8NpPHhO96NBwbhV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Cufw51GxH3TRru8xL9vDGHiYi8Mmjk6D/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>TPL-REQ-001_Template-Documento-de-Requisitos.docx</t>
+          <t>TPL-PCP-001_Template-Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1IGz8Jxln6UO_tCFNplT6fcHxq-5KEVB5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1MzCnCw8RflPBrznE_xSEWci1LAaCoVLl/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TPL-REQ-001_Template-Documento-de-Requisitos.md</t>
+          <t>TPL-PCP-001_Template-Documento-de-Design.md</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19Uus1IU9ab_z960ITUxm8xaNluk7_LGz/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1vGR1UiffaWOvicnoU8NpPHhO96NBwbhV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TPL-REQ-002_Template-Matriz-de-Rastreabilidade.docx</t>
+          <t>TPL-REQ-001_Template-Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1W_0c8aevifCLVgNw8ecK3Djf4ar3Oatj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1IGz8Jxln6UO_tCFNplT6fcHxq-5KEVB5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TPL-REQ-002_Template-Matriz-de-Rastreabilidade.md</t>
+          <t>TPL-REQ-001_Template-Documento-de-Requisitos.md</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/168VucASymzvMt5g-p_F1ZhfwocT5z7Ww/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19Uus1IU9ab_z960ITUxm8xaNluk7_LGz/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TPL-VV-001_Template-Plano-de-Verificacao-e-Validacao.docx</t>
+          <t>TPL-REQ-002_Template-Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s0sjWb1MolACQ-3-GQajFDpnilc7kILw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1W_0c8aevifCLVgNw8ecK3Djf4ar3Oatj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TPL-VV-001_Template-Plano-de-Verificacao-e-Validacao.md</t>
+          <t>TPL-REQ-002_Template-Matriz-de-Rastreabilidade.md</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1QLlkyRwI39PE_ih1Vz-rXkSWnivf4fQb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/168VucASymzvMt5g-p_F1ZhfwocT5z7Ww/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>TPL-VV-002_Template-Registro-de-Revisao-por-Pares.docx</t>
+          <t>TPL-VV-001_Template-Plano-de-Verificacao-e-Validacao.docx</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dgiWFADcf1hSgfkggK742ZZe0eEzaIcW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1s0sjWb1MolACQ-3-GQajFDpnilc7kILw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TPL-VV-002_Template-Registro-de-Revisao-por-Pares.md</t>
+          <t>TPL-VV-001_Template-Plano-de-Verificacao-e-Validacao.md</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4741,51 +4741,51 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DFf9iA8lOkL7694hyz2x_PV62A_itJoA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1QLlkyRwI39PE_ih1Vz-rXkSWnivf4fQb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>00_INDICE-AASPCNJ01_Mapa-de-Registros.md</t>
+          <t>TPL-VV-002_Template-Registro-de-Revisao-por-Pares.docx</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D36lT0gskRVQ2uCke-m0hlrWD_zs6lXk/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dgiWFADcf1hSgfkggK742ZZe0eEzaIcW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ADAP-AASPCNJ01-001_Registro-de-Adaptacao.docx</t>
+          <t>TPL-VV-002_Template-Registro-de-Revisao-por-Pares.md</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14GFOTJj6jxDsV62h60zCqIgxnRW-DbWW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1DFf9iA8lOkL7694hyz2x_PV62A_itJoA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ADAP-AASPCNJ01-001_Registro-de-Adaptacao.md</t>
+          <t>00_INDICE-AASPCNJ01_Mapa-de-Registros.md</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1AQtE9Q0KvpKNIY8fWtCWUrUCzhlx9iTa/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D36lT0gskRVQ2uCke-m0hlrWD_zs6lXk/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ATA-AASPCNJ01-001_Ata-Alinhamento-Fluxo-CNJ.docx</t>
+          <t>00_INDICEAASPCNJ01_MapadeRegistros.docx</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12sOcC6FDaP-3OdoM1_duAMNNcbgYsQvb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1kf3EdS_AsVImdD6P_03zCt-OF7_UHj6N/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4841,17 +4841,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ATA-AASPCNJ01-001_Ata-Alinhamento-Fluxo-CNJ.md</t>
+          <t>ADAP-AASPCNJ01-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MEhewPJ_pd35kgdky_xETqE3I6XR7zMC/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14GFOTJj6jxDsV62h60zCqIgxnRW-DbWW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4863,17 +4863,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>CAP-AASPCNJ01-001_Registro-de-Capacitacao-da-Equipe.docx</t>
+          <t>ADAP-AASPCNJ01-001_Registro-de-Adaptacao.md</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11db2exVuX-huVhgL8azaDzByfMFQv_pb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1AQtE9Q0KvpKNIY8fWtCWUrUCzhlx9iTa/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4885,17 +4885,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CAP-AASPCNJ01-001_Registro-de-Capacitacao-da-Equipe.md</t>
+          <t>ATA-AASPCNJ01-001_Ata-Alinhamento-Fluxo-CNJ.docx</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jba7CzH_o_sggKZ6Y8pjjfxXTPwIMjf4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/12sOcC6FDaP-3OdoM1_duAMNNcbgYsQvb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4907,17 +4907,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>CR-AASPCNJ01-001_Change-Request.docx</t>
+          <t>ATA-AASPCNJ01-001_Ata-Alinhamento-Fluxo-CNJ.md</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1J3XOn56R7ruWa8vhPAnVzI7r092DFLY-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1MEhewPJ_pd35kgdky_xETqE3I6XR7zMC/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>CR-AASPCNJ01-001_Change-Request.md</t>
+          <t>CAP-AASPCNJ01-001_Registro-de-Capacitacao-da-Equipe.docx</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LC7TXf4KqwN2oIEgL4sq74Zhg_eCPYST/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11db2exVuX-huVhgL8azaDzByfMFQv_pb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4951,17 +4951,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>GCO-AASPCNJ01-001_Registro-de-Configuracao.docx</t>
+          <t>CAP-AASPCNJ01-001_Registro-de-Capacitacao-da-Equipe.md</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1IJozbK4BobNpyION4zPWa_s2auynxhv9/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jba7CzH_o_sggKZ6Y8pjjfxXTPwIMjf4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4973,17 +4973,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>GCO-AASPCNJ01-001_Registro-de-Configuracao.md</t>
+          <t>CR-AASPCNJ01-001_Change-Request.docx</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Dolv6F6w1b-HrjYBemHVis-JZjL3-vJR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1J3XOn56R7ruWa8vhPAnVzI7r092DFLY-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4995,17 +4995,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>GDE-AASPCNJ01-001_Registro-de-Analise-de-Decisao.docx</t>
+          <t>CR-AASPCNJ01-001_Change-Request.md</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1EpobYWmsjCftVdxosshioK0mCuXVFlEq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LC7TXf4KqwN2oIEgL4sq74Zhg_eCPYST/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5017,17 +5017,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>GDE-AASPCNJ01-001_Registro-de-Analise-de-Decisao.md</t>
+          <t>GCO-AASPCNJ01-001_Registro-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15uYGS_DNz4Dt1mxmx4-PkQB9MUGfjffr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1IJozbK4BobNpyION4zPWa_s2auynxhv9/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5039,17 +5039,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>GEST-AASPCNJ01_Planilha-de-Gestao-do-Projeto.xlsx</t>
+          <t>GCO-AASPCNJ01-001_Registro-de-Configuracao.md</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Vdng-5mBCjlXpajdZ6ScLD67c8e85qob/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Dolv6F6w1b-HrjYBemHVis-JZjL3-vJR/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>GQA-AASPCNJ01-001_Registro-de-GQA.docx</t>
+          <t>GDE-AASPCNJ01-001_Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1AI6TXKQ5f6Oh5g6VmFgzTmXNQHEtLOlh/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1EpobYWmsjCftVdxosshioK0mCuXVFlEq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>GQA-AASPCNJ01-001_Registro-de-GQA.md</t>
+          <t>GDE-AASPCNJ01-001_Registro-de-Analise-de-Decisao.md</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1aYLuwSN8gKUIFpg3W53cgZGHwjUDmpb7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15uYGS_DNz4Dt1mxmx4-PkQB9MUGfjffr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5105,17 +5105,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ITP-AASPCNJ01-001_Estrategia-de-Integracao.docx</t>
+          <t>GEST-AASPCNJ01_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tobpnNoEQf5LarNnPEJAEJnt5BAZGrtQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Vdng-5mBCjlXpajdZ6ScLD67c8e85qob/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5127,17 +5127,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ITP-AASPCNJ01-001_Estrategia-de-Integracao.md</t>
+          <t>GQA-AASPCNJ01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cnLnAHipePGdvP26u1bQqQNAGlLCQ_LC/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1AI6TXKQ5f6Oh5g6VmFgzTmXNQHEtLOlh/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5149,17 +5149,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MED-AASPCNJ01-001_Registro-de-Medicao.docx</t>
+          <t>GQA-AASPCNJ01-001_Registro-de-GQA.md</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ePiJ3ONIXZf2gN00FzXuyUCIXdrpezsx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1aYLuwSN8gKUIFpg3W53cgZGHwjUDmpb7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5171,17 +5171,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MED-AASPCNJ01-001_Registro-de-Medicao.md</t>
+          <t>ITP-AASPCNJ01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uewnWBXzHNoc6W1skfMxGLgrWRS-lGh3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tobpnNoEQf5LarNnPEJAEJnt5BAZGrtQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5193,17 +5193,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PCP-AASPCNJ01-001_Documento-de-Design.docx</t>
+          <t>ITP-AASPCNJ01-001_Estrategia-de-Integracao.md</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ywDtDrM3zHptY2XfL6ut22ra3MEbuLTe/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1cnLnAHipePGdvP26u1bQqQNAGlLCQ_LC/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5215,17 +5215,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PCP-AASPCNJ01-001_Documento-de-Design.md</t>
+          <t>MED-AASPCNJ01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Unza8xmgkJujBYgKw8pg35-61abEm6WL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ePiJ3ONIXZf2gN00FzXuyUCIXdrpezsx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5237,17 +5237,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PLA-AASPCNJ01-001_Plano-de-Projeto.docx</t>
+          <t>MED-AASPCNJ01-001_Registro-de-Medicao.md</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1y9zo8Fx1AewE2z9GVdmhsecKySyDoSf6/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1uewnWBXzHNoc6W1skfMxGLgrWRS-lGh3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5259,17 +5259,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PLA-AASPCNJ01-001_Plano-de-Projeto.md</t>
+          <t>PCP-AASPCNJ01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15UPh6z7b9ZUbUVUBpANR2ow4EsIDxn9Y/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ywDtDrM3zHptY2XfL6ut22ra3MEbuLTe/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5281,17 +5281,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>RAC-AASPCNJ01-001_Relatorio-de-Acompanhamento.docx</t>
+          <t>PCP-AASPCNJ01-001_Documento-de-Design.md</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1G_0Odyq4HbI3nfCyDh7-zZoXDgu_BiON/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Unza8xmgkJujBYgKw8pg35-61abEm6WL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>RAC-AASPCNJ01-001_Relatorio-de-Acompanhamento.md</t>
+          <t>PLA-AASPCNJ01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16scQtbSvdpQbF0OS7KCRBRDLBpLI6gt7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1y9zo8Fx1AewE2z9GVdmhsecKySyDoSf6/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5325,17 +5325,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>RASTR-AASPCNJ01-001_Matriz-de-Rastreabilidade.docx</t>
+          <t>PLA-AASPCNJ01-001_Plano-de-Projeto.md</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1lfPyboZZ3hd-8g3IzjQRQciVYXCztgZw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15UPh6z7b9ZUbUVUBpANR2ow4EsIDxn9Y/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5347,17 +5347,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>RASTR-AASPCNJ01-001_Matriz-de-Rastreabilidade.md</t>
+          <t>RAC-AASPCNJ01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1iDvjlcbuCL2sr01UQ1vqRONHz0aST6x8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1G_0Odyq4HbI3nfCyDh7-zZoXDgu_BiON/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>REL-VV-AASPCNJ01-001_Relatorio-de-Execucao-de-Testes.docx</t>
+          <t>RAC-AASPCNJ01-001_Relatorio-de-Acompanhamento.md</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1whC8gTS2Mz1CW7QajDlOMvfXNlxt5AP6/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/16scQtbSvdpQbF0OS7KCRBRDLBpLI6gt7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5391,17 +5391,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>REL-VV-AASPCNJ01-001_Relatorio-de-Execucao-de-Testes.md</t>
+          <t>RASTR-AASPCNJ01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UECG0sMcEQrEyTkMtTW2vDyOGYuPYlov/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1lfPyboZZ3hd-8g3IzjQRQciVYXCztgZw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5413,17 +5413,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>REQ-AASPCNJ01-001_Documento-de-Requisitos.docx</t>
+          <t>RASTR-AASPCNJ01-001_Matriz-de-Rastreabilidade.md</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1GDwHhtK1Nc-2AptWo8HIryVHeOF8hzj5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1iDvjlcbuCL2sr01UQ1vqRONHz0aST6x8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5435,17 +5435,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>REQ-AASPCNJ01-001_Documento-de-Requisitos.md</t>
+          <t>REL-VV-AASPCNJ01-001_Relatorio-de-Execucao-de-Testes.docx</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YFHxBJU-mxG2nTGtwGVL2EGqDw6MYkcV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1whC8gTS2Mz1CW7QajDlOMvfXNlxt5AP6/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5457,17 +5457,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>REV-AASPCNJ01-001_Registro-de-Revisao-por-Pares.docx</t>
+          <t>REL-VV-AASPCNJ01-001_Relatorio-de-Execucao-de-Testes.md</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1PfM9kKAjFJofhtJn5xqgicqG-0-v3mA-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1UECG0sMcEQrEyTkMtTW2vDyOGYuPYlov/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5479,17 +5479,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>REV-AASPCNJ01-001_Registro-de-Revisao-por-Pares.md</t>
+          <t>REQ-AASPCNJ01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YPUEV8VMC4rLiB6ie182lY_9nRz72wdA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1GDwHhtK1Nc-2AptWo8HIryVHeOF8hzj5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5501,17 +5501,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>TAP-AASPCNJ01-001_Termo-de-Abertura.docx</t>
+          <t>REQ-AASPCNJ01-001_Documento-de-Requisitos.md</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hKBUW2dTTfmd8PEs36tEuIQjsKjPAuRF/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YFHxBJU-mxG2nTGtwGVL2EGqDw6MYkcV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5523,17 +5523,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>TAP-AASPCNJ01-001_Termo-de-Abertura.md</t>
+          <t>REV-AASPCNJ01-001_Registro-de-Revisao-por-Pares.docx</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1l6PmtiKd-wy4CyjEgbhN3gky-4NRb3lk/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1PfM9kKAjFJofhtJn5xqgicqG-0-v3mA-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5545,17 +5545,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>VV-AASPCNJ01-001_Plano-de-VV.docx</t>
+          <t>REV-AASPCNJ01-001_Registro-de-Revisao-por-Pares.md</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/199h316ZoZ43k7W_rnPpNq6GTBr502zuu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YPUEV8VMC4rLiB6ie182lY_9nRz72wdA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5567,83 +5567,83 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>VV-AASPCNJ01-001_Plano-de-VV.md</t>
+          <t>TAP-AASPCNJ01-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1svrQKE2lJHz91RMvgbx21RNEHw60XMoz/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hKBUW2dTTfmd8PEs36tEuIQjsKjPAuRF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.docx</t>
+          <t>TAP-AASPCNJ01-001_Termo-de-Abertura.md</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NaEJlUDHw0FE6fgH28gpifHft7ZLxUyL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1l6PmtiKd-wy4CyjEgbhN3gky-4NRb3lk/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.md</t>
+          <t>VV-AASPCNJ01-001_Plano-de-VV.docx</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jd-ueS7tJ7ipM9MvSxY0E9QI04RMOAxj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/199h316ZoZ43k7W_rnPpNq6GTBr502zuu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.docx</t>
+          <t>VV-AASPCNJ01-001_Plano-de-VV.md</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LNzyoQkTM7oLgWtSCPY6VxNqt4JS_MzM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1svrQKE2lJHz91RMvgbx21RNEHw60XMoz/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5655,17 +5655,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.md</t>
+          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JDPNC85L1TdEuweMvEmJphAH00Y8VbT0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NaEJlUDHw0FE6fgH28gpifHft7ZLxUyL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5677,17 +5677,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-001_Ata-de-Kickoff.docx</t>
+          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.md</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pjAXblbrxR8Y6p5eq2BDYRBpiYlK3Ag_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jd-ueS7tJ7ipM9MvSxY0E9QI04RMOAxj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5699,17 +5699,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-001_Ata-de-Kickoff.md</t>
+          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15oaq3TW916Xz4agaxLeZq1-WTml1R5YU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LNzyoQkTM7oLgWtSCPY6VxNqt4JS_MzM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5721,17 +5721,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.docx</t>
+          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cypxWHL-NU9CPnLV47N-bKnP0QrSIB17/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JDPNC85L1TdEuweMvEmJphAH00Y8VbT0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5743,17 +5743,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.md</t>
+          <t>ATA-FRUKI01-001_Ata-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ficMpIGp18dxZ3mASn0bnpOcFIF6IkM5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pjAXblbrxR8Y6p5eq2BDYRBpiYlK3Ag_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.docx</t>
+          <t>ATA-FRUKI01-001_Ata-de-Kickoff.md</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1m0odZUeHy212r9AQwyZ_sfwXzznT4oqJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15oaq3TW916Xz4agaxLeZq1-WTml1R5YU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5787,17 +5787,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.md</t>
+          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.docx</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Qk8B-Ny6zACkDanQ0QBsqznIzvzIX3xd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1cypxWHL-NU9CPnLV47N-bKnP0QrSIB17/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5809,17 +5809,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.docx</t>
+          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.md</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10Qo6yB8nqAQmzacMbuLZaVv1ZaX178Lt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ficMpIGp18dxZ3mASn0bnpOcFIF6IkM5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5831,17 +5831,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.md</t>
+          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.docx</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1rfeMludEbjF7UISCTitVTklQgOVogPet/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1m0odZUeHy212r9AQwyZ_sfwXzznT4oqJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5853,17 +5853,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.docx</t>
+          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.md</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1VmGwsZK4GLu_zpzmrHnD2XOChsiR1GZr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Qk8B-Ny6zACkDanQ0QBsqznIzvzIX3xd/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5875,17 +5875,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.md</t>
+          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.docx</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fL2lzK5ltJRAvrvBkZRGzHxNEI9xu5Bw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/10Qo6yB8nqAQmzacMbuLZaVv1ZaX178Lt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5897,17 +5897,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.docx</t>
+          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.md</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ujgsYTHnAVE_J60APn-OqGSRaCTbfPHf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1rfeMludEbjF7UISCTitVTklQgOVogPet/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5919,17 +5919,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.md</t>
+          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.docx</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/18EWiPMrnjSsiQaE_8C28PSBqL_lgVLlm/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1VmGwsZK4GLu_zpzmrHnD2XOChsiR1GZr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5941,17 +5941,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.docx</t>
+          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.md</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bNAl7ljD0PhTyZEb-2ngdIbBzCpvNY2q/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fL2lzK5ltJRAvrvBkZRGzHxNEI9xu5Bw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5963,17 +5963,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.md</t>
+          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.docx</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RmwGe1-htZ1eswLCBIdw6KiYYnUMyFz7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ujgsYTHnAVE_J60APn-OqGSRaCTbfPHf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-008_Ata-Kickoff-PacoteFinal24.md</t>
+          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.md</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RNsmRLVuhzH7B7xEow8TR1epFtoTJuTG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18EWiPMrnjSsiQaE_8C28PSBqL_lgVLlm/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.docx</t>
+          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.docx</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1z2TIuyQQTiU7fOKmK0kQfziTtE8NqiLc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bNAl7ljD0PhTyZEb-2ngdIbBzCpvNY2q/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.md</t>
+          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.md</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/18ut_8KPcueRiLUgl0CPLPR-G2vvZPtx3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RmwGe1-htZ1eswLCBIdw6KiYYnUMyFz7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6051,17 +6051,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>GCO-FRUKI01-001_Registro-de-Configuracao.docx</t>
+          <t>ATA-FRUKI01-008_Ata-Kickoff-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fMcui7ebx_4af41JtRltlCCJzDWkd1eA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RNsmRLVuhzH7B7xEow8TR1epFtoTJuTG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6073,17 +6073,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>GCO-FRUKI01-001_Registro-de-Configuracao.md</t>
+          <t>ATAFRUKI01008_AtaKickoffPacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19M3LWTGKSzJ_rDQJfGF5sSg2Stj4ooYw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11alVpwlnsPjgd1_PO4OzMBXeJLRz6PXi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>GDE-FRUKI01-001_Registro-de-Decisao.docx</t>
+          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.docx</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1h8FKsNP59PnO8tzm2WEJ_vgsZYRSmjwX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1z2TIuyQQTiU7fOKmK0kQfziTtE8NqiLc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>GDE-FRUKI01-001_Registro-de-Decisao.md</t>
+          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.md</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1y8vwxSDf1lQ_dMEoGp96MINftpHX1yzj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18ut_8KPcueRiLUgl0CPLPR-G2vvZPtx3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>GQA-FRUKI01-001_Registro-de-GQA.docx</t>
+          <t>GCO-FRUKI01-001_Registro-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jmdev8ggRDsbM_CrkMQY_oKaImvKG4vM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fMcui7ebx_4af41JtRltlCCJzDWkd1eA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>GQA-FRUKI01-001_Registro-de-GQA.md</t>
+          <t>GCO-FRUKI01-001_Registro-de-Configuracao.md</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LQg4Ts7Gp-dH1rHTCtPzOWBXODTb-xB0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19M3LWTGKSzJ_rDQJfGF5sSg2Stj4ooYw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.docx</t>
+          <t>GDE-FRUKI01-001_Registro-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19YCw05XWIRh-NaI5GWf1c-MF6m5AhIra/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1h8FKsNP59PnO8tzm2WEJ_vgsZYRSmjwX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.md</t>
+          <t>GDE-FRUKI01-001_Registro-de-Decisao.md</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1V-b-qbGgRW_GmmllG836nIib4F-1bxmQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1y8vwxSDf1lQ_dMEoGp96MINftpHX1yzj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.docx</t>
+          <t>GQA-FRUKI01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1A-6S0ZZmHteTzIjSNP46H2OJYgeI-Gc7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jmdev8ggRDsbM_CrkMQY_oKaImvKG4vM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.md</t>
+          <t>GQA-FRUKI01-001_Registro-de-GQA.md</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1u4DcmW9hpA01pW7nlBsxOxkvs7OFFkAX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LQg4Ts7Gp-dH1rHTCtPzOWBXODTb-xB0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>LI-FRUKI01-001_Licoes-Aprendidas.docx</t>
+          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pXvWCErdbUdvvAcXV93935DeGW6bJ7xL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19YCw05XWIRh-NaI5GWf1c-MF6m5AhIra/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>LI-FRUKI01-001_Licoes-Aprendidas.md</t>
+          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.md</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1-LL6sPo2lPFF-5U-rT-v0w15M_USlgul/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1V-b-qbGgRW_GmmllG836nIib4F-1bxmQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>MED-FRUKI01-001_Registro-de-Medicao.docx</t>
+          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D6gCK_SBP31WdmYGToQH2iCZV1RdzhWI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1A-6S0ZZmHteTzIjSNP46H2OJYgeI-Gc7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>MED-FRUKI01-001_Registro-de-Medicao.md</t>
+          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1VXH2Vf2-E0ExrU0D-meV5m2J1TU5rnT3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1u4DcmW9hpA01pW7nlBsxOxkvs7OFFkAX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PCP-FRUKI01-001_Documento-de-Design.docx</t>
+          <t>LI-FRUKI01-001_Licoes-Aprendidas.docx</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ff6Ha1FH1T1XAJGnmdy2QvkrqXxCUg2s/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pXvWCErdbUdvvAcXV93935DeGW6bJ7xL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PCP-FRUKI01-001_Documento-de-Design.md</t>
+          <t>LI-FRUKI01-001_Licoes-Aprendidas.md</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZdDvNKE7Q1pA5rx5QPnYLd9FQHaqq-W8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-LL6sPo2lPFF-5U-rT-v0w15M_USlgul/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.docx</t>
+          <t>MED-FRUKI01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17KodAvypysQkbqocfQIrlE2q1dfRIUnY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D6gCK_SBP31WdmYGToQH2iCZV1RdzhWI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.md</t>
+          <t>MED-FRUKI01-001_Registro-de-Medicao.md</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1OSDTx1gAc6_yJw_cN8rhwy4doQynXsws/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1VXH2Vf2-E0ExrU0D-meV5m2J1TU5rnT3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PLA-FRUKI01-001_Plano-de-Projeto.docx</t>
+          <t>PCP-FRUKI01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1WEPaZNg7rxj29B48l_scz7x7CyLlvoSf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ff6Ha1FH1T1XAJGnmdy2QvkrqXxCUg2s/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PLA-FRUKI01-001_Plano-de-Projeto.md</t>
+          <t>PCP-FRUKI01-001_Documento-de-Design.md</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ak4cVI3YUmLkRgLKhcjIooEnGCJzS8J8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZdDvNKE7Q1pA5rx5QPnYLd9FQHaqq-W8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.docx</t>
+          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1d0l6IhtfbI9hE0UYxQm6nVq9grpjKnpn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17KodAvypysQkbqocfQIrlE2q1dfRIUnY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.md</t>
+          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s4eNRbcYfsKtdn4cleCJkIN9t2cJAjGI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1OSDTx1gAc6_yJw_cN8rhwy4doQynXsws/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.docx</t>
+          <t>PLA-FRUKI01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_C3hZUp-7-2ldAa2BmIfZ3tMfa9WX0bd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1WEPaZNg7rxj29B48l_scz7x7CyLlvoSf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.md</t>
+          <t>PLA-FRUKI01-001_Plano-de-Projeto.md</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13Yx9B8mhKozIn9UHPmgI25DWFBsOfqD8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ak4cVI3YUmLkRgLKhcjIooEnGCJzS8J8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6579,17 +6579,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>RAC-FRUKI01-002_Planilha-de-Gestao-do-Projeto.xlsx</t>
+          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RsktvVNbrH1f-RmcV3_AmIu3uJt9Q7sH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1d0l6IhtfbI9hE0UYxQm6nVq9grpjKnpn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>RAC-FRUKI01-002_Relatorio-de-Acompanhamento-Pacote1.md</t>
+          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1o6AlWFp1nR1m5JRHVda54B19LaoFoMPO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1s4eNRbcYfsKtdn4cleCJkIN9t2cJAjGI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.docx</t>
+          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SokajsndvgCtPAX7FyUpNp9mIDxQrVQf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_C3hZUp-7-2ldAa2BmIfZ3tMfa9WX0bd/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.md</t>
+          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.md</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ezQXGXqPC-2UMfRdDvudgmasO6TMO5n8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13Yx9B8mhKozIn9UHPmgI25DWFBsOfqD8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6667,17 +6667,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.docx</t>
+          <t>RAC-FRUKI01-002_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1S4nR_PkZnGQrm6ppWv47ftgH2ptyG9xJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RsktvVNbrH1f-RmcV3_AmIu3uJt9Q7sH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.md</t>
+          <t>RAC-FRUKI01-002_Relatorio-de-Acompanhamento-Pacote1.md</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s3__jTdqb1JrJQw3l9DS-tzsy28cYC2k/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1o6AlWFp1nR1m5JRHVda54B19LaoFoMPO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>REQ-FRUKI01-001_Documento-de-Requisitos.docx</t>
+          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1mCQ9GroaEFEjulblg31P0Kdknw95w8LJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SokajsndvgCtPAX7FyUpNp9mIDxQrVQf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>REQ-FRUKI01-001_Documento-de-Requisitos.md</t>
+          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.md</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1m-7E7kW4OvRkUWA6EpO3BFveXiLIVHOF/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ezQXGXqPC-2UMfRdDvudgmasO6TMO5n8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.docx</t>
+          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1GexOXykQE4rnKFPmeW1kVQac18vsnlnQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1S4nR_PkZnGQrm6ppWv47ftgH2ptyG9xJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.md</t>
+          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1QSxYq6k8W1KxoVcr90P_31Xzmbb5uN5x/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1s3__jTdqb1JrJQw3l9DS-tzsy28cYC2k/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>TAE-FRUKI01-001_Termo-de-Encerramento.docx</t>
+          <t>REQ-FRUKI01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JNvLtWIaqno7WXqzPfQwcK1bRE3UjCRv/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1mCQ9GroaEFEjulblg31P0Kdknw95w8LJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>TAE-FRUKI01-001_Termo-de-Encerramento.md</t>
+          <t>REQ-FRUKI01-001_Documento-de-Requisitos.md</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CWoASfmkMEYq_njAEpXGu_vwEjx7pAEn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1m-7E7kW4OvRkUWA6EpO3BFveXiLIVHOF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.docx</t>
+          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D3T0RHrOPhOq08Edxc1fWW-cZ1uR-e2n/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1GexOXykQE4rnKFPmeW1kVQac18vsnlnQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.md</t>
+          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TJpNI9gAt8nH0qi87whhkajt8msTG1TO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1QSxYq6k8W1KxoVcr90P_31Xzmbb5uN5x/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>TAP-FRUKI01-001_Termo-de-Abertura.docx</t>
+          <t>TAE-FRUKI01-001_Termo-de-Encerramento.docx</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ehO_9gQoPrLS-Ykhxfnnsrn9KZ9o8zdH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JNvLtWIaqno7WXqzPfQwcK1bRE3UjCRv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>TAP-FRUKI01-001_Termo-de-Abertura.md</t>
+          <t>TAE-FRUKI01-001_Termo-de-Encerramento.md</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14-7t7EZ-5YdrL7xVn6VgTR75jDcQ9EW_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CWoASfmkMEYq_njAEpXGu_vwEjx7pAEn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.docx</t>
+          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UUmn_lYKBv8eG5UZBaLipFbSMdnYTxgU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D3T0RHrOPhOq08Edxc1fWW-cZ1uR-e2n/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.md</t>
+          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1q0Jciu5Wzc6Zn7-k55piZ2OS7Ty4gw71/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TJpNI9gAt8nH0qi87whhkajt8msTG1TO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>VV-FRUKI01-001_Plano-VeV.docx</t>
+          <t>TAP-FRUKI01-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1yCFY98oM8rlf44HUIeERib4_7jtYsKeU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ehO_9gQoPrLS-Ykhxfnnsrn9KZ9o8zdH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>VV-FRUKI01-001_Plano-VeV.md</t>
+          <t>TAP-FRUKI01-001_Termo-de-Abertura.md</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZtSNIU4pURtj7fcqmo-Ze_PUgT8Xd8qS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14-7t7EZ-5YdrL7xVn6VgTR75jDcQ9EW_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.docx</t>
+          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1d_okleyBKoPtPW2zEy7300KiXoWL62oj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1UUmn_lYKBv8eG5UZBaLipFbSMdnYTxgU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.md</t>
+          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7051,19 +7051,19 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ifZ0yJp1bIsYSQtVRi9gIzDztsm9Uj3c/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1q0Jciu5Wzc6Zn7-k55piZ2OS7Ty4gw71/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>ADAP-GASMIG02-001_Registro-de-Adaptacao.docx</t>
+          <t>VV-FRUKI01-001_Plano-VeV.docx</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7073,19 +7073,19 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uDnjyU3hDOdzbVZPUFA-1PGqXCsuDeS7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1yCFY98oM8rlf44HUIeERib4_7jtYsKeU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>ADAP-GASMIG02-001_Registro-de-Adaptacao.md</t>
+          <t>VV-FRUKI01-001_Plano-VeV.md</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7095,19 +7095,19 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bejNoYCCCfk5qhr7XWZz2N5g8q3KPhCD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZtSNIU4pURtj7fcqmo-Ze_PUgT8Xd8qS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>ADAP-GASMIG02-002_Registro-de-Adaptacao-OS002.docx</t>
+          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7117,19 +7117,19 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1oQshhvn5DIq1DoB3rybc8jEbP_OdEnfn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1d_okleyBKoPtPW2zEy7300KiXoWL62oj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>ADAP-GASMIG02-002_Registro-de-Adaptacao-OS002.md</t>
+          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Yi_n_zxaS-YAOGbQ8gg16RdRtmvKn6CA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ifZ0yJp1bIsYSQtVRi9gIzDztsm9Uj3c/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>ATA-GASMIG02-001_Ata-de-Kickoff.docx</t>
+          <t>ADAP-GASMIG02-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1XcstqfQTQC0cm8wZgfc9oLgjSknU6Ueq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1uDnjyU3hDOdzbVZPUFA-1PGqXCsuDeS7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ATA-GASMIG02-001_Ata-de-Kickoff.md</t>
+          <t>ADAP-GASMIG02-001_Registro-de-Adaptacao.md</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/173I8V-9u9y4GjYm6CqXrqhL5_XLf0-Tx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bejNoYCCCfk5qhr7XWZz2N5g8q3KPhCD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>ATA-GASMIG02-002_Ata-de-Aceite-OS001.docx</t>
+          <t>ADAP-GASMIG02-002_Registro-de-Adaptacao-OS002.docx</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CcRbEbIcDWeHO7sOznH_FcuK-uVVusM0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1oQshhvn5DIq1DoB3rybc8jEbP_OdEnfn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ATA-GASMIG02-002_Ata-de-Aceite-OS001.md</t>
+          <t>ADAP-GASMIG02-002_Registro-de-Adaptacao-OS002.md</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SMbROaSFGiRfxwoXqmEw9SWLkqJ0nZYZ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Yi_n_zxaS-YAOGbQ8gg16RdRtmvKn6CA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ATA-GASMIG02-003_Apresentacao-Entrega-OS002.docx</t>
+          <t>ATA-GASMIG02-001_Ata-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YCW3PFHS2p1bh8O6VWyZ8y2NFoG6ZWFN/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1XcstqfQTQC0cm8wZgfc9oLgjSknU6Ueq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7261,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ATA-GASMIG02-003_Apresentacao-Entrega-OS002.md</t>
+          <t>ATA-GASMIG02-001_Ata-de-Kickoff.md</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Un3zSWdjWObqjJfrr8dwWvNnHDKNzuMk/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/173I8V-9u9y4GjYm6CqXrqhL5_XLf0-Tx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>CAP-GASMIG02-001_Registro-de-Capacitacao-da-Equipe.docx</t>
+          <t>ATA-GASMIG02-002_Ata-de-Aceite-OS001.docx</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ibleg7tRQDHfYp3ahRpAlbYjKetFDzzT/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CcRbEbIcDWeHO7sOznH_FcuK-uVVusM0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>CAP-GASMIG02-001_Registro-de-Capacitacao-da-Equipe.md</t>
+          <t>ATA-GASMIG02-002_Ata-de-Aceite-OS001.md</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1S5Rvx0kYOz7QPQDU_BA3SpNA1xdAk8Fa/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SMbROaSFGiRfxwoXqmEw9SWLkqJ0nZYZ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GCO-GASMIG02-001_Gerencia-de-Configuracao.docx</t>
+          <t>ATA-GASMIG02-003_Apresentacao-Entrega-OS002.docx</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1qpIzDVbsmVYkiXW9NNdciOuv5iovMNu4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YCW3PFHS2p1bh8O6VWyZ8y2NFoG6ZWFN/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GCO-GASMIG02-001_Gerencia-de-Configuracao.md</t>
+          <t>ATA-GASMIG02-003_Apresentacao-Entrega-OS002.md</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/193BAen9QIQt12KAzqakGH_bNUvMEdxpj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Un3zSWdjWObqjJfrr8dwWvNnHDKNzuMk/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDE-GASMIG02-001_Registro-de-Analise-de-Decisao.docx</t>
+          <t>CAP-GASMIG02-001_Registro-de-Capacitacao-da-Equipe.docx</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1sqAtX-R1-EjASMtMCnp_fjiessTaSaQU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ibleg7tRQDHfYp3ahRpAlbYjKetFDzzT/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDE-GASMIG02-001_Registro-de-Analise-de-Decisao.md</t>
+          <t>CAP-GASMIG02-001_Registro-de-Capacitacao-da-Equipe.md</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15jlfJFiL4Kw0-bg2ZZcKnt7eKmay43k5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1S5Rvx0kYOz7QPQDU_BA3SpNA1xdAk8Fa/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7415,17 +7415,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GEST-GASMIG02_Planilha-de-Gestao-do-Projeto.xlsx</t>
+          <t>GCO-GASMIG02-001_Gerencia-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1r_dSFP9AmEnj79FkmqU80OkuYWnwzfZS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1qpIzDVbsmVYkiXW9NNdciOuv5iovMNu4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7437,17 +7437,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>GQA-GASMIG02-001_Registro-de-GQA.docx</t>
+          <t>GCO-GASMIG02-001_Gerencia-de-Configuracao.md</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1V-T1g_9AKu9TLFPROMR0fA1gkyx180a-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/193BAen9QIQt12KAzqakGH_bNUvMEdxpj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7459,17 +7459,17 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>GQA-GASMIG02-001_Registro-de-GQA.md</t>
+          <t>GDE-GASMIG02-001_Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uDY2HGSwfZRlYwyZ5zGbGQ_290rYm_Xd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1sqAtX-R1-EjASMtMCnp_fjiessTaSaQU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>ITP-GASMIG02-002_Estrategia-de-Integracao-OS002.docx</t>
+          <t>GDE-GASMIG02-001_Registro-de-Analise-de-Decisao.md</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JIAbQHVpTSO3V0AKGnWyVwEs6zuTWX7R/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15jlfJFiL4Kw0-bg2ZZcKnt7eKmay43k5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7503,17 +7503,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>ITP-GASMIG02-002_Estrategia-de-Integracao-OS002.md</t>
+          <t>GEST-GASMIG02_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15xAI-a66USbhl_h-DlQ4iWYBif6a4NYy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1r_dSFP9AmEnj79FkmqU80OkuYWnwzfZS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>LI-GASMIG02-001_Licoes-Aprendidas.docx</t>
+          <t>GQA-GASMIG02-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ra9yyJuVYa2tmQW0DKwbJgannxAI2W0E/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1V-T1g_9AKu9TLFPROMR0fA1gkyx180a-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>LI-GASMIG02-001_Licoes-Aprendidas.md</t>
+          <t>GQA-GASMIG02-001_Registro-de-GQA.md</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jn56o4n7EISf_OPXoT7W91T_SeJSteQA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1uDY2HGSwfZRlYwyZ5zGbGQ_290rYm_Xd/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>MED-GASMIG02-001_Registro-de-Medicao.docx</t>
+          <t>ITP-GASMIG02-002_Estrategia-de-Integracao-OS002.docx</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LtjN_WSjn_g1wQ_RRLe4Z4KP6Cnu-Ohx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JIAbQHVpTSO3V0AKGnWyVwEs6zuTWX7R/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>MED-GASMIG02-001_Registro-de-Medicao.md</t>
+          <t>ITP-GASMIG02-002_Estrategia-de-Integracao-OS002.md</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1yRECVQiPUAD3E8A6sSqcIjuCWsGJFOnN/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15xAI-a66USbhl_h-DlQ4iWYBif6a4NYy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCP-GASMIG02-001_Documento-de-Design.docx</t>
+          <t>LI-GASMIG02-001_Licoes-Aprendidas.docx</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YI-40O6IWGMB0C_R6ytpbxc2w1E7W4fF/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ra9yyJuVYa2tmQW0DKwbJgannxAI2W0E/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCP-GASMIG02-001_Documento-de-Design.md</t>
+          <t>LI-GASMIG02-001_Licoes-Aprendidas.md</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1rRXvNXOxYx1RmwJPihw-IlOEnMHL3LPi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jn56o4n7EISf_OPXoT7W91T_SeJSteQA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCP-GASMIG02-002_Documento-de-Design-OS002.docx</t>
+          <t>MED-GASMIG02-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Q4M2R4uqiy81BP8L3HiQ_idRqmpMt8Cw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LtjN_WSjn_g1wQ_RRLe4Z4KP6Cnu-Ohx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCP-GASMIG02-002_Documento-de-Design-OS002.md</t>
+          <t>MED-GASMIG02-001_Registro-de-Medicao.md</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jR60AUVUBrZqmoZx6a1AKAAmbEdEUR0V/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1yRECVQiPUAD3E8A6sSqcIjuCWsGJFOnN/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PLA-GASMIG02-001_Plano-de-Projeto.docx</t>
+          <t>PCP-GASMIG02-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZIwX-h0RDNJfhO5AXev2vqhYrGHOr2qf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YI-40O6IWGMB0C_R6ytpbxc2w1E7W4fF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PLA-GASMIG02-001_Plano-de-Projeto.md</t>
+          <t>PCP-GASMIG02-001_Documento-de-Design.md</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1q5NeTQRiY7BnnB2UiWdcG_ggbMB_Oigy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1rRXvNXOxYx1RmwJPihw-IlOEnMHL3LPi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PLA-GASMIG02-002_Plano-de-Projeto-OS002.docx</t>
+          <t>PCP-GASMIG02-002_Documento-de-Design-OS002.docx</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jfUDk7bhCtOXUYDcBnpjOx8FARp2VqPH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Q4M2R4uqiy81BP8L3HiQ_idRqmpMt8Cw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7767,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PLA-GASMIG02-002_Plano-de-Projeto-OS002.md</t>
+          <t>PCP-GASMIG02-002_Documento-de-Design-OS002.md</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1OQok5rhtLilsAl3lboUjxAeWoRCa6SXA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jR60AUVUBrZqmoZx6a1AKAAmbEdEUR0V/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>RAC-GASMIG02-001_Relatorio-de-Acompanhamento.docx</t>
+          <t>PLA-GASMIG02-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bAl8o8UPkTb1AHypGNvRxEJG8UYswpvS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZIwX-h0RDNJfhO5AXev2vqhYrGHOr2qf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>RAC-GASMIG02-001_Relatorio-de-Acompanhamento.md</t>
+          <t>PLA-GASMIG02-001_Plano-de-Projeto.md</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/18grlbdgF-XIQJtb8UNmCvJ25UOqHWb9b/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1q5NeTQRiY7BnnB2UiWdcG_ggbMB_Oigy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>RASTR-GASMIG02-001_Matriz-de-Rastreabilidade.docx</t>
+          <t>PLA-GASMIG02-002_Plano-de-Projeto-OS002.docx</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_delTbo-PEeRpuGGGagv5p2SOF-ZNRos/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jfUDk7bhCtOXUYDcBnpjOx8FARp2VqPH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>RASTR-GASMIG02-001_Matriz-de-Rastreabilidade.md</t>
+          <t>PLA-GASMIG02-002_Plano-de-Projeto-OS002.md</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s5eS3sxpXkZh0TY8Ws0nl6jo8CRWPWyi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1OQok5rhtLilsAl3lboUjxAeWoRCa6SXA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>RASTR-GASMIG02-002_Matriz-de-Rastreabilidade-OS002.docx</t>
+          <t>RAC-GASMIG02-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tfy9oNEOsThCKNb1YrvQq8Ll1jX9kYJO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bAl8o8UPkTb1AHypGNvRxEJG8UYswpvS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>RASTR-GASMIG02-002_Matriz-de-Rastreabilidade-OS002.md</t>
+          <t>RAC-GASMIG02-001_Relatorio-de-Acompanhamento.md</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1WiIbZeuVyYE2ZPrnLjkoiqVH3_8Y3Igz/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18grlbdgF-XIQJtb8UNmCvJ25UOqHWb9b/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>REQ-GASMIG02-001_Documento-de-Requisitos.docx</t>
+          <t>RASTR-GASMIG02-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13duq0igfGKvJAHKh_sD9TN7WqTpuOfdn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_delTbo-PEeRpuGGGagv5p2SOF-ZNRos/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>REQ-GASMIG02-001_Documento-de-Requisitos.md</t>
+          <t>RASTR-GASMIG02-001_Matriz-de-Rastreabilidade.md</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1qU0dScZMsyE9b5u1RENM0M85uevSdmrL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1s5eS3sxpXkZh0TY8Ws0nl6jo8CRWPWyi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>REQ-GASMIG02-002_Documento-de-Requisitos-OS002.docx</t>
+          <t>RASTR-GASMIG02-002_Matriz-de-Rastreabilidade-OS002.docx</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_yN7yHPBc9iKilAlxd4pxj52G1_WoCHP/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tfy9oNEOsThCKNb1YrvQq8Ll1jX9kYJO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>REQ-GASMIG02-002_Documento-de-Requisitos-OS002.md</t>
+          <t>RASTR-GASMIG02-002_Matriz-de-Rastreabilidade-OS002.md</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tyw98Wg84EnhfdKkHSJw6IoGaXSZ6JgK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1WiIbZeuVyYE2ZPrnLjkoiqVH3_8Y3Igz/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>REV-GASMIG02-001_Registro-de-Verificacao-Tecnica.docx</t>
+          <t>REQ-GASMIG02-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1biHfNjSf_g7hnUcjBATCG48aG7ARNvRL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13duq0igfGKvJAHKh_sD9TN7WqTpuOfdn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>REV-GASMIG02-001_Registro-de-Verificacao-Tecnica.md</t>
+          <t>REQ-GASMIG02-001_Documento-de-Requisitos.md</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uDopfyiOr-PKrdBbesatAYkF1YOgH1g6/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1qU0dScZMsyE9b5u1RENM0M85uevSdmrL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>TAE-GASMIG02-001_Termo-de-Encerramento-OS001.docx</t>
+          <t>REQ-GASMIG02-002_Documento-de-Requisitos-OS002.docx</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1mw7eJBj6HANyIYJ1MgxEnO59ML9sl5aa/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_yN7yHPBc9iKilAlxd4pxj52G1_WoCHP/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>TAE-GASMIG02-001_Termo-de-Encerramento-OS001.md</t>
+          <t>REQ-GASMIG02-002_Documento-de-Requisitos-OS002.md</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16Tvn5wYajcpGwNyPouZCvoJWXDedha5s/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tyw98Wg84EnhfdKkHSJw6IoGaXSZ6JgK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>TAE-GASMIG02-002_Termo-de-Encerramento-OS002.docx</t>
+          <t>REV-GASMIG02-001_Registro-de-Verificacao-Tecnica.docx</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1-zvT45vPsVTAwmcEzQVak8qKT4dnQWEr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1biHfNjSf_g7hnUcjBATCG48aG7ARNvRL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>TAE-GASMIG02-002_Termo-de-Encerramento-OS002.md</t>
+          <t>REV-GASMIG02-001_Registro-de-Verificacao-Tecnica.md</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Gvd3sqaF500esvT_KQXRRYQOKtSLBa1f/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1uDopfyiOr-PKrdBbesatAYkF1YOgH1g6/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>TAP-GASMIG02-001_Termo-de-Abertura.docx</t>
+          <t>TAE-GASMIG02-001_Termo-de-Encerramento-OS001.docx</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1WW3VNRafS44JkZiXK29Rm7bYI7NbP9rS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1mw7eJBj6HANyIYJ1MgxEnO59ML9sl5aa/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>TAP-GASMIG02-001_Termo-de-Abertura.md</t>
+          <t>TAE-GASMIG02-001_Termo-de-Encerramento-OS001.md</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1X37fcpWgIcSM5LirpbU23geQekmjCp_i/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/16Tvn5wYajcpGwNyPouZCvoJWXDedha5s/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>TAP-GASMIG02-002_Termo-de-Abertura-OS002.docx</t>
+          <t>TAE-GASMIG02-002_Termo-de-Encerramento-OS002.docx</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cMUOhgzZzj6wwWIijFMDugRVZIl8aPvf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-zvT45vPsVTAwmcEzQVak8qKT4dnQWEr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>TAP-GASMIG02-002_Termo-de-Abertura-OS002.md</t>
+          <t>TAE-GASMIG02-002_Termo-de-Encerramento-OS002.md</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1EDT02kT9MVQV0gWPgpmAcCbVHa8T5GH8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Gvd3sqaF500esvT_KQXRRYQOKtSLBa1f/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>VV-GASMIG02-001_Plano-de-VV.docx</t>
+          <t>TAP-GASMIG02-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15t1yh5oMbpFZ47rREDx9kJPgS8oXyRmy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1WW3VNRafS44JkZiXK29Rm7bYI7NbP9rS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>VV-GASMIG02-001_Plano-de-VV.md</t>
+          <t>TAP-GASMIG02-001_Termo-de-Abertura.md</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1u0GkYIZ3U_T3KbW9zDIyrX41XWlzafgu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1X37fcpWgIcSM5LirpbU23geQekmjCp_i/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>VV-GASMIG02-002_Plano-de-VV-OS002.docx</t>
+          <t>TAP-GASMIG02-002_Termo-de-Abertura-OS002.docx</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/18GgauiJykVy8AASSKtJcqkt2FR-6AuRv/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1cMUOhgzZzj6wwWIijFMDugRVZIl8aPvf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>VV-GASMIG02-002_Plano-de-VV-OS002.md</t>
+          <t>TAP-GASMIG02-002_Termo-de-Abertura-OS002.md</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8305,19 +8305,19 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hDwgWy26ua7WcoidKXwkRKdPA3f8SgHB/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1EDT02kT9MVQV0gWPgpmAcCbVHa8T5GH8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>ADAP-PROFARMA01-001_Registro-de-Adaptacao.docx</t>
+          <t>VV-GASMIG02-001_Plano-de-VV.docx</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8327,19 +8327,19 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1aRgkciq4Ed3iPJgEbe1jJnpkXKlF4Tma/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15t1yh5oMbpFZ47rREDx9kJPgS8oXyRmy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>ADAP-PROFARMA01-001_Registro-de-Adaptacao.md</t>
+          <t>VV-GASMIG02-001_Plano-de-VV.md</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8349,19 +8349,19 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1qa1eP5ZefDj1uNO-X1akjz55I4ZqmCOn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1u0GkYIZ3U_T3KbW9zDIyrX41XWlzafgu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>ATA-PROFARMA01-001_Ata-de-Kickoff.docx</t>
+          <t>VV-GASMIG02-002_Plano-de-VV-OS002.docx</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8371,19 +8371,19 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uNkVDge5WAgwLTCcUFZmBLlqKog16nmG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18GgauiJykVy8AASSKtJcqkt2FR-6AuRv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>ATA-PROFARMA01-001_Ata-de-Kickoff.md</t>
+          <t>VV-GASMIG02-002_Plano-de-VV-OS002.md</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1lUV0rrT2F--Db0coxhXjcOre7lWH4HOU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hDwgWy26ua7WcoidKXwkRKdPA3f8SgHB/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>ATA-PROFARMA01-002_Ata-de-Aceite-Final.docx</t>
+          <t>ADAP-PROFARMA01-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1odIVE62I5L7iqqLFUCACbHt3w2HRB8yR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1aRgkciq4Ed3iPJgEbe1jJnpkXKlF4Tma/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>ATA-PROFARMA01-002_Ata-de-Aceite-Final.md</t>
+          <t>ADAP-PROFARMA01-001_Registro-de-Adaptacao.md</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fb6iusuVg05dDsai8VJhfW4ZxA-qpnxZ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1qa1eP5ZefDj1uNO-X1akjz55I4ZqmCOn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>CR-PROFARMA01-001_Registro-de-Change-Requests.docx</t>
+          <t>ATA-PROFARMA01-001_Ata-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1XWRRoeJ6NnvjCG3S0hlyPyxnMfkf9vM7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1uNkVDge5WAgwLTCcUFZmBLlqKog16nmG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>CR-PROFARMA01-001_Registro-de-Change-Requests.md</t>
+          <t>ATA-PROFARMA01-001_Ata-de-Kickoff.md</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1kgckhl0v57S7-e70hCKJB6Eo8eW2gT1y/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1lUV0rrT2F--Db0coxhXjcOre7lWH4HOU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>CTQ-PROFARMA01-001_Cenarios-de-Teste-Homologacao.docx</t>
+          <t>ATA-PROFARMA01-002_Ata-de-Aceite-Final.docx</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ts70FWbIasG3sf9qDBSw8cXldJfRJ7bY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1odIVE62I5L7iqqLFUCACbHt3w2HRB8yR/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>CTQ-PROFARMA01-001_Cenarios-de-Teste-Homologacao.md</t>
+          <t>ATA-PROFARMA01-002_Ata-de-Aceite-Final.md</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16ZD1X77Pqc4pDhauwVkg0ioDD6nVFAmy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fb6iusuVg05dDsai8VJhfW4ZxA-qpnxZ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>GCO-PROFARMA01-001_Registro-de-Gerencia-de-Configuracao.docx</t>
+          <t>CR-PROFARMA01-001_Registro-de-Change-Requests.docx</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ld1PXP0yafu0eW7nUNXN0iRCm1P7cskc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1XWRRoeJ6NnvjCG3S0hlyPyxnMfkf9vM7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>GCO-PROFARMA01-001_Registro-de-Gerencia-de-Configuracao.md</t>
+          <t>CR-PROFARMA01-001_Registro-de-Change-Requests.md</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Sa_Vs1t1DTIcQX0MLGesk4T6YVBc-Rlk/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1kgckhl0v57S7-e70hCKJB6Eo8eW2gT1y/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>GDE-PROFARMA01-001_Registro-de-Analise-de-Decisao.docx</t>
+          <t>CTQ-PROFARMA01-001_Cenarios-de-Teste-Homologacao.docx</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1wU_hxVhwrX-XUT1OQmEKxw80Mz0T5Rat/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ts70FWbIasG3sf9qDBSw8cXldJfRJ7bY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>GDE-PROFARMA01-001_Registro-de-Analise-de-Decisao.md</t>
+          <t>CTQ-PROFARMA01-001_Cenarios-de-Teste-Homologacao.md</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Fn6AEOrG_9rfsHc5rb-55Ba6AJXD-oqJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/16ZD1X77Pqc4pDhauwVkg0ioDD6nVFAmy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8625,17 +8625,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>GEST-PROFARMA01_Planilha-de-Gestao-do-Projeto.xlsx</t>
+          <t>GCO-PROFARMA01-001_Registro-de-Gerencia-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12SEFOVCAA1jVQRgM1c1RDR_CL3KaW32_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ld1PXP0yafu0eW7nUNXN0iRCm1P7cskc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8647,17 +8647,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>GQA-PROFARMA01-001_Registro-de-GQA.docx</t>
+          <t>GCO-PROFARMA01-001_Registro-de-Gerencia-de-Configuracao.md</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hefq-kmdiYVOIvc0RoWHcSVQDBbL8Fq4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Sa_Vs1t1DTIcQX0MLGesk4T6YVBc-Rlk/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8669,17 +8669,17 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>GQA-PROFARMA01-001_Registro-de-GQA.md</t>
+          <t>GDE-PROFARMA01-001_Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ejtinVxoovxalMob3EU5LzijUCO0eo0V/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1wU_hxVhwrX-XUT1OQmEKxw80Mz0T5Rat/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8691,17 +8691,17 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ITP-PROFARMA01-001_Estrategia-de-Integracao.docx</t>
+          <t>GDE-PROFARMA01-001_Registro-de-Analise-de-Decisao.md</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DKKcqAZK78dkV2UIRRSXHtELjnxdw4aj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Fn6AEOrG_9rfsHc5rb-55Ba6AJXD-oqJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8713,17 +8713,17 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ITP-PROFARMA01-001_Estrategia-de-Integracao.md</t>
+          <t>GEST-PROFARMA01_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hbMF9jFqMlJF3soSLRNy6LTp11g408Pn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/12SEFOVCAA1jVQRgM1c1RDR_CL3KaW32_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>LI-PROFARMA01-001_Licoes-Aprendidas.docx</t>
+          <t>GQA-PROFARMA01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NMayhfr_e6Li-R0NEGoST5QATJgifMc7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hefq-kmdiYVOIvc0RoWHcSVQDBbL8Fq4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>LI-PROFARMA01-001_Licoes-Aprendidas.md</t>
+          <t>GQA-PROFARMA01-001_Registro-de-GQA.md</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1iG2LYXClAx5nZ4zuk_S74DvZ1Q0LMHQ_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ejtinVxoovxalMob3EU5LzijUCO0eo0V/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>MED-PROFARMA01-001_Registro-de-Medicao.docx</t>
+          <t>ITP-PROFARMA01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nmbiWfvYMAAa7Y5pO14VxaZgxEPQuKOn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1DKKcqAZK78dkV2UIRRSXHtELjnxdw4aj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>MED-PROFARMA01-001_Registro-de-Medicao.md</t>
+          <t>ITP-PROFARMA01-001_Estrategia-de-Integracao.md</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1QDJ9-TSu_9GDbyhDRN6ywUgTeuAJ4QiH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hbMF9jFqMlJF3soSLRNy6LTp11g408Pn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PCP-PROFARMA01-001_Documento-de-Design.docx</t>
+          <t>LI-PROFARMA01-001_Licoes-Aprendidas.docx</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1t0fD748MR_EBRMHsgQzVGLKRnJ4Zq7__/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NMayhfr_e6Li-R0NEGoST5QATJgifMc7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PCP-PROFARMA01-001_Documento-de-Design.md</t>
+          <t>LI-PROFARMA01-001_Licoes-Aprendidas.md</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1xz3lOI7tT1T9MaUytvzP3u2djp_-VSll/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1iG2LYXClAx5nZ4zuk_S74DvZ1Q0LMHQ_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PLA-PROFARMA01-001_Plano-de-Projeto.docx</t>
+          <t>MED-PROFARMA01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/189Kp-xA8BJ3SsO9NhxDyDOUtX3dADifK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nmbiWfvYMAAa7Y5pO14VxaZgxEPQuKOn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PLA-PROFARMA01-001_Plano-de-Projeto.md</t>
+          <t>MED-PROFARMA01-001_Registro-de-Medicao.md</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UiPpMmAewO-ZAlFVC7Wgy3mUVTqk8KTG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1QDJ9-TSu_9GDbyhDRN6ywUgTeuAJ4QiH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>RAC-PROFARMA01-001_Relatorio-de-Acompanhamento.docx</t>
+          <t>PCP-PROFARMA01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HjCxyFwvC7Fxp4OXwxjqqL7OyYlSfI9x/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1t0fD748MR_EBRMHsgQzVGLKRnJ4Zq7__/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>RAC-PROFARMA01-001_Relatorio-de-Acompanhamento.md</t>
+          <t>PCP-PROFARMA01-001_Documento-de-Design.md</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1WKuyyC2s6ukY52aDxjmqfD6w2L5l_GRn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1xz3lOI7tT1T9MaUytvzP3u2djp_-VSll/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>RASTR-PROFARMA01-001_Matriz-de-Rastreabilidade.docx</t>
+          <t>PLA-PROFARMA01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ep0JvVMNhdLVRwWXVMIyfLxurd7ReAyI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/189Kp-xA8BJ3SsO9NhxDyDOUtX3dADifK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>RASTR-PROFARMA01-001_Matriz-de-Rastreabilidade.md</t>
+          <t>PLA-PROFARMA01-001_Plano-de-Projeto.md</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TChhbQ3yhiT2-Q5VN8cbxtuO2C65slPV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1UiPpMmAewO-ZAlFVC7Wgy3mUVTqk8KTG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>REL-VV-PROFARMA01-001_Relatorio-de-Execucao-de-Testes.docx</t>
+          <t>RAC-PROFARMA01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1KF8zj0lufb0VPg6riJwGhibojJJIopHM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1HjCxyFwvC7Fxp4OXwxjqqL7OyYlSfI9x/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>REL-VV-PROFARMA01-001_Relatorio-de-Execucao-de-Testes.md</t>
+          <t>RAC-PROFARMA01-001_Relatorio-de-Acompanhamento.md</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1-GrCtAPUfBcRFM4tMJfIEAO-o_cvFqOt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1WKuyyC2s6ukY52aDxjmqfD6w2L5l_GRn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>REQ-PROFARMA01-001_Documento-de-Requisitos.docx</t>
+          <t>RASTR-PROFARMA01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17OE2PW4XkEy3OnJlSb6rtsHHh9ouTFJE/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ep0JvVMNhdLVRwWXVMIyfLxurd7ReAyI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>REQ-PROFARMA01-001_Documento-de-Requisitos.md</t>
+          <t>RASTR-PROFARMA01-001_Matriz-de-Rastreabilidade.md</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1T0waKCjFQoXryc5x292hRhOggesgV4Pt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TChhbQ3yhiT2-Q5VN8cbxtuO2C65slPV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>REV-PROFARMA01-001_Registro-de-Revisao-Tecnica.docx</t>
+          <t>REL-VV-PROFARMA01-001_Relatorio-de-Execucao-de-Testes.docx</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dHd-EpgVX2Mg2Wo5Y_uxB8KFH4qphhxM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1KF8zj0lufb0VPg6riJwGhibojJJIopHM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>REV-PROFARMA01-001_Registro-de-Revisao-Tecnica.md</t>
+          <t>REL-VV-PROFARMA01-001_Relatorio-de-Execucao-de-Testes.md</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1oPm581spQso7WLZsNUHItMYAVQGqD6Qq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-GrCtAPUfBcRFM4tMJfIEAO-o_cvFqOt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>TAE-PROFARMA01-001_Termo-de-Encerramento.docx</t>
+          <t>REQ-PROFARMA01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1k_UZ_jWRVmpHA1Iiysa7vKvUwQ1T8QED/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17OE2PW4XkEy3OnJlSb6rtsHHh9ouTFJE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>TAE-PROFARMA01-001_Termo-de-Encerramento.md</t>
+          <t>REQ-PROFARMA01-001_Documento-de-Requisitos.md</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1G8wrZkaa7n3kidURBXK6tUzzupMHpeyb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1T0waKCjFQoXryc5x292hRhOggesgV4Pt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>TAP-PROFARMA01-001_Termo-de-Abertura.docx</t>
+          <t>REV-PROFARMA01-001_Registro-de-Revisao-Tecnica.docx</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13BKbRnLmlBDMBkioH54vOpmicKqlei8W/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dHd-EpgVX2Mg2Wo5Y_uxB8KFH4qphhxM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>TAP-PROFARMA01-001_Termo-de-Abertura.md</t>
+          <t>REV-PROFARMA01-001_Registro-de-Revisao-Tecnica.md</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1EViPFMzb6dgDVBr-wLeSrGXIJB25-2v2/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1oPm581spQso7WLZsNUHItMYAVQGqD6Qq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>VV-PROFARMA01-001_Plano-de-VV.docx</t>
+          <t>TAE-PROFARMA01-001_Termo-de-Encerramento.docx</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15tRkpsMad47tD4gPdlLKImY5ipIadjxw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1k_UZ_jWRVmpHA1Iiysa7vKvUwQ1T8QED/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>VV-PROFARMA01-001_Plano-de-VV.md</t>
+          <t>TAE-PROFARMA01-001_Termo-de-Encerramento.md</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -9251,19 +9251,19 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pFat-uajlAcSBqyMC8Xr5TIDMOz5Yqa1/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1G8wrZkaa7n3kidURBXK6tUzzupMHpeyb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>05_capacidade</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>MAPA-CAP-001_Mapa-de-Capacidade-dos-Processos.docx</t>
+          <t>TAP-PROFARMA01-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -9273,19 +9273,19 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YaGYkBQnoCkiO6AygwtZCQKSxZkMIRNU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13BKbRnLmlBDMBkioH54vOpmicKqlei8W/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>05_capacidade</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MAPA-CAP-001_Mapa-de-Capacidade-dos-Processos.md</t>
+          <t>TAP-PROFARMA01-001_Termo-de-Abertura.md</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9295,19 +9295,19 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Cf81NchDsh8A185sbhMAt1NJTCks3snY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1EViPFMzb6dgDVBr-wLeSrGXIJB25-2v2/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>05_capacidade</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.docx</t>
+          <t>VV-PROFARMA01-001_Plano-de-VV.docx</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -9317,19 +9317,19 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16fsO_4U6QBJxV0HSWpFJsHX-XQ4HhLhT/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15tRkpsMad47tD4gPdlLKImY5ipIadjxw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>05_capacidade</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.md</t>
+          <t>VV-PROFARMA01-001_Plano-de-VV.md</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NHV3d4WHuUhUcTOtjtGi-uB1yR3BC6mL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pFat-uajlAcSBqyMC8Xr5TIDMOz5Yqa1/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -9351,22 +9351,110 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
+          <t>MAPA-CAP-001_Mapa-de-Capacidade-dos-Processos.docx</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1YaGYkBQnoCkiO6AygwtZCQKSxZkMIRNU/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>05_capacidade</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>MAPA-CAP-001_Mapa-de-Capacidade-dos-Processos.md</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Cf81NchDsh8A185sbhMAt1NJTCks3snY/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>05_capacidade</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.docx</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/16fsO_4U6QBJxV0HSWpFJsHX-XQ4HhLhT/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>05_capacidade</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.md</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1NHV3d4WHuUhUcTOtjtGi-uB1yR3BC6mL/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>05_capacidade</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
           <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.xlsx</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr">
+      <c r="C410" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D406" s="2" t="inlineStr">
+      <c r="D410" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/14kYNYwEsp3nawnEA9t25kWyYey51aYlu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D406"/>
+  <autoFilter ref="A1:D410"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -9773,6 +9861,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId403"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId404"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId409"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MAPA-DRIVE_Indice-de-Links.xlsx
+++ b/MAPA-DRIVE_Indice-de-Links.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mapa de Links Drive" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapa de Links Drive'!$A$1:$D$410</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapa de Links Drive'!$A$1:$D$261</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D410"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -458,66 +458,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>(raiz)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ATA-GPC-001_Reuniao-Analise-Critica-de-Processos.docx</t>
+          <t>Ata-de-criação-SEPG.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s9RPnB6u6YPiKqHsOoyV3sM4jk8waSQ6/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1EFI0RcRsilCo8p7NDsd71-f3bWtlWZMc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>(raiz)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATA-GPC-001_Reuniao-Analise-Critica-de-Processos.md</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
+          <t>Avaliacão_Oficial_Planilha-Indicadores_SW_2024-Nivel C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1EEuTIt9ISGnUeoNd7Lt7DD9vNFJlB59u/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1iiroC88KQ1SPTis5VBGRxBChmZUizI1hubZXxpyzNBE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>(raiz)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CONV-ORG-001_Convencao-de-Nomenclatura-e-Versionamento.docx</t>
+          <t>TPL-GPC-002_Ata-Reuniao-SEPG.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1yKI99GViOo-a1ADKW4vs6yG4raqzyxXL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1sGkGUkG4K6JYd8AWGganOiN7E2bJZj8j/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -529,17 +525,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CONV-ORG-001_Convencao-de-Nomenclatura-e-Versionamento.md</t>
+          <t>ATA-GPC-001_Reuniao-Analise-Critica-de-Processos.docx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17HJQfMjPnEOk_ZAYsaufEELNizZREYM6/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1mSEGlpnnXBRwaVqlnsioWGVZQCfdyXVD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -551,17 +547,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EST-GPC-001_Estrategia-de-Garantia-da-Qualidade.docx</t>
+          <t>CHK-Auditoria Organizacional-Timeware_junho2026.xls</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xls</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1PcLyYQbGTpNvDjGdDvV7Csshp6DRAEKQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dLEs2NkG672GBNtPByTx6_RSOLUWkkmJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -573,17 +569,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EST-GPC-001_Estrategia-de-Garantia-da-Qualidade.md</t>
+          <t>CONV-ORG-001_Convencao-de-Nomenclatura-e-Versionamento.docx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1aT-otYaoxJ83fFgBmnO_1XNfaZshZ5a8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Ag4-jg-EEHXvggj27dmSr_07uzkYh77k/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -595,7 +591,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EST-GPC-002_Estrategia-de-Gerencia-de-Riscos.docx</t>
+          <t>EST-GPC-001_Estrategia-de-Garantia-da-Qualidade.docx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -605,7 +601,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1WFa93nIx6l-4It8LE8jSdtbGLqneOXPs/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1PdyKvi2sk8adOJE2mKW3L5QumD9shj-v/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -617,17 +613,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EST-GPC-002_Estrategia-de-Gerencia-de-Riscos.md</t>
+          <t>EST-GPC-002_Estrategia-de-Gerencia-de-Riscos.docx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MllGYXnjqDoA_xHcSpMnljQFAnxBCMCr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jNY12kyO2w-DJKhz8aizdHI9Q7HBo3Pl/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -649,7 +645,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13ypkmhks1HUEva1c1WNgZWom0H1NRndJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1vNp-iv47mRXMyLEeR3f1pEDN4JXA1Zhv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -661,17 +657,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GQA-ORG-001_Auditoria-Organizacional.md</t>
+          <t>GUIA-GPC-001_Guia-de-Adaptacao-do-Processo-Padrao.docx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1g6vfBg9quFs8q5ORxAXmvd7gCa_vKjX6/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ha36PVPtCC4YIeBXc0qZ_aLGJVNxY3I0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -683,7 +679,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GUIA-GPC-001_Guia-de-Adaptacao-do-Processo-Padrao.docx</t>
+          <t>GUIA-GPC-002_Guia-de-Auditorias-de-GQA.docx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -693,7 +689,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s7X2zQ0vnCUHx3Jzm3m8eliwIIpX9Zcc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NrY7N_tj_u-cK3iwpjIzjraez005KrzW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -705,17 +701,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GUIA-GPC-001_Guia-de-Adaptacao-do-Processo-Padrao.md</t>
+          <t>PLA-GPC-001_Plano-de-Gestao-e-Melhoria-de-Processos.docx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1I0lk9tEWdpP_DW_eqSOXbmpOobbMvuK_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/131GoQo25d8-YX5ejvh1DAAUeMWl1Mk-K/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -727,7 +723,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PLA-GPC-001_Plano-de-Gestao-e-Melhoria-de-Processos.docx</t>
+          <t>POL-ORG-001_Politica-Organizacional-de-Processos.docx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -737,7 +733,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Lw-0QgXqeLuTy6iWmVjVmiXtaVdBtqcj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1GmI7A4qb2yBY7y6tfUmd7UEtsKXqSFhy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -749,17 +745,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PLA-GPC-001_Plano-de-Gestao-e-Melhoria-de-Processos.md</t>
+          <t>PRO-GPC-001_Processo-Padrao-Organizacional.docx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1xcLwP7ixzwYPLjkZGzmuTKLRVC9URm3F/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NU3XFUjMKuLcBIEW6DrgKIz0BNWi3KxV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -771,7 +767,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>POL-ORG-001_Politica-Organizacional-de-Processos.docx</t>
+          <t>PRO-GPC-002_Definicao-do-Time-de-Melhoria-Continua.docx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -781,7 +777,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1KBJHr12DQ0TM51UqpNkQiMlsOKsZNdHS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1lh--xCFmICNqD7GKkDmQ1F3MOPTgox1V/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -793,17 +789,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>POL-ORG-001_Politica-Organizacional-de-Processos.md</t>
+          <t>PRO-OSW-001_Governanca-Organizacional-de-Processos.docx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19p6sKCbL0INg_e5ccIT_qYegWID3mH7d/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1aLxm5g-o_qTP6V_LSQybcTC7nzdMgUAt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -815,7 +811,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PRO-GPC-001_Processo-Padrao-Organizacional.docx</t>
+          <t>PRO-OSW-002_Gestao-de-Portfolio-de-Projetos.docx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -825,7 +821,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15z2lvvglDk45Eh6jA-mzJbaYCuTnLEsa/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bZr4oVRjUSGwYvRuL4v_cEioy6gOgJro/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -837,17 +833,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PRO-GPC-001_Processo-Padrao-Organizacional.md</t>
+          <t>REG-GPC-001_Registro-de-Melhorias-de-Processo.docx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13J3dcvr__Vs5_XIzyjVt-wlG3VxWIric/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1h_fkAu9MjScpjg3l9r3OHepLf0zU8eA9/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -859,7 +855,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PRO-GPC-002_Definicao-do-Time-de-Melhoria-Continua.docx</t>
+          <t>REG-GPC-002_Plano-de-Implementacao-de-Melhorias.docx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -869,7 +865,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SQNp-nJBm5anlx8cMGkrzZokborcrgav/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1GCLn8iMOKMAUf2w_FjpOSx40cmfO741E/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -881,17 +877,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PRO-GPC-002_Definicao-do-Time-de-Melhoria-Continua.md</t>
+          <t>REG-OSW-001_Painel-de-Portfolio.docx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZMItgBSAAiuUyTxp_5M5ENp6QC4qYrWe/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1kAjVXkatpQad4EuU19Il6BzL0c8IkITD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -903,7 +899,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PRO-OSW-001_Governanca-Organizacional-de-Processos.docx</t>
+          <t>REG-OSW-002_Comunicacao-da-Politica-Organizacional.docx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -913,7 +909,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1oClWBy8t0wSsbqu6c1WeAVBkLizpN9Cp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nqnyQ3vWpXA8HPeQMRc2X0XuZNOUx1uu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -925,17 +921,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PRO-OSW-001_Governanca-Organizacional-de-Processos.md</t>
+          <t>REG-OSW-003_Riscos-Organizacionais.xlsx</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jOjPRa6GiU7fW8xrIvx8oeRfke0fyYvd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1P2hhQaWTAbOlyifwPrbaEdF3kTwqLMFP/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -947,51 +943,51 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PRO-OSW-002_Gestao-de-Portfolio-de-Projetos.docx</t>
+          <t>Timeware_GQA_-_CHK-Auditoria_QA_do_QA_Jun2026.xlsx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dh_076oGwPXwRO50M1MTXkldD0x2jn34/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JjU5851rE_9gVpEN9ySdnLYAiGseVaME/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>01_apoio</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PRO-OSW-002_Gestao-de-Portfolio-de-Projetos.md</t>
+          <t>DIAG-GPC-001_Fluxo-do-Processo-Padrao.svg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1J9FGVXCdeNnpRGualWPacksTPwIIZsoB/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1lMaZ2M1qKHfkGfIVAhc4rRyD26-LJJPI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>01_apoio</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REG-GPC-001_Registro-de-Melhorias-de-Processo.docx</t>
+          <t>GUIA-GCO-001_Guia-de-Nomenclaturas-Tecnicas.docx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1001,41 +997,41 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12mK6HP6TI01uERtCD5cowZ59frP8MITS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1aSfVOk1WBb8itN0-9jMHO5yhYxsrGM2_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>01_apoio</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>REG-GPC-001_Registro-de-Melhorias-de-Processo.md</t>
+          <t>PLA-CAP-001_Plano-de-Capacitacao.docx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NhvbapiCkmSZduNELja-urzuNU_rJZmx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fRYqINyOJrh7ily2FW-e2XnQH0z-mYd6/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>01_apoio</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>REG-GPC-002_Plano-de-Implementacao-de-Melhorias.docx</t>
+          <t>PLA-GCO-001_Plano-de-Gerencia-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1045,41 +1041,41 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10CueJB2QqzBsWk0c5xw9g-SMlhLe6aCq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZNsiKFYVP1IvPlpovyJhhKNfVfPMlibj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>01_apoio</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>REG-GPC-002_Plano-de-Implementacao-de-Melhorias.md</t>
+          <t>PLA-MED-001_Plano-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Y7EUeDcEsFcccvzUAngHWSyyh6yfBudU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bl5-_poxJigRv4_5gQj8K3dFDIEqQF5e/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>01_apoio</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>REG-OSW-001_Painel-de-Portfolio.docx</t>
+          <t>PRO-AQU-001_Processo-de-Aquisicao.docx</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1089,41 +1085,41 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16GzPsr1B98jKvGynRIZbGMIuB3-xgBNX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18vVN8pTYAeP69xbHsnIGPgNLHq_IIwWt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>01_apoio</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>REG-OSW-001_Painel-de-Portfolio.md</t>
+          <t>PRO-CAP-001_Processo-de-Capacitacao.docx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_KlCtM-JtsNP7nfXJ-amWm_W-RNRQR2T/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1QrUMeBMUAYoppls0b02CNlbDE3l6lW1-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>01_apoio</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>REG-OSW-002_Comunicacao-da-Politica-Organizacional.docx</t>
+          <t>PRO-GCO-001_Processo-de-Gerencia-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1133,29 +1129,29 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nJCJ4U3BnvuCSpMTp5w9K5IgSFF-_0X-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1DjbxKyj6bxsfBJkA-tiicqTASjH0DMNN/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00_governanca</t>
+          <t>01_apoio</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>REG-OSW-002_Comunicacao-da-Politica-Organizacional.md</t>
+          <t>PRO-GDE-001_Processo-de-Gerencia-de-Decisoes.docx</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uJSd2QS0Zx_M3FSSIWiYQ6YGd_GbK-_0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1N_0Tta90F4vg9JbjPvLPshqAwPCgVhxj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1167,17 +1163,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DIAG-GPC-001_Fluxo-do-Processo-Padrao.svg</t>
+          <t>PRO-MED-001_Processo-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1VcE5l4Q3ZKn1xnD22cW6oGtMI0ZGcoaq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1zqYLBqG8Tjj9k-oKjR6HxyhS9f7L8KHG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1185,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GUIA-GCO-001_Guia-de-Nomenclaturas-Tecnicas.docx</t>
+          <t>REG-MED-001_Repositorio-Organizacional-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1199,41 +1195,41 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RdyMfVvNDDoMRVoEDgg9XqrGPw0xZfvP/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Zbskc4JksK9Unm6Fn46DkvKMs_qmjul2/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GUIA-GCO-001_Guia-de-Nomenclaturas-Tecnicas.md</t>
+          <t>AVA-CAP-001_Avaliacao-Processo-Padrao-Geral.docx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hNRZy_3-cU8McKmBLSWs9PuGwbMftoUY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13GOC8q0K9e_qbFDzlZxlgbOCTnf4dNkL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PLA-CAP-001_Plano-de-Capacitacao.docx</t>
+          <t>AVA-CAP-002_Avaliacao-GPR.docx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1243,41 +1239,41 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15f8l5cLRx2GUtPtEOgB5YMr_B8wLzUyX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1wNPYzKfOdRuIbvvDjr-otCb8GoRhCG7q/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PLA-CAP-001_Plano-de-Capacitacao.md</t>
+          <t>AVA-CAP-003_Avaliacao-Tecnico-REQ-PCP-VV.docx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SNg3LxGK2LzuGArQi4Y6ZnshmsaL1k8V/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TCtnSs7NzilCXO2KQAs1VUIkJGhMTACn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PLA-GCO-001_Plano-de-Gerencia-de-Configuracao.docx</t>
+          <t>AVA-CAP-004_Avaliacao-GCO-ITP.docx</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1287,41 +1283,41 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1EByQS4N7fnjNayOj6xD9FIic8lY2dVWk/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1US9vp7JZU04JucCuED_goKxGr9ZZ-9g3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PLA-GCO-001_Plano-de-Gerencia-de-Configuracao.md</t>
+          <t>AVA-CAP-005_Avaliacao-GPC-MED-CAP.docx</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1GAXEf-Rgw6FUAl1GJsabUA75uoGycy0y/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18zWHf9BsL7jy-klnk-aRjv7NYjIwYyvX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PLA-MED-001_Plano-de-Medicao.docx</t>
+          <t>GUIA-CAP-001_MiniManual-GPR.docx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1331,41 +1327,41 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1OIs1jn8y5vbVwuATrGkxl8k8lufjArMd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1v97Th4VFwmg8-yIKfjJ5XnM8xQZ9gQ6S/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PLA-MED-001_Plano-de-Medicao.md</t>
+          <t>GUIA-CAP-002_MiniManual-REQ.docx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1V6NiR6exNC6XMpHqGNWw9GAoS704bjEr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Q0pAd_F2SgWNtfEyv-QNjTzg1kks8aOn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PRO-AQU-001_Processo-de-Aquisicao.docx</t>
+          <t>GUIA-CAP-003_MiniManual-PCP.docx</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1375,41 +1371,41 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11QhxjcAqXMJqQ5JRPC3uRorX8htrC0Gv/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1veYVFsie7Lr-JwZtv9R7XPIgC5G3fUgj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PRO-AQU-001_Processo-de-Aquisicao.md</t>
+          <t>GUIA-CAP-004_MiniManual-VV.docx</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fr64cQA9CxVUTdpaaEaliRkY-USP8gfu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1aVOG1oejstTXFMvTGK8o3gSs9xZjLrnB/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PRO-CAP-001_Processo-de-Capacitacao.docx</t>
+          <t>GUIA-CAP-005_MiniManual-GCO.docx</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1419,41 +1415,41 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1-R1f0avcdbEkKxwPDvBlJF5RqJlUI4bK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1e9ikwsWjrezS3sra9hJLorItDERWDv7K/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PRO-CAP-001_Processo-de-Capacitacao.md</t>
+          <t>GUIA-CAP-006_MiniManual-ITP.docx</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FCGW2TBeSVry2MaWPkzx8oF0oh6P2x7b/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tqFdOOTK77v62duzBsmvNVwcIigjTPvG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PRO-GCO-001_Processo-de-Gerencia-de-Configuracao.docx</t>
+          <t>GUIA-CAP-007_MiniManual-GDE.docx</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1463,41 +1459,41 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14nFj1LZ8Ua49h8KWxHzERS2-7zXtXgGq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1prpCXsG_qqc7gT4T0IfgJGYcohNXRDl1/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PRO-GCO-001_Processo-de-Gerencia-de-Configuracao.md</t>
+          <t>GUIA-CAP-008_MiniManual-MED.docx</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YOiurj5y8HJEMKovAMxawzEpvR-ycQty/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Y_YmTBtBwJjLQUKsAmH5ZvaVisALAAoI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PRO-GDE-001_Processo-de-Gerencia-de-Decisoes.docx</t>
+          <t>GUIA-CAP-009_MiniManual-GPC.docx</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1507,41 +1503,41 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_NACA9i2s6L-ZwzbonY6mDbNK84z_bc8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SDGOr0CiUxIjNDBuODC6wdgpp8NSoeGj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PRO-GDE-001_Processo-de-Gerencia-de-Decisoes.md</t>
+          <t>GUIA-CAP-010_MiniManual-OSW.docx</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZgPCPbKCTJxmI0de7UCEMaNMsWMwhlOB/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NX19Hv07nAVcyyvkPPEyYyUGJkKDsAWb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PRO-MED-001_Processo-de-Medicao.docx</t>
+          <t>GUIA-CAP-011_MiniManual-CAP.docx</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1551,63 +1547,63 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Z2FhoHfN_g3Wvgqd6OmWooBY-gT0fFvW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1aXxOmf0e15DbrsWn1ZaraHcPjntfbJA0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PRO-MED-001_Processo-de-Medicao.md</t>
+          <t>GUIA-CAP-012_MiniManual-AQU.docx</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14bS2beLkw_RodEHv_m2d_jKOXkpYITxl/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1KRovoA8y4usjBw54k-6koFndZbEtft3p/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>REG-MED-001_Repositorio-Organizacional-de-Medicao.md</t>
+          <t>MAT-CAP-013_Trilha-COO-Portfolio.docx</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1y9d_Tifq5ymLZi471yNVKwhp2oIbkxeM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1s2-1ARa6uoXvZ242Rr1TSykDk33AhWAf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>01_apoio</t>
+          <t>01_apoio/cap</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>REGMED001_RepositorioOrganizacionaldeMedicao.docx</t>
+          <t>MAT-CAP-014_Trilha-Time-Melhoria-SEPG.docx</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1617,7 +1613,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FOAiyoGlyqXioyDAXV4gCyqsJZvaJ1aB/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1HaW1EHn2aAQqY9xK89ODIgI2IvxWrDyP/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1625,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AVA-CAP-001_Avaliacao-Processo-Padrao-Geral.docx</t>
+          <t>MAT-CAP-015_Trilha-RH-Pessoas.docx</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1639,7 +1635,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1L0MK80X6mMOf0oDMYQtBVmYKD-LLuB6O/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1UWNTFbXxQ_kmJqSGNOkRFeX-iSomPnSG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1651,17 +1647,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AVA-CAP-001_Avaliacao-Processo-Padrao-Geral.md</t>
+          <t>MAT-CAP-016_Trilha-Tech-Lead-Arquiteto.docx</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11rB7oDMvWo0GvcL1GhUM824bC85cmAOj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15nIEUZFERE0EJV4QZk9xpQBwlNUZFCcF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1669,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AVA-CAP-002_Avaliacao-GPR.docx</t>
+          <t>MAT-CAP-017_Trilha-PO-PM.docx</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1683,7 +1679,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13zYWvkkv4II08CrmYt3n0cmDwTCC3AeP/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JHBn9SgnWJf6uzC3G1GGvmPIS9fZIWPa/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1691,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AVA-CAP-002_Avaliacao-GPR.md</t>
+          <t>MAT-CAP-018_Trilha-Devs.docx</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13DugViGDC7m2Xqk-fBxWN2IqvwpSwQnc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dR90Hw5yPrDYtExr8YoHJM4aEYVnXWWh/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1713,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AVA-CAP-003_Avaliacao-Tecnico-REQ-PCP-VV.docx</t>
+          <t>MAT-CAP-019_Trilha-DevOps.docx</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1727,7 +1723,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ihIG6DY8eq0B3qpLdXJMixozPhWv-bwT/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1kSQSizbFFaPxnmhXWmsUbvmTu5xwA6-M/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1739,17 +1735,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AVA-CAP-003_Avaliacao-Tecnico-REQ-PCP-VV.md</t>
+          <t>MAT-CAP-020_Trilha-QA.docx</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nskpt_7NeBQU76v1SecFt3shK616OHdU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Dj-qizipNW-ltxCZWvmxHzxaJTcRtZL_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1757,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AVA-CAP-004_Avaliacao-GCO-ITP.docx</t>
+          <t>MAT-CAP-021_Trilha-GCO-Baseline.docx</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1771,7 +1767,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HR8kPCFtn1YeCpdGSKCsvjEVsTpKdvoZ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CN4W49RgtDofz8gTKGpO-XG91s1JU8NG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1783,17 +1779,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AVA-CAP-004_Avaliacao-GCO-ITP.md</t>
+          <t>MAT-CAP-022_Trilha-Responsavel-Medicao.docx</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JbcegYCdahfdayymHIawCep5N8sEbCqF/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SrbC85jEtMo7UKhvKff-j4hV_cn6J0Gc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1801,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AVA-CAP-005_Avaliacao-GPC-MED-CAP.docx</t>
+          <t>MAT-CAP-023_Trilha-Tecnica-Onboarding.docx</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1815,7 +1811,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1KMJLMsB9KciEhNQxSNieI3A9O1d7wTsL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1b74pAiJa0SgmSlw6aIgafAJsLb1FO6JT/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1827,17 +1823,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AVA-CAP-005_Avaliacao-GPC-MED-CAP.md</t>
+          <t>REG-CAP-001B_Sessao-Reforco-Jan2025.docx</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1f4ODSbjmha6LhJjT7d86A1HOEnf4Pq0T/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1MKVD45n4shRUHW_6Y9s0dAbpRqrJ1Iyj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1845,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GUIA-CAP-001_MiniManual-GPR.docx</t>
+          <t>REG-CAP-001_Sessao-Treinamento-Dez2024.docx</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1859,7 +1855,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1rS4OTxRrRrbua89Qg2Br9jrmOrjabfEu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1d3uKsFw7u-EivN-32-gbwbb2e1R9qqvt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1871,17 +1867,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GUIA-CAP-001_MiniManual-GPR.md</t>
+          <t>REG-CAP-002B_Sessao-Reforco-Set2025.docx</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1obKGUSvsgBmoAzGF1j5sAjUYz72erOCV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ld5yom8HOzJ8lnJjbei2JFBf-YmI4BrJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1889,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GUIA-CAP-002_MiniManual-REQ.docx</t>
+          <t>REG-CAP-002_Sessao-Treinamento-Mar2025.docx</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1903,7 +1899,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1wy0aD3f_ffoR5L742FgEMWqlKSj1gt1_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13QC7eLlcwKHSakbvo-zzE6dHLCwAxpN3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1915,17 +1911,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GUIA-CAP-002_MiniManual-REQ.md</t>
+          <t>REG-CAP-003_Sessao-Treinamento-Ago2025.docx</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1oVcmJVt3NVuN5MfJL80bJfdXJA7FL_hc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14TYg_YEqr0RMpHXS8s7SHiAJTJhV5YoI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1933,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GUIA-CAP-003_MiniManual-PCP.docx</t>
+          <t>REG-CAP-004_Sessao-Treinamento-Jan2026.docx</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1947,7 +1943,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DCGLP9f5Pho42AMAjWzZn4A73E45bHBH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1PAWKGhzVbZS4SeyDrutAj9mM-HMGxKs4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1959,17 +1955,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GUIA-CAP-003_MiniManual-PCP.md</t>
+          <t>REG-CAP-005_Sessao-Treinamento-Mai2026.docx</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1APDWRdjS_qW3Zq5bDTRFOVjC3h4DXSZ7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D8oZJ-zFZ1xCaEkheX1fr_UVX0Vlfq6g/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1977,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GUIA-CAP-004_MiniManual-VV.docx</t>
+          <t>REG-CAP-006_Sessao-Gestao-Out2025.docx</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1991,7 +1987,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10OrGMaay8ZyWKQQtlPWAIStN2EArM2lX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Qv8t4ZXt2I3tLI9pg_HOwCekuEI4JzX5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2003,17 +1999,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GUIA-CAP-004_MiniManual-VV.md</t>
+          <t>REG-CAP-007_Sessao-Tecnico-Jan2026.docx</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1l5pgpbqAvQlIEz6MGdE7qmLi8kJ15eVU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hVZts-J6HjJj_U41MyHZklhTMlp9xYn5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2021,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GUIA-CAP-005_MiniManual-GCO.docx</t>
+          <t>REG-CAP-008_Sessao-Tecnico-Fev2026.docx</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2035,7 +2031,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Ehp57xo1dNee43TBPc6l8McdEHqBIusA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17Dvw_Q_iCQ10w0arFOOoMakjpaqGOstI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2047,17 +2043,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GUIA-CAP-005_MiniManual-GCO.md</t>
+          <t>REG-CAP-009_Reciclagem-Mar2026.docx</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1amNy8d4c3vZV__wkBMaIzOeky16bLvcn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1df4AZerHPxQz0rBtvFH3zHkMramhnvzU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2065,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GUIA-CAP-006_MiniManual-ITP.docx</t>
+          <t>REG-CAP-010_Onboarding-Tecnico-Jan2026.docx</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2079,7 +2075,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dbKffWaDaaHkSpQ6wAuqyJujuyQ7Dkyy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_YQ9DpRBydaU04jOIZ5JK2ooImBDHgfZ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2091,17 +2087,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GUIA-CAP-006_MiniManual-ITP.md</t>
+          <t>REG-CAP-011_Workshop-Azure-APIM-Mar2026.docx</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gAPICKSawMohY7R2radBCHl6OyRZ-oA8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fXmJU_h1MhW7evekDBwhWHMvT3KpvGzN/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2109,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GUIA-CAP-007_MiniManual-GDE.docx</t>
+          <t>REG-CAP-012_Workshop-Automacao-Testes-Fev2026.docx</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2123,7 +2119,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MgTl2w9fZz3aHeHW0ZSdEKN9TmEHt7eY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1qAcFU5xyyEbbxrLk2XL75L-EmBsJiqsi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2135,17 +2131,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GUIA-CAP-007_MiniManual-GDE.md</t>
+          <t>REG-CAP-013_Consultoria-Desenho-Processos-Jun2025.docx</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1csGF1cCc8vi1dA5OlfKCh9q-g3FoMRg5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1BYatkn9c-PMuHuOVurTVVcZb3UXP8Zu7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2153,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GUIA-CAP-008_MiniManual-MED.docx</t>
+          <t>REG-CAP-CV-001_Indice-de-Curriculos.docx</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2167,7 +2163,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15dXPTmal-yqg9B2vQyoSZEUX8OxZksFr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1QwGtPfGUwvcmpBkFxl9R60DSuJXCiunl/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2179,17 +2175,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GUIA-CAP-008_MiniManual-MED.md</t>
+          <t>REL-CAP-001_Relatorio-de-Eficacia-2025.docx</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MJf9WWhQQUdXuXW8VKazxIUzmFVSButZ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1vOW1WaWQyddaHXdkJfFkmVP7o4RDzxeX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2197,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GUIA-CAP-009_MiniManual-GPC.docx</t>
+          <t>TLP-CAP-003_Formulario-de-Avaliacao-do-Instrutor.docx</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2211,7 +2207,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1kNivoZ1Wr4QXbjReNplUIfqigeOtJ8_o/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JWxBzA34W7LlDEoejzTlBRwAGwvbR0H0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2223,17 +2219,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GUIA-CAP-009_MiniManual-GPC.md</t>
+          <t>TPL-CAP-001_Registro-de-Sessao-de-Treinamento.docx</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15s8hqDo_2kh_qrkEqvbBSzSXvOVJa-hI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZRcOc9EUe_tGu93X2_CHESAL31GaR5tC/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2241,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GUIA-CAP-010_MiniManual-OSW.docx</t>
+          <t>TPL-CAP-002_Relatorio-de-Eficacia-de-Treinamento.docx</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2255,173 +2251,173 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12S8LyYhsEzQv4A0D6qDZRLgC30S0nqmK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1IyIJpISZPSI_fDzTWieJCoN1E7E-5Cgb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>01_apoio/cap/curriculos</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GUIA-CAP-010_MiniManual-OSW.md</t>
+          <t>CV-Caroline-Jenifer_QA.pdf</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15XAGw1n2P_mXvbGIEvHRGmnJKgbNgKBR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1C7vxxTRerQM1J7J344iub0tfSV86ozhc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>01_apoio/cap/curriculos</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GUIA-CAP-011_MiniManual-CAP.docx</t>
+          <t>CV-Cezar-Velazquez_TechLead.pdf</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TMwHMbbq0D8I17CWr-cPGP7TzW-GJms0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Wj_kGQvhXViFApjmjJDfvzUvbSuyqqV3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>01_apoio/cap/curriculos</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GUIA-CAP-011_MiniManual-CAP.md</t>
+          <t>CV-Flavio-Fernandes_GQA-Arquitetura.pdf</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17ZZI8mUkEkCoRTmXrJe_mY8Qj0kol-N1/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1GSQQ2yS_E7-HnE2BFPsf1A-hkq2AVjPd/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>01_apoio/cap/curriculos</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GUIA-CAP-012_MiniManual-AQU.docx</t>
+          <t>CV-Karen-Wada_Consultora-Processos.pdf</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1xT56t0Yfh7YnSZ1TPx8TYla_9D9w7Xc4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jX6ax9IDMALDHpoTCrcMMerF_nGIGpCr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>01_apoio/cap/curriculos</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GUIA-CAP-012_MiniManual-AQU.md</t>
+          <t>CV-Silvio-Baroni_SEPG-GPC.pdf</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1aS7ue400NH7RXhsiAch-o_IBnooTKg6b/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1rC4NvQveAUCAWQOkNiU8VvlVX2AkTN6i/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>01_apoio/cap/curriculos</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MAT-CAP-013_Trilha-COO-Portfolio.docx</t>
+          <t>CV-Wilson-Yamada_Sponsor-Portfolio.pdf</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13YO3MTQBznbYFOc_akFM-UwWdsobodLj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11gRQH_6m7Eq1ojWkfu6hRK_AqTqY65ak/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>02_projeto</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MAT-CAP-013_Trilha-COO-Portfolio.md</t>
+          <t>GUIA-GPR-001_Roteiro-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ifOoba9-maD6zF6_4fqVJBohKkJFBfIc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Iqum1Ej_iNdiaXLJ3I1sp0JrI0iWUvnk/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>02_projeto</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MAT-CAP-014_Trilha-Time-Melhoria-SEPG.docx</t>
+          <t>PRO-GPR-001_Processo-de-Gerencia-de-Projetos.docx</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2431,41 +2427,41 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RkTsNavdx3osAAgqlgFzkTLFIGwkMTBi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1EWyaanDh-iLbsEOhoz5E62LDSuGvmTij/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>02_projeto</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MAT-CAP-014_Trilha-Time-Melhoria-SEPG.md</t>
+          <t>PRO-ITP-001_Processo-de-Integracao-do-Produto.docx</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TTaEJ-gZEKxjrSZ4XVrBQgqrRjnoTBeL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11NtIkxH-4lYyR7a53UTbDIMAfxzzNmL6/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>02_projeto</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MAT-CAP-015_Trilha-RH-Pessoas.docx</t>
+          <t>PRO-PCP-001_Processo-de-Projeto-e-Construcao-do-Produto.docx</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2475,41 +2471,41 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1apnEAcH2MS8RsyDsvl5Hqfnz5xkrCXpe/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1s0FDXL-yA-t3Q9yzDXdUt_0a8xDtib7F/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>02_projeto</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MAT-CAP-015_Trilha-RH-Pessoas.md</t>
+          <t>PRO-REQ-001_Processo-de-Engenharia-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SgEIYvz-cRVmg2aEiwKHdYPJixBAT5fk/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ym-pv-GPmpf_t1ir19bOtfIgJZyX0BPt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>02_projeto</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MAT-CAP-016_Trilha-Tech-Lead-Arquiteto.docx</t>
+          <t>PRO-VV-001_Processo-de-Verificacao-e-Validacao.docx</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2519,41 +2515,41 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JS4_FKAPYHzz1B65YTGL8uVkSAo0-ad-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18yE_PzywceT3Z60vRqPC-yJjw4Su3528/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MAT-CAP-016_Trilha-Tech-Lead-Arquiteto.md</t>
+          <t>EXEMPLO-GPR-005_Status-Report-Exemplo-Preenchido.docx</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12tV94PVD8CSJO7GBtuiV_wkAX8uhxZQD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1L0rob_f1ODSOZXHoXgV_w_znX6JwKNga/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MAT-CAP-017_Trilha-PO-PM.docx</t>
+          <t>TPL-GDE-001_Template-Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2563,41 +2559,41 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Nk9RNKlXzfJwijqhfm-wJysHm8et6cBG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1wHbMGhvGpwUGtEj4oPQQ1KV97zLwEy7n/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MAT-CAP-017_Trilha-PO-PM.md</t>
+          <t>TPL-GPC-001_Template-Registro-de-Verificacao-de-GQA.docx</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1a8ORfbTfL6Ic6l8ECE1SiYTM8YUwaszg/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19rnaNwNh_stfJKjPUPjCKs5Yl6USfbxY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MAT-CAP-018_Trilha-Devs.docx</t>
+          <t>TPL-GPR-001_Template-Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2607,41 +2603,41 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cYBe6kG7LK67kpPVPQj-jfolwxk57Z-S/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/190E2DG0B4jgwqg4oJ8uTXDUNNd1ROXkM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MAT-CAP-018_Trilha-Devs.md</t>
+          <t>TPL-GPR-002_Template-Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Agyekcmbs8jKVYHF930x3mGtdS1b-l0w/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dFy9pqLoURReKkf88DW9zlI5isnqV9BG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MAT-CAP-019_Trilha-DevOps.docx</t>
+          <t>TPL-GPR-003_Template-Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2651,41 +2647,41 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1om6pDV7QThxnwkx52889J2_3pOrWACKm/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1oKWodTuwtumhMDYy6eGs2cIuaJDT828w/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MAT-CAP-019_Trilha-DevOps.md</t>
+          <t>TPL-GPR-004_Template-Termo-de-Encerramento.docx</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13xgrU-0Pthp_6P6woHdUfiDyHwpVmb_g/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NgZq_uG9A-W3qCyb89O4VDZBpJf5QeKR/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MAT-CAP-020_Trilha-QA.docx</t>
+          <t>TPL-GPR-005_Template-Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2695,41 +2691,41 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1KUq-32kGvzsKicpUN_Kxy0aRMPu0Y_oi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RrYtWXZU-EYDEKO8RRN7cWL8eDs7eJBr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MAT-CAP-020_Trilha-QA.md</t>
+          <t>TPL-GPR-006_Template-Change-Request.docx</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13k32H05H8n7d1ZA3BoOeoL1NyXsHKGva/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1eA_EZaEl4h-zUvvmULGvgDT-f_zzSARu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MAT-CAP-021_Trilha-GCO-Baseline.docx</t>
+          <t>TPL-ITP-001_Template-Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2739,41 +2735,41 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1xG7FbLTcLVNY9Tf75MM3Ttu_t3ZRjTix/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1mj5YGF4Ph8FMqz3DRx8ti-vrPmrFZiAb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MAT-CAP-021_Trilha-GCO-Baseline.md</t>
+          <t>TPL-ORG-001_Template-Ata-de-Reuniao.docx</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dJ_MTeu8qbYjaw50Wbh0c8Eh-ZKGZ-48/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TcB0DCLd2cfon4P5-t6SmMDQ2H8DiNLL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MAT-CAP-022_Trilha-Responsavel-Medicao.docx</t>
+          <t>TPL-PCP-001_Template-Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2783,41 +2779,41 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1VRdJxBk4wlBQ_-jq7Ue_4DhHQ3PbKjsC/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RHOuxY9-cS4dat55nWo3YnowBN9UP867/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MAT-CAP-022_Trilha-Responsavel-Medicao.md</t>
+          <t>TPL-REQ-001_Template-Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1vL14qqXbQD_Tse191WLvePN5uB2ewpcG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CjKEf7sYu272riKdQQ5L4YbyfM4KqNe0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MAT-CAP-023_Trilha-Tecnica-Onboarding.docx</t>
+          <t>TPL-REQ-002_Template-Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2827,41 +2823,41 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1sKQLlANRH_jIB6WIy0v6ko5XemKojdC-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1wRjUaxEY4zg7_yfZTTfB01iEETZiYN5T/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MAT-CAP-023_Trilha-Tecnica-Onboarding.md</t>
+          <t>TPL-VV-001_Template-Plano-de-Verificacao-e-Validacao.docx</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1oHF_OtwhrXzCkBYJnrTDkTjNhey3vmk_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11M6t6WkYgji_gubuFgyKj7WmRvLYnnYI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>03_templates</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>REG-CAP-001B_Sessao-Reforco-Jan2025.docx</t>
+          <t>TPL-VV-002_Template-Registro-de-Revisao-por-Pares.docx</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2871,41 +2867,41 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1O-P9xpYwaW_vd1xmsRiwgyP9FQ3j7nCp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CQTzVoOCaj1aSZ3l16gqSykf09IwYRtj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>REG-CAP-001B_Sessao-Reforco-Jan2025.md</t>
+          <t>00_INDICE-AASPAP01_Mapa-de-Registros.docx</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ABAnRyZSxwoJObVCP84fEt-N4fXR1bxQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1q7KCwgqQ5w0lUx4x26DYYFCx5gMmuglM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>REG-CAP-001_Sessao-Treinamento-Dez2024.docx</t>
+          <t>ADAP-AASPAP01-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2915,41 +2911,41 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nO1WhH6T77KWemD0dxO2ZTXuzXbJU8at/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1K4Q7uEZFdHy_r6nJhALzqCO-aH9fSg0o/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>REG-CAP-001_Sessao-Treinamento-Dez2024.md</t>
+          <t>ATA-AASPAP01-001_Ata-Alinhamento-Fluxo-CNJ.docx</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1enrf4ZAUhttkVPDlVmCyLdbwOwHgJXKy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1xnhEepqAaUxgcarVXwtyBITSBo4LiLVq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>REG-CAP-002B_Sessao-Reforco-Set2025.docx</t>
+          <t>CR-AASPAP01-001_Change-Request.docx</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2959,41 +2955,41 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1lOL9e-11IVGVyS4TvsF21Ht325Nl0NAS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1p94Xtd_QSXghPgdDQiaj9m8JoArrHree/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>REG-CAP-002B_Sessao-Reforco-Set2025.md</t>
+          <t>CR-AASPAP01-002_Change-Request.docx</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Ljd3g8eppyULGODYbJzt1962L0O-VoSp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1e495VArI_U_3TMW7KQc0p3GfqUiAek4a/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>REG-CAP-002_Sessao-Treinamento-Mar2025.docx</t>
+          <t>GCO-AASPAP01-001_Registro-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3003,85 +2999,85 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1S4KO93SuNshpOxu3g41TjnZW3HajFBNw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Rl6GXnN1H9mRl0V6bSYw9Pl_D-0THH_O/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>REG-CAP-002_Sessao-Treinamento-Mar2025.md</t>
+          <t>GDE-AASPAP01-001_Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NbodP8vj_SS999XcRiCu4aslfdXw9FAP/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1sDGfP0m6WdyKS4MYzHLLZNNQCyus0xJw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>REG-CAP-003_Sessao-Treinamento-Ago2025.docx</t>
+          <t>GEST-AASPAP01_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1x2iX2AevFRS44IkePAvaC9BF1t8i5mup/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZB2yOn7Pt1eviyaL1-XMCaiamiCql6gz/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>REG-CAP-003_Sessao-Treinamento-Ago2025.md</t>
+          <t>GQA-AASPAP01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZKJFrUa_v0JpLre9LLNPti6sLE-qt-sI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19WE56UNWv-aVGiPL24PzStXvX1NuplXF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>REG-CAP-004_Sessao-Treinamento-Jan2026.docx</t>
+          <t>ITP-AASPAP01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3091,41 +3087,41 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jJ7Gjeu_ds4huXMAF7e564NeJBgICJDz/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1cSlw8Kqi3fPboNG2KDMoRuWYLii5s1Qm/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>REG-CAP-004_Sessao-Treinamento-Jan2026.md</t>
+          <t>MED-AASPAP01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15qmHgk5_9u0ep5Je0R1femPBgim9Wvsw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17jDdprZJdXPr-muQAYnQNXoMNU1VOSAV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>REG-CAP-005_Sessao-Treinamento-Mai2026.docx</t>
+          <t>PCP-AASPAP01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3135,41 +3131,41 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1wGWK2W15Bws7fpOpta5AaqqvTpBMe7s5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1MkxkyhMa5O4d9ee1JVYHNZV59BxiHU3m/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>REG-CAP-005_Sessao-Treinamento-Mai2026.md</t>
+          <t>PLA-AASPAP01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11POQMlFp5psX9W4oAWk5J842VZvU83hY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D7tchEQKaqeZMZ2vNNa0wgnXevI-Br8H/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>REG-CAP-006_Sessao-Gestao-Out2025.docx</t>
+          <t>RAC-AASPAP01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3179,41 +3175,41 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11Nd6v2QxAipLc6gR1WDvH81DS2FfMKox/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/155bBfagbpaZdKxRSqXQzkmZSQkmCHNt0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>REG-CAP-006_Sessao-Gestao-Out2025.md</t>
+          <t>RASTR-AASPAP01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10jW0RgPOO_YOPYdh0MiDkP1r6oAkPiS1/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nqVdGrDD5CJ_3zPB3IehiBEhuDKSxZlS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>REG-CAP-007_Sessao-Tecnico-Jan2026.docx</t>
+          <t>REL-VV-AASPAP01-001_Relatorio-de-Execucao-de-Testes.docx</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3223,41 +3219,41 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16Lpc4ZfSV0HGifzpJwfeEjIgidwCo2pR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TzIWFlAfEpqwWO0JIF3DACKPzPgC2sPV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>REG-CAP-007_Sessao-Tecnico-Jan2026.md</t>
+          <t>REQ-AASPAP01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SthU41muR1B9KQ-AjTzdPy7C7zjAx6St/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1kV_N6w7TU5Cwe5SYWL3tcptlcr4oazYt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>REG-CAP-008_Sessao-Tecnico-Fev2026.docx</t>
+          <t>REV-AASPAP01-001_Registro-de-Revisao-por-Pares.docx</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3267,41 +3263,41 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UYtCRfbMeXCdL_aXzAz-wpCs8bTC-sR1/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1b2XcTr_rrP1ntnEzllbB2gHNdFaEaLsQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>REG-CAP-008_Sessao-Tecnico-Fev2026.md</t>
+          <t>TAP-AASPAP01-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FCa5wLWvxiOHu1GJfKqXrdYfvC8mg7MG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1vj9arb9bNdy4z2DLV7U8sEbBp4GuIMHw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>REG-CAP-009_Reciclagem-Mar2026.docx</t>
+          <t>VV-AASPAP01-001_Plano-de-VV.docx</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3311,569 +3307,569 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1xgHZsTCrfuBCgwvVfWaSTZGsS3GZ7xiR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11Vx-bMcQfovROo3RwVY7-dQClEVcFp1e/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>REG-CAP-009_Reciclagem-Mar2026.md</t>
+          <t>andamentos_ApisParceiras.jpg</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>jpg</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1X5pxMU4f1oCgfCn65m8SE8bQkPUiYnl8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1di53G9P1RLs2VtusPoTRJay3fOG7c1L2/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>REG-CAP-010_Onboarding-Tecnico-Jan2026.docx</t>
+          <t>andamentos_arquitetura.svg</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pWjwFRZgCCd2D4MIN9AEhMIX176WACAg/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hwULBFas2YSOqC3BIi0dVbGelx-U-Mp0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>REG-CAP-010_Onboarding-Tecnico-Jan2026.md</t>
+          <t>andamentos_historicoPreservado.jpeg</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>jpeg</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jt5GFjbCsNurYrDdCoW-Pjmdr5BanLwK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Nx8OtLH1th3lVs3pRHd1yJjZ-l5jsR4s/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>REG-CAP-011_Workshop-Azure-APIM-Mar2026.docx</t>
+          <t>andamentos_historicoPreservado1.jpg</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>jpg</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11KTzVFyJCNcVZHItsY2HZwL8YX2CHk7r/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1zXIyrAtYHinI0oETDvC-PQ0sgF4Z6Fjy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>REG-CAP-011_Workshop-Azure-APIM-Mar2026.md</t>
+          <t>andamentos_historicoPreservado2.jpg</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>jpg</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1qu5roDPPeKIxp3C-DCMHOtkuavzA6DX_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1l8sW0voE8k-y6ew1dTbd5aePqlr5UffM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>REG-CAP-012_Workshop-Automacao-Testes-Fev2026.docx</t>
+          <t>andamentos_retry_webhook.jpeg</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>jpeg</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10RHw3_QQb3-yF4aCqLMMk7vNzROKhbXH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15lXDLmdWW620DS2qE9-qwIEzvAgmpGlW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>REG-CAP-012_Workshop-Automacao-Testes-Fev2026.md</t>
+          <t>devops_andamentos_branches.png</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13aw-J5V35sDlLWbE4MMCvt06qA8p-InU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YaLDEwp8l6FoyFTaMTEWMmeLqbT6gfnx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>REG-CAP-013_Consultoria-Desenho-Processos-Jun2025.docx</t>
+          <t>devops_andamentos_commits.png</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FpzpCSb3W1th24HWN5iUTN_O17YSW1NZ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fkX4bzm8iFGVFOtMtIK4rEtjZhF1bomY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>REG-CAP-013_Consultoria-Desenho-Processos-Jun2025.md</t>
+          <t>devops_andamentos_estrutura.png</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1sgqmkafBuD0gJ_EPNluW16VXUquFp24v/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1w_Hj4o0YyA0oYRSE1_5d1VE67_JisEFY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>REG-CAP-CV-001_Indice-de-Curriculos.docx</t>
+          <t>devops_andamentos_pipeline_ci.png</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1K0cu6iTTt70jGgGBXDo9pRWwPj3sGva4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1p1VezDp1C0XYPSOjQk978cQmrvGVrTWo/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>REG-CAP-CV-001_Indice-de-Curriculos.md</t>
+          <t>devops_andamentos_pipeline_cicd.png</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14INGstsvVIz7rsXaOxlfArjNflLSFd5x/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Zf1k0e36NnyOxq-zv6Rrz22N5tvM8x49/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>REL-CAP-001_Relatorio-de-Eficacia-2025.docx</t>
+          <t>devops_andamentos_pr_detail_1.png</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gXdIOCwtTvOW-QrBf8UYFEv2YEH8q6A3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1FSv2kmZbKNXOk5tjctohUFqHtn-BZ9bu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>REL-CAP-001_Relatorio-de-Eficacia-2025.md</t>
+          <t>devops_andamentos_pr_detail_2.png</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bEjNu5MAK6AZSURmLyDRxn2jegRay09J/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1oBhgj_wDBy_Ap5QoTy-HRRu7a62wsa6S/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TPL-CAP-001_Registro-de-Sessao-de-Treinamento.docx</t>
+          <t>devops_andamentos_prs.png</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CVkEt9LrB9ClXXPqYteGC9NnEgYKoXFe/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14Se4mDLpHgV5EjT8w7kd1TypMmOEmzMU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TPL-CAP-001_Registro-de-Sessao-de-Treinamento.md</t>
+          <t>devops_andamentos_tags.png</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1V6nwWP49ThNknbf0gvVkK19GFRQMZC4l/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fGjCYwKyDczuhAJPkpaxCMdrrCi7BRc4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TPL-CAP-002_Relatorio-de-Eficacia-de-Treinamento.docx</t>
+          <t>estrutura_andamentosProcessuais.png</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1m3HpIJ0JgLVQM9LaEDxMUgidJhkg6RJO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1BQ_7ZiscsMUDn84a_vBXcghhchm29hLs/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>01_apoio/cap</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TPL-CAP-002_Relatorio-de-Eficacia-de-Treinamento.md</t>
+          <t>00_INDICEAASPCNJ01_MapadeRegistros.docx</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1GHbjdOCqWlo0_K4rnKN-kgJDs-A9aNAI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1kf3EdS_AsVImdD6P_03zCt-OF7_UHj6N/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>01_apoio/cap/curriculos</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CV-Caroline-Jenifer_QA.pdf</t>
+          <t>ADAP-AASPCNJ01-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1C7vxxTRerQM1J7J344iub0tfSV86ozhc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14GFOTJj6jxDsV62h60zCqIgxnRW-DbWW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>01_apoio/cap/curriculos</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CV-Cezar-Velazquez_TechLead.pdf</t>
+          <t>ATA-AASPCNJ01-001_Ata-Alinhamento-Fluxo-CNJ.docx</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Wj_kGQvhXViFApjmjJDfvzUvbSuyqqV3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/12sOcC6FDaP-3OdoM1_duAMNNcbgYsQvb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>01_apoio/cap/curriculos</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CV-Flavio-Fernandes_GQA-Arquitetura.pdf</t>
+          <t>CAP-AASPCNJ01-001_Registro-de-Capacitacao-da-Equipe.docx</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1GSQQ2yS_E7-HnE2BFPsf1A-hkq2AVjPd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11db2exVuX-huVhgL8azaDzByfMFQv_pb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>01_apoio/cap/curriculos</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CV-Karen-Wada_Consultora-Processos.pdf</t>
+          <t>CR-AASPCNJ01-001_Change-Request.docx</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jX6ax9IDMALDHpoTCrcMMerF_nGIGpCr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1J3XOn56R7ruWa8vhPAnVzI7r092DFLY-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>01_apoio/cap/curriculos</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CV-Silvio-Baroni_SEPG-GPC.pdf</t>
+          <t>GCO-AASPCNJ01-001_Registro-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1rC4NvQveAUCAWQOkNiU8VvlVX2AkTN6i/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1IJozbK4BobNpyION4zPWa_s2auynxhv9/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>01_apoio/cap/curriculos</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CV-Wilson-Yamada_Sponsor-Portfolio.pdf</t>
+          <t>GDE-AASPCNJ01-001_Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11gRQH_6m7Eq1ojWkfu6hRK_AqTqY65ak/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1EpobYWmsjCftVdxosshioK0mCuXVFlEq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GUIA-GPR-001_Roteiro-de-Kickoff.docx</t>
+          <t>GEST-AASPCNJ01-001_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1icahhXdwUOXQA3txofLbVmOaFKnbaCxu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Vdng-5mBCjlXpajdZ6ScLD67c8e85qob/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>GUIA-GPR-001_Roteiro-de-Kickoff.md</t>
+          <t>GQA-AASPCNJ01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1N1YGy0ljWuoaq603HAmFjpJwrF1Yw-Ac/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1AI6TXKQ5f6Oh5g6VmFgzTmXNQHEtLOlh/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PRO-GPR-001_Processo-de-Gerencia-de-Projetos.docx</t>
+          <t>ITP-AASPCNJ01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3883,41 +3879,41 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1k8QAAFCQmb8sJAMKlrR-Pnv6MZqD1Xcy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tobpnNoEQf5LarNnPEJAEJnt5BAZGrtQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PRO-GPR-001_Processo-de-Gerencia-de-Projetos.md</t>
+          <t>MED-AASPCNJ01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tuaDp9oFw0sAVv4qe0BgsSPNKD_JgoMn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ePiJ3ONIXZf2gN00FzXuyUCIXdrpezsx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PRO-ITP-001_Processo-de-Integracao-do-Produto.docx</t>
+          <t>PCP-AASPCNJ01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3927,41 +3923,41 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Ua11xIFEHx4QTKpoKXZd3pFLXrES7OXW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ywDtDrM3zHptY2XfL6ut22ra3MEbuLTe/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PRO-ITP-001_Processo-de-Integracao-do-Produto.md</t>
+          <t>PLA-AASPCNJ01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1QdieFmzpCLXLGRwy_9QwjFuzKPM_-_03/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1y9zo8Fx1AewE2z9GVdmhsecKySyDoSf6/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PRO-PCP-001_Processo-de-Projeto-e-Construcao-do-Produto.docx</t>
+          <t>RAC-AASPCNJ01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3971,41 +3967,41 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1PFGeQPHNKcUFMFNIO9lT1CkO9RyUe0CD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1G_0Odyq4HbI3nfCyDh7-zZoXDgu_BiON/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PRO-PCP-001_Processo-de-Projeto-e-Construcao-do-Produto.md</t>
+          <t>RASTR-AASPCNJ01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D9wE8bol3nzsW802mrEujCEmqDJcaG3K/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1lfPyboZZ3hd-8g3IzjQRQciVYXCztgZw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PRO-REQ-001_Processo-de-Engenharia-de-Requisitos.docx</t>
+          <t>REL-VV-AASPCNJ01-001_Relatorio-de-Execucao-de-Testes.docx</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4015,41 +4011,41 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FE8Ytpu1fUrggTPn7A1hAI2rut4oeRV2/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1whC8gTS2Mz1CW7QajDlOMvfXNlxt5AP6/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PRO-REQ-001_Processo-de-Engenharia-de-Requisitos.md</t>
+          <t>REQ-AASPCNJ01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1mEmw_8na4H8-Wysz_K51-hNyfMGq7B25/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1GDwHhtK1Nc-2AptWo8HIryVHeOF8hzj5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PRO-VV-001_Processo-de-Verificacao-e-Validacao.docx</t>
+          <t>REV-AASPCNJ01-001_Registro-de-Revisao-por-Pares.docx</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4059,63 +4055,63 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UloaOSeholVwPG1uQTnwaYMCDd_Eqgu7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1PfM9kKAjFJofhtJn5xqgicqG-0-v3mA-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>02_projeto</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PRO-VV-001_Processo-de-Verificacao-e-Validacao.md</t>
+          <t>TAP-AASPCNJ01-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1QFnmCgrpXpIPNqirQS9EwAVR38zDCJE3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hKBUW2dTTfmd8PEs36tEuIQjsKjPAuRF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EXEMPLO-GPR-005_Status-Report-Exemplo-Preenchido.md</t>
+          <t>VV-AASPCNJ01-001_Plano-de-VV.docx</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tk09ctAQgOW2xowJIjnVQX9lx_DFpMvi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/199h316ZoZ43k7W_rnPpNq6GTBr502zuu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EXEMPLOGPR005_StatusReportExemploPreenchido.docx</t>
+          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4125,19 +4121,19 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1xdb1hYORBdN9jrAxuuqEunXIoDzptTBH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NaEJlUDHw0FE6fgH28gpifHft7ZLxUyL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TPL-GDE-001_Template-Registro-de-Analise-de-Decisao.docx</t>
+          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4147,41 +4143,41 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1V2VwWHjezpUNsDIy0eNM31mo0ydqiHa8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LNzyoQkTM7oLgWtSCPY6VxNqt4JS_MzM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TPL-GDE-001_Template-Registro-de-Analise-de-Decisao.md</t>
+          <t>ATA-FRUKI01-001_Ata-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1xqVF8ueYmwaKzDsDypX6n0YLy7Qq-6jU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pjAXblbrxR8Y6p5eq2BDYRBpiYlK3Ag_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TPL-GPC-001_Template-Registro-de-Verificacao-de-GQA.docx</t>
+          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.docx</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4191,41 +4187,41 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1vklwYMZeJFJ_hsULzyPPQfHSIBH2sPCG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1cypxWHL-NU9CPnLV47N-bKnP0QrSIB17/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TPL-GPC-001_Template-Registro-de-Verificacao-de-GQA.md</t>
+          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.docx</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TFVY8JIrsAd9K-a52ymx0PvhlA4yUgbE/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1m0odZUeHy212r9AQwyZ_sfwXzznT4oqJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TPL-GPR-001_Template-Plano-de-Projeto.docx</t>
+          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.docx</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4235,41 +4231,41 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JG7_Er7Cq5FfiS44dfcZlg0dKUwzWetA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/10Qo6yB8nqAQmzacMbuLZaVv1ZaX178Lt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TPL-GPR-001_Template-Plano-de-Projeto.md</t>
+          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.docx</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s74PRIyXyCSuRPi2_yCL3GsYk_N9pR0k/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1VmGwsZK4GLu_zpzmrHnD2XOChsiR1GZr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TPL-GPR-002_Template-Termo-de-Abertura.docx</t>
+          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.docx</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4279,41 +4275,41 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fw6vq92uHpUuJoVNuHbDPbVFC3gxVEm8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ujgsYTHnAVE_J60APn-OqGSRaCTbfPHf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TPL-GPR-002_Template-Termo-de-Abertura.md</t>
+          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.docx</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pvb4FoBeV8cBmdEE7OLmIntCAmxNMD4A/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bNAl7ljD0PhTyZEb-2ngdIbBzCpvNY2q/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TPL-GPR-003_Template-Registro-de-Adaptacao.docx</t>
+          <t>ATAFRUKI01008_AtaKickoffPacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4323,41 +4319,41 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17Q9cPXicAvMqAXYPz8ljpb5S2i0NePx_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11alVpwlnsPjgd1_PO4OzMBXeJLRz6PXi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TPL-GPR-003_Template-Registro-de-Adaptacao.md</t>
+          <t>AnaliseDecisao_FTFRUKI_TIMEWARE.xlsx</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/131xkb1wj3ZoJbRgkuNefU8bmLwACM3VD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19sYcZ40SHiEe7qUV7jau-3fruYrAzjWp/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TPL-GPR-004_Template-Termo-de-Encerramento.docx</t>
+          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.docx</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4367,41 +4363,41 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LFj2UMUcCD7ewIGlkRdshUo-HmJUMmad/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1z2TIuyQQTiU7fOKmK0kQfziTtE8NqiLc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TPL-GPR-004_Template-Termo-de-Encerramento.md</t>
+          <t>GCO-FRUKI01-001_Registro-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/133uiwTw2s2O63F5E-DBBeCh1MmFvOCS9/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fMcui7ebx_4af41JtRltlCCJzDWkd1eA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TPL-GPR-005_Template-Relatorio-de-Acompanhamento.docx</t>
+          <t>GDE-FRUKI01-001_Registro-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4411,41 +4407,41 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1U4pFEFtk7OwhzNix2RDuOcvWNT55XJQo/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1h8FKsNP59PnO8tzm2WEJ_vgsZYRSmjwX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>TPL-GPR-005_Template-Relatorio-de-Acompanhamento.md</t>
+          <t>GEST-FRUKI01-001_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HUSg5x0hlen1UY4RjPAiWh1a_ETf1RCu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RsktvVNbrH1f-RmcV3_AmIu3uJt9Q7sH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TPL-GPR-006_Template-Change-Request.docx</t>
+          <t>GQA-FRUKI01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4455,41 +4451,41 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1p400uzBBwZpSWLeGNzJlFy_so7UoDURu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jmdev8ggRDsbM_CrkMQY_oKaImvKG4vM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TPL-GPR-006_Template-Change-Request.md</t>
+          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HwSihP8liBxJcEfLsgiHgwJZFgulkd_y/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19YCw05XWIRh-NaI5GWf1c-MF6m5AhIra/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TPL-ITP-001_Template-Estrategia-de-Integracao.docx</t>
+          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4499,41 +4495,41 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1n3gUvRn54vsEAgZWQeXLxfbAoDoQRzEO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1A-6S0ZZmHteTzIjSNP46H2OJYgeI-Gc7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>TPL-ITP-001_Template-Estrategia-de-Integracao.md</t>
+          <t>LI-FRUKI01-001_Licoes-Aprendidas.docx</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gTeyMOv_qhfqWZf8J7Se4O9kxJiJDrZO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pXvWCErdbUdvvAcXV93935DeGW6bJ7xL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TPL-ORG-001_Template-Ata-de-Reuniao.docx</t>
+          <t>MED-FRUKI01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4543,41 +4539,41 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bdb2aarUtu2uLyhgCFVtS3FiyiKb7CF5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D6gCK_SBP31WdmYGToQH2iCZV1RdzhWI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>TPL-ORG-001_Template-Ata-de-Reuniao.md</t>
+          <t>PCP-FRUKI01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Cufw51GxH3TRru8xL9vDGHiYi8Mmjk6D/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ff6Ha1FH1T1XAJGnmdy2QvkrqXxCUg2s/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>TPL-PCP-001_Template-Documento-de-Design.docx</t>
+          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4587,41 +4583,41 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MzCnCw8RflPBrznE_xSEWci1LAaCoVLl/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17KodAvypysQkbqocfQIrlE2q1dfRIUnY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TPL-PCP-001_Template-Documento-de-Design.md</t>
+          <t>PLA-FRUKI01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1vGR1UiffaWOvicnoU8NpPHhO96NBwbhV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1WEPaZNg7rxj29B48l_scz7x7CyLlvoSf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TPL-REQ-001_Template-Documento-de-Requisitos.docx</t>
+          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4631,41 +4627,41 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1IGz8Jxln6UO_tCFNplT6fcHxq-5KEVB5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1d0l6IhtfbI9hE0UYxQm6nVq9grpjKnpn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TPL-REQ-001_Template-Documento-de-Requisitos.md</t>
+          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19Uus1IU9ab_z960ITUxm8xaNluk7_LGz/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_C3hZUp-7-2ldAa2BmIfZ3tMfa9WX0bd/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TPL-REQ-002_Template-Matriz-de-Rastreabilidade.docx</t>
+          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4675,41 +4671,41 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1W_0c8aevifCLVgNw8ecK3Djf4ar3Oatj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SokajsndvgCtPAX7FyUpNp9mIDxQrVQf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TPL-REQ-002_Template-Matriz-de-Rastreabilidade.md</t>
+          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/168VucASymzvMt5g-p_F1ZhfwocT5z7Ww/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1S4nR_PkZnGQrm6ppWv47ftgH2ptyG9xJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>TPL-VV-001_Template-Plano-de-Verificacao-e-Validacao.docx</t>
+          <t>REQ-FRUKI01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4719,41 +4715,41 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s0sjWb1MolACQ-3-GQajFDpnilc7kILw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1mCQ9GroaEFEjulblg31P0Kdknw95w8LJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TPL-VV-001_Template-Plano-de-Verificacao-e-Validacao.md</t>
+          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1QLlkyRwI39PE_ih1Vz-rXkSWnivf4fQb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1GexOXykQE4rnKFPmeW1kVQac18vsnlnQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TPL-VV-002_Template-Registro-de-Revisao-por-Pares.docx</t>
+          <t>TAE-FRUKI01-001_Termo-de-Encerramento.docx</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4763,63 +4759,63 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dgiWFADcf1hSgfkggK742ZZe0eEzaIcW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JNvLtWIaqno7WXqzPfQwcK1bRE3UjCRv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>03_templates</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>TPL-VV-002_Template-Registro-de-Revisao-por-Pares.md</t>
+          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DFf9iA8lOkL7694hyz2x_PV62A_itJoA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D3T0RHrOPhOq08Edxc1fWW-cZ1uR-e2n/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>00_INDICE-AASPCNJ01_Mapa-de-Registros.md</t>
+          <t>TAP-FRUKI01-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D36lT0gskRVQ2uCke-m0hlrWD_zs6lXk/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ehO_9gQoPrLS-Ykhxfnnsrn9KZ9o8zdH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>00_INDICEAASPCNJ01_MapadeRegistros.docx</t>
+          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4829,19 +4825,19 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1kf3EdS_AsVImdD6P_03zCt-OF7_UHj6N/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1UUmn_lYKBv8eG5UZBaLipFbSMdnYTxgU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ADAP-AASPCNJ01-001_Registro-de-Adaptacao.docx</t>
+          <t>VV-FRUKI01-001_Plano-VeV.docx</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4851,41 +4847,41 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14GFOTJj6jxDsV62h60zCqIgxnRW-DbWW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1yCFY98oM8rlf44HUIeERib4_7jtYsKeU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ADAP-AASPCNJ01-001_Registro-de-Adaptacao.md</t>
+          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1AQtE9Q0KvpKNIY8fWtCWUrUCzhlx9iTa/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1d_okleyBKoPtPW2zEy7300KiXoWL62oj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ATA-AASPCNJ01-001_Ata-Alinhamento-Fluxo-CNJ.docx</t>
+          <t>ADAP-GASMIG02-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4895,41 +4891,41 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12sOcC6FDaP-3OdoM1_duAMNNcbgYsQvb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1uDnjyU3hDOdzbVZPUFA-1PGqXCsuDeS7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ATA-AASPCNJ01-001_Ata-Alinhamento-Fluxo-CNJ.md</t>
+          <t>ADAP-GASMIG02-002_Registro-de-Adaptacao-OS002.docx</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MEhewPJ_pd35kgdky_xETqE3I6XR7zMC/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1oQshhvn5DIq1DoB3rybc8jEbP_OdEnfn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>CAP-AASPCNJ01-001_Registro-de-Capacitacao-da-Equipe.docx</t>
+          <t>ATA-GASMIG02-001_Ata-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4939,41 +4935,41 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11db2exVuX-huVhgL8azaDzByfMFQv_pb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1XcstqfQTQC0cm8wZgfc9oLgjSknU6Ueq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>CAP-AASPCNJ01-001_Registro-de-Capacitacao-da-Equipe.md</t>
+          <t>ATA-GASMIG02-002_Ata-de-Aceite-OS001.docx</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jba7CzH_o_sggKZ6Y8pjjfxXTPwIMjf4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CcRbEbIcDWeHO7sOznH_FcuK-uVVusM0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>CR-AASPCNJ01-001_Change-Request.docx</t>
+          <t>ATA-GASMIG02-003_Apresentacao-Entrega-OS002.docx</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4983,41 +4979,41 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1J3XOn56R7ruWa8vhPAnVzI7r092DFLY-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YCW3PFHS2p1bh8O6VWyZ8y2NFoG6ZWFN/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>CR-AASPCNJ01-001_Change-Request.md</t>
+          <t>AnaliseDecisao_FTGASMIG_TIMEWARE.xlsx</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LC7TXf4KqwN2oIEgL4sq74Zhg_eCPYST/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1u5oCqJrnQuaPBUMqTNQvaukwxqZvsmQi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>GCO-AASPCNJ01-001_Registro-de-Configuracao.docx</t>
+          <t>CAP-GASMIG02-001_Registro-de-Capacitacao-da-Equipe.docx</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5027,41 +5023,41 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1IJozbK4BobNpyION4zPWa_s2auynxhv9/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ibleg7tRQDHfYp3ahRpAlbYjKetFDzzT/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>GCO-AASPCNJ01-001_Registro-de-Configuracao.md</t>
+          <t>GCO-GASMIG02-001_Gerencia-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Dolv6F6w1b-HrjYBemHVis-JZjL3-vJR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1qpIzDVbsmVYkiXW9NNdciOuv5iovMNu4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>GDE-AASPCNJ01-001_Registro-de-Analise-de-Decisao.docx</t>
+          <t>GDE-GASMIG02-001_Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5071,63 +5067,63 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1EpobYWmsjCftVdxosshioK0mCuXVFlEq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1sqAtX-R1-EjASMtMCnp_fjiessTaSaQU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>GDE-AASPCNJ01-001_Registro-de-Analise-de-Decisao.md</t>
+          <t>GEST-GASMIG02_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15uYGS_DNz4Dt1mxmx4-PkQB9MUGfjffr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1r_dSFP9AmEnj79FkmqU80OkuYWnwzfZS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>GEST-AASPCNJ01_Planilha-de-Gestao-do-Projeto.xlsx</t>
+          <t>GQA-GASMIG02-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Vdng-5mBCjlXpajdZ6ScLD67c8e85qob/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1V-T1g_9AKu9TLFPROMR0fA1gkyx180a-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>GQA-AASPCNJ01-001_Registro-de-GQA.docx</t>
+          <t>ITP-GASMIG02-002_Estrategia-de-Integracao-OS002.docx</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5137,41 +5133,41 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1AI6TXKQ5f6Oh5g6VmFgzTmXNQHEtLOlh/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JIAbQHVpTSO3V0AKGnWyVwEs6zuTWX7R/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>GQA-AASPCNJ01-001_Registro-de-GQA.md</t>
+          <t>LI-GASMIG02-001_Licoes-Aprendidas.docx</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1aYLuwSN8gKUIFpg3W53cgZGHwjUDmpb7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ra9yyJuVYa2tmQW0DKwbJgannxAI2W0E/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ITP-AASPCNJ01-001_Estrategia-de-Integracao.docx</t>
+          <t>MED-GASMIG02-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5181,41 +5177,41 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tobpnNoEQf5LarNnPEJAEJnt5BAZGrtQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LtjN_WSjn_g1wQ_RRLe4Z4KP6Cnu-Ohx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ITP-AASPCNJ01-001_Estrategia-de-Integracao.md</t>
+          <t>PCP-GASMIG02-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cnLnAHipePGdvP26u1bQqQNAGlLCQ_LC/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YI-40O6IWGMB0C_R6ytpbxc2w1E7W4fF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MED-AASPCNJ01-001_Registro-de-Medicao.docx</t>
+          <t>PCP-GASMIG02-002_Documento-de-Design-OS002.docx</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5225,41 +5221,41 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ePiJ3ONIXZf2gN00FzXuyUCIXdrpezsx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Q4M2R4uqiy81BP8L3HiQ_idRqmpMt8Cw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MED-AASPCNJ01-001_Registro-de-Medicao.md</t>
+          <t>PLA-GASMIG02-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uewnWBXzHNoc6W1skfMxGLgrWRS-lGh3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZIwX-h0RDNJfhO5AXev2vqhYrGHOr2qf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PCP-AASPCNJ01-001_Documento-de-Design.docx</t>
+          <t>PLA-GASMIG02-002_Plano-de-Projeto-OS002.docx</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5269,41 +5265,41 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ywDtDrM3zHptY2XfL6ut22ra3MEbuLTe/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jfUDk7bhCtOXUYDcBnpjOx8FARp2VqPH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PCP-AASPCNJ01-001_Documento-de-Design.md</t>
+          <t>RAC-GASMIG02-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Unza8xmgkJujBYgKw8pg35-61abEm6WL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bAl8o8UPkTb1AHypGNvRxEJG8UYswpvS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PLA-AASPCNJ01-001_Plano-de-Projeto.docx</t>
+          <t>RASTR-GASMIG02-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5313,41 +5309,41 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1y9zo8Fx1AewE2z9GVdmhsecKySyDoSf6/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_delTbo-PEeRpuGGGagv5p2SOF-ZNRos/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PLA-AASPCNJ01-001_Plano-de-Projeto.md</t>
+          <t>RASTR-GASMIG02-002_Matriz-de-Rastreabilidade-OS002.docx</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15UPh6z7b9ZUbUVUBpANR2ow4EsIDxn9Y/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tfy9oNEOsThCKNb1YrvQq8Ll1jX9kYJO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>RAC-AASPCNJ01-001_Relatorio-de-Acompanhamento.docx</t>
+          <t>REQ-GASMIG02-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5357,41 +5353,41 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1G_0Odyq4HbI3nfCyDh7-zZoXDgu_BiON/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13duq0igfGKvJAHKh_sD9TN7WqTpuOfdn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>RAC-AASPCNJ01-001_Relatorio-de-Acompanhamento.md</t>
+          <t>REQ-GASMIG02-002_Documento-de-Requisitos-OS002.docx</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16scQtbSvdpQbF0OS7KCRBRDLBpLI6gt7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_yN7yHPBc9iKilAlxd4pxj52G1_WoCHP/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>RASTR-AASPCNJ01-001_Matriz-de-Rastreabilidade.docx</t>
+          <t>REV-GASMIG02-001_Registro-de-Verificacao-Tecnica.docx</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5401,41 +5397,41 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1lfPyboZZ3hd-8g3IzjQRQciVYXCztgZw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1biHfNjSf_g7hnUcjBATCG48aG7ARNvRL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>RASTR-AASPCNJ01-001_Matriz-de-Rastreabilidade.md</t>
+          <t>TAE-GASMIG02-001_Termo-de-Encerramento-OS001.docx</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1iDvjlcbuCL2sr01UQ1vqRONHz0aST6x8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1mw7eJBj6HANyIYJ1MgxEnO59ML9sl5aa/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>REL-VV-AASPCNJ01-001_Relatorio-de-Execucao-de-Testes.docx</t>
+          <t>TAE-GASMIG02-002_Termo-de-Encerramento-OS002.docx</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5445,41 +5441,41 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1whC8gTS2Mz1CW7QajDlOMvfXNlxt5AP6/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-zvT45vPsVTAwmcEzQVak8qKT4dnQWEr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>REL-VV-AASPCNJ01-001_Relatorio-de-Execucao-de-Testes.md</t>
+          <t>TAP-GASMIG02-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UECG0sMcEQrEyTkMtTW2vDyOGYuPYlov/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1WW3VNRafS44JkZiXK29Rm7bYI7NbP9rS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>REQ-AASPCNJ01-001_Documento-de-Requisitos.docx</t>
+          <t>TAP-GASMIG02-002_Termo-de-Abertura-OS002.docx</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5489,41 +5485,41 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1GDwHhtK1Nc-2AptWo8HIryVHeOF8hzj5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1cMUOhgzZzj6wwWIijFMDugRVZIl8aPvf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>REQ-AASPCNJ01-001_Documento-de-Requisitos.md</t>
+          <t>VV-GASMIG02-001_Plano-de-VV.docx</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YFHxBJU-mxG2nTGtwGVL2EGqDw6MYkcV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15t1yh5oMbpFZ47rREDx9kJPgS8oXyRmy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>REV-AASPCNJ01-001_Registro-de-Revisao-por-Pares.docx</t>
+          <t>VV-GASMIG02-002_Plano-de-VV-OS002.docx</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5533,41 +5529,41 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1PfM9kKAjFJofhtJn5xqgicqG-0-v3mA-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18GgauiJykVy8AASSKtJcqkt2FR-6AuRv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>REV-AASPCNJ01-001_Registro-de-Revisao-por-Pares.md</t>
+          <t>ADAP-PROFARMA01-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YPUEV8VMC4rLiB6ie182lY_9nRz72wdA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1aRgkciq4Ed3iPJgEbe1jJnpkXKlF4Tma/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>TAP-AASPCNJ01-001_Termo-de-Abertura.docx</t>
+          <t>ATA-PROFARMA01-001_Ata-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5577,85 +5573,85 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hKBUW2dTTfmd8PEs36tEuIQjsKjPAuRF/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1uNkVDge5WAgwLTCcUFZmBLlqKog16nmG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>TAP-AASPCNJ01-001_Termo-de-Abertura.md</t>
+          <t>ATA-PROFARMA01-002_Ata-de-Aceite-Final.docx</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1l6PmtiKd-wy4CyjEgbhN3gky-4NRb3lk/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1odIVE62I5L7iqqLFUCACbHt3w2HRB8yR/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>VV-AASPCNJ01-001_Plano-de-VV.docx</t>
+          <t>Analise-Decisao_PROFARMA_TIMEWARE.xlsx</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/199h316ZoZ43k7W_rnPpNq6GTBr502zuu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1iS1LRiviBLZgmxymc7Hfq7szzjUGkHjK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>VV-AASPCNJ01-001_Plano-de-VV.md</t>
+          <t>CR-PROFARMA01-001_Registro-de-Change-Requests.docx</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1svrQKE2lJHz91RMvgbx21RNEHw60XMoz/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1XWRRoeJ6NnvjCG3S0hlyPyxnMfkf9vM7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.docx</t>
+          <t>CTQ-PROFARMA01-001_Cenarios-de-Teste-Homologacao.docx</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5665,41 +5661,41 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NaEJlUDHw0FE6fgH28gpifHft7ZLxUyL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ts70FWbIasG3sf9qDBSw8cXldJfRJ7bY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.md</t>
+          <t>EV-AzureDevOps-PROFARMA01-001.docx</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jd-ueS7tJ7ipM9MvSxY0E9QI04RMOAxj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1K3LjcxoNE5lRsuUe0IIkCtwreoj3Bizv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.docx</t>
+          <t>EV-Jira-PROFARMA01-001.docx</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5709,41 +5705,41 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LNzyoQkTM7oLgWtSCPY6VxNqt4JS_MzM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ftGwgagbTkMohz_ZpKcLT0Z1_cPq_4A9/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.md</t>
+          <t>EV-Swagger-PROFARMA01-001.docx</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JDPNC85L1TdEuweMvEmJphAH00Y8VbT0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17hu5hEzQctuc6OaDun7ki1pn1f-fp7cL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-001_Ata-de-Kickoff.docx</t>
+          <t>GCO-PROFARMA01-001_Registro-de-Gerencia-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5753,85 +5749,85 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pjAXblbrxR8Y6p5eq2BDYRBpiYlK3Ag_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ld1PXP0yafu0eW7nUNXN0iRCm1P7cskc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-001_Ata-de-Kickoff.md</t>
+          <t>GDE-PROFARMA01-001_Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15oaq3TW916Xz4agaxLeZq1-WTml1R5YU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1wU_hxVhwrX-XUT1OQmEKxw80Mz0T5Rat/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.docx</t>
+          <t>GEST-PROFARMA01_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cypxWHL-NU9CPnLV47N-bKnP0QrSIB17/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/12SEFOVCAA1jVQRgM1c1RDR_CL3KaW32_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.md</t>
+          <t>GQA-PROFARMA01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ficMpIGp18dxZ3mASn0bnpOcFIF6IkM5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hefq-kmdiYVOIvc0RoWHcSVQDBbL8Fq4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.docx</t>
+          <t>ITP-PROFARMA01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5841,41 +5837,41 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1m0odZUeHy212r9AQwyZ_sfwXzznT4oqJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1DKKcqAZK78dkV2UIRRSXHtELjnxdw4aj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.md</t>
+          <t>LI-PROFARMA01-001_Licoes-Aprendidas.docx</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Qk8B-Ny6zACkDanQ0QBsqznIzvzIX3xd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NMayhfr_e6Li-R0NEGoST5QATJgifMc7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.docx</t>
+          <t>MED-PROFARMA01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5885,41 +5881,41 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10Qo6yB8nqAQmzacMbuLZaVv1ZaX178Lt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nmbiWfvYMAAa7Y5pO14VxaZgxEPQuKOn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.md</t>
+          <t>PCP-PROFARMA01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1rfeMludEbjF7UISCTitVTklQgOVogPet/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1t0fD748MR_EBRMHsgQzVGLKRnJ4Zq7__/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.docx</t>
+          <t>PLA-PROFARMA01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5929,41 +5925,41 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1VmGwsZK4GLu_zpzmrHnD2XOChsiR1GZr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/189Kp-xA8BJ3SsO9NhxDyDOUtX3dADifK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.md</t>
+          <t>RAC-PROFARMA01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fL2lzK5ltJRAvrvBkZRGzHxNEI9xu5Bw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1HjCxyFwvC7Fxp4OXwxjqqL7OyYlSfI9x/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.docx</t>
+          <t>RASTR-PROFARMA01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5973,41 +5969,41 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ujgsYTHnAVE_J60APn-OqGSRaCTbfPHf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ep0JvVMNhdLVRwWXVMIyfLxurd7ReAyI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.md</t>
+          <t>REL-VV-PROFARMA01-001_Relatorio-de-Execucao-de-Testes.docx</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/18EWiPMrnjSsiQaE_8C28PSBqL_lgVLlm/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1KF8zj0lufb0VPg6riJwGhibojJJIopHM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.docx</t>
+          <t>REQ-PROFARMA01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6017,63 +6013,63 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bNAl7ljD0PhTyZEb-2ngdIbBzCpvNY2q/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17OE2PW4XkEy3OnJlSb6rtsHHh9ouTFJE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.md</t>
+          <t>REV-PROFARMA01-001_Registro-de-Revisao-Tecnica.docx</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RmwGe1-htZ1eswLCBIdw6KiYYnUMyFz7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dHd-EpgVX2Mg2Wo5Y_uxB8KFH4qphhxM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-008_Ata-Kickoff-PacoteFinal24.md</t>
+          <t>TAE-PROFARMA01-001_Termo-de-Encerramento.docx</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RNsmRLVuhzH7B7xEow8TR1epFtoTJuTG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1k_UZ_jWRVmpHA1Iiysa7vKvUwQ1T8QED/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>ATAFRUKI01008_AtaKickoffPacoteFinal24.docx</t>
+          <t>TAP-PROFARMA01-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6083,19 +6079,19 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11alVpwlnsPjgd1_PO4OzMBXeJLRz6PXi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13BKbRnLmlBDMBkioH54vOpmicKqlei8W/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.docx</t>
+          <t>VV-PROFARMA01-001_Plano-de-VV.docx</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6105,41 +6101,41 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1z2TIuyQQTiU7fOKmK0kQfziTtE8NqiLc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15tRkpsMad47tD4gPdlLKImY5ipIadjxw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>05_capacidade</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.md</t>
+          <t>MAPA-CAP-001_Mapa-de-Capacidade-dos-Processos.docx</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/18ut_8KPcueRiLUgl0CPLPR-G2vvZPtx3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17csazhVOlhhgaMN-DCmoQEUiJsfrN1Il/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>05_capacidade</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>GCO-FRUKI01-001_Registro-de-Configuracao.docx</t>
+          <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.docx</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6149,3312 +6145,34 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fMcui7ebx_4af41JtRltlCCJzDWkd1eA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1j98CQbhiUr74uV7VenwJcEhnLmLupxhe/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>05_capacidade</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>GCO-FRUKI01-001_Registro-de-Configuracao.md</t>
+          <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.xlsx</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19M3LWTGKSzJ_rDQJfGF5sSg2Stj4ooYw/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>GDE-FRUKI01-001_Registro-de-Decisao.docx</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D262" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1h8FKsNP59PnO8tzm2WEJ_vgsZYRSmjwX/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>GDE-FRUKI01-001_Registro-de-Decisao.md</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1y8vwxSDf1lQ_dMEoGp96MINftpHX1yzj/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>GQA-FRUKI01-001_Registro-de-GQA.docx</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1jmdev8ggRDsbM_CrkMQY_oKaImvKG4vM/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>GQA-FRUKI01-001_Registro-de-GQA.md</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D265" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1LQg4Ts7Gp-dH1rHTCtPzOWBXODTb-xB0/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.docx</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D266" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/19YCw05XWIRh-NaI5GWf1c-MF6m5AhIra/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.md</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D267" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1V-b-qbGgRW_GmmllG836nIib4F-1bxmQ/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.docx</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1A-6S0ZZmHteTzIjSNP46H2OJYgeI-Gc7/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.md</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1u4DcmW9hpA01pW7nlBsxOxkvs7OFFkAX/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>LI-FRUKI01-001_Licoes-Aprendidas.docx</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D270" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1pXvWCErdbUdvvAcXV93935DeGW6bJ7xL/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>LI-FRUKI01-001_Licoes-Aprendidas.md</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1-LL6sPo2lPFF-5U-rT-v0w15M_USlgul/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>MED-FRUKI01-001_Registro-de-Medicao.docx</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1D6gCK_SBP31WdmYGToQH2iCZV1RdzhWI/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>MED-FRUKI01-001_Registro-de-Medicao.md</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1VXH2Vf2-E0ExrU0D-meV5m2J1TU5rnT3/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>PCP-FRUKI01-001_Documento-de-Design.docx</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ff6Ha1FH1T1XAJGnmdy2QvkrqXxCUg2s/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>PCP-FRUKI01-001_Documento-de-Design.md</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ZdDvNKE7Q1pA5rx5QPnYLd9FQHaqq-W8/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.docx</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/17KodAvypysQkbqocfQIrlE2q1dfRIUnY/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.md</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D277" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1OSDTx1gAc6_yJw_cN8rhwy4doQynXsws/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>PLA-FRUKI01-001_Plano-de-Projeto.docx</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D278" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1WEPaZNg7rxj29B48l_scz7x7CyLlvoSf/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>PLA-FRUKI01-001_Plano-de-Projeto.md</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D279" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ak4cVI3YUmLkRgLKhcjIooEnGCJzS8J8/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.docx</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D280" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1d0l6IhtfbI9hE0UYxQm6nVq9grpjKnpn/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.md</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D281" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1s4eNRbcYfsKtdn4cleCJkIN9t2cJAjGI/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.docx</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1_C3hZUp-7-2ldAa2BmIfZ3tMfa9WX0bd/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.md</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D283" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/13Yx9B8mhKozIn9UHPmgI25DWFBsOfqD8/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>RAC-FRUKI01-002_Planilha-de-Gestao-do-Projeto.xlsx</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>xlsx</t>
-        </is>
-      </c>
-      <c r="D284" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1RsktvVNbrH1f-RmcV3_AmIu3uJt9Q7sH/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>RAC-FRUKI01-002_Relatorio-de-Acompanhamento-Pacote1.md</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D285" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1o6AlWFp1nR1m5JRHVda54B19LaoFoMPO/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.docx</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D286" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1SokajsndvgCtPAX7FyUpNp9mIDxQrVQf/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.md</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D287" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ezQXGXqPC-2UMfRdDvudgmasO6TMO5n8/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.docx</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D288" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1S4nR_PkZnGQrm6ppWv47ftgH2ptyG9xJ/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.md</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D289" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1s3__jTdqb1JrJQw3l9DS-tzsy28cYC2k/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>REQ-FRUKI01-001_Documento-de-Requisitos.docx</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D290" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1mCQ9GroaEFEjulblg31P0Kdknw95w8LJ/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>REQ-FRUKI01-001_Documento-de-Requisitos.md</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D291" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1m-7E7kW4OvRkUWA6EpO3BFveXiLIVHOF/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.docx</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D292" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1GexOXykQE4rnKFPmeW1kVQac18vsnlnQ/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.md</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D293" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1QSxYq6k8W1KxoVcr90P_31Xzmbb5uN5x/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>TAE-FRUKI01-001_Termo-de-Encerramento.docx</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D294" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1JNvLtWIaqno7WXqzPfQwcK1bRE3UjCRv/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>TAE-FRUKI01-001_Termo-de-Encerramento.md</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D295" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1CWoASfmkMEYq_njAEpXGu_vwEjx7pAEn/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.docx</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D296" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1D3T0RHrOPhOq08Edxc1fWW-cZ1uR-e2n/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.md</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D297" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1TJpNI9gAt8nH0qi87whhkajt8msTG1TO/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>TAP-FRUKI01-001_Termo-de-Abertura.docx</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D298" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ehO_9gQoPrLS-Ykhxfnnsrn9KZ9o8zdH/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>TAP-FRUKI01-001_Termo-de-Abertura.md</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D299" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/14-7t7EZ-5YdrL7xVn6VgTR75jDcQ9EW_/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.docx</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D300" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1UUmn_lYKBv8eG5UZBaLipFbSMdnYTxgU/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.md</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D301" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1q0Jciu5Wzc6Zn7-k55piZ2OS7Ty4gw71/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>VV-FRUKI01-001_Plano-VeV.docx</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D302" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1yCFY98oM8rlf44HUIeERib4_7jtYsKeU/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>VV-FRUKI01-001_Plano-VeV.md</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D303" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ZtSNIU4pURtj7fcqmo-Ze_PUgT8Xd8qS/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.docx</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D304" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1d_okleyBKoPtPW2zEy7300KiXoWL62oj/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.md</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D305" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ifZ0yJp1bIsYSQtVRi9gIzDztsm9Uj3c/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>ADAP-GASMIG02-001_Registro-de-Adaptacao.docx</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D306" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1uDnjyU3hDOdzbVZPUFA-1PGqXCsuDeS7/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>ADAP-GASMIG02-001_Registro-de-Adaptacao.md</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D307" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1bejNoYCCCfk5qhr7XWZz2N5g8q3KPhCD/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>ADAP-GASMIG02-002_Registro-de-Adaptacao-OS002.docx</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D308" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1oQshhvn5DIq1DoB3rybc8jEbP_OdEnfn/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>ADAP-GASMIG02-002_Registro-de-Adaptacao-OS002.md</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D309" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Yi_n_zxaS-YAOGbQ8gg16RdRtmvKn6CA/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>ATA-GASMIG02-001_Ata-de-Kickoff.docx</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D310" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1XcstqfQTQC0cm8wZgfc9oLgjSknU6Ueq/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>ATA-GASMIG02-001_Ata-de-Kickoff.md</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D311" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/173I8V-9u9y4GjYm6CqXrqhL5_XLf0-Tx/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>ATA-GASMIG02-002_Ata-de-Aceite-OS001.docx</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D312" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1CcRbEbIcDWeHO7sOznH_FcuK-uVVusM0/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>ATA-GASMIG02-002_Ata-de-Aceite-OS001.md</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D313" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1SMbROaSFGiRfxwoXqmEw9SWLkqJ0nZYZ/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>ATA-GASMIG02-003_Apresentacao-Entrega-OS002.docx</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D314" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1YCW3PFHS2p1bh8O6VWyZ8y2NFoG6ZWFN/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>ATA-GASMIG02-003_Apresentacao-Entrega-OS002.md</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D315" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Un3zSWdjWObqjJfrr8dwWvNnHDKNzuMk/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>CAP-GASMIG02-001_Registro-de-Capacitacao-da-Equipe.docx</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D316" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ibleg7tRQDHfYp3ahRpAlbYjKetFDzzT/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>CAP-GASMIG02-001_Registro-de-Capacitacao-da-Equipe.md</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D317" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1S5Rvx0kYOz7QPQDU_BA3SpNA1xdAk8Fa/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>GCO-GASMIG02-001_Gerencia-de-Configuracao.docx</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D318" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1qpIzDVbsmVYkiXW9NNdciOuv5iovMNu4/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>GCO-GASMIG02-001_Gerencia-de-Configuracao.md</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D319" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/193BAen9QIQt12KAzqakGH_bNUvMEdxpj/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>GDE-GASMIG02-001_Registro-de-Analise-de-Decisao.docx</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D320" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1sqAtX-R1-EjASMtMCnp_fjiessTaSaQU/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>GDE-GASMIG02-001_Registro-de-Analise-de-Decisao.md</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D321" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/15jlfJFiL4Kw0-bg2ZZcKnt7eKmay43k5/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>GEST-GASMIG02_Planilha-de-Gestao-do-Projeto.xlsx</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>xlsx</t>
-        </is>
-      </c>
-      <c r="D322" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1r_dSFP9AmEnj79FkmqU80OkuYWnwzfZS/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>GQA-GASMIG02-001_Registro-de-GQA.docx</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D323" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1V-T1g_9AKu9TLFPROMR0fA1gkyx180a-/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>GQA-GASMIG02-001_Registro-de-GQA.md</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D324" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1uDY2HGSwfZRlYwyZ5zGbGQ_290rYm_Xd/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>ITP-GASMIG02-002_Estrategia-de-Integracao-OS002.docx</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D325" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1JIAbQHVpTSO3V0AKGnWyVwEs6zuTWX7R/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>ITP-GASMIG02-002_Estrategia-de-Integracao-OS002.md</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D326" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/15xAI-a66USbhl_h-DlQ4iWYBif6a4NYy/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>LI-GASMIG02-001_Licoes-Aprendidas.docx</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D327" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ra9yyJuVYa2tmQW0DKwbJgannxAI2W0E/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>LI-GASMIG02-001_Licoes-Aprendidas.md</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D328" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1jn56o4n7EISf_OPXoT7W91T_SeJSteQA/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>MED-GASMIG02-001_Registro-de-Medicao.docx</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D329" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1LtjN_WSjn_g1wQ_RRLe4Z4KP6Cnu-Ohx/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>MED-GASMIG02-001_Registro-de-Medicao.md</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D330" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1yRECVQiPUAD3E8A6sSqcIjuCWsGJFOnN/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>PCP-GASMIG02-001_Documento-de-Design.docx</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D331" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1YI-40O6IWGMB0C_R6ytpbxc2w1E7W4fF/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>PCP-GASMIG02-001_Documento-de-Design.md</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D332" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1rRXvNXOxYx1RmwJPihw-IlOEnMHL3LPi/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>PCP-GASMIG02-002_Documento-de-Design-OS002.docx</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D333" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Q4M2R4uqiy81BP8L3HiQ_idRqmpMt8Cw/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>PCP-GASMIG02-002_Documento-de-Design-OS002.md</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D334" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1jR60AUVUBrZqmoZx6a1AKAAmbEdEUR0V/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>PLA-GASMIG02-001_Plano-de-Projeto.docx</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D335" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ZIwX-h0RDNJfhO5AXev2vqhYrGHOr2qf/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>PLA-GASMIG02-001_Plano-de-Projeto.md</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D336" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1q5NeTQRiY7BnnB2UiWdcG_ggbMB_Oigy/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>PLA-GASMIG02-002_Plano-de-Projeto-OS002.docx</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D337" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1jfUDk7bhCtOXUYDcBnpjOx8FARp2VqPH/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>PLA-GASMIG02-002_Plano-de-Projeto-OS002.md</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D338" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1OQok5rhtLilsAl3lboUjxAeWoRCa6SXA/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>RAC-GASMIG02-001_Relatorio-de-Acompanhamento.docx</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D339" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1bAl8o8UPkTb1AHypGNvRxEJG8UYswpvS/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>RAC-GASMIG02-001_Relatorio-de-Acompanhamento.md</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D340" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/18grlbdgF-XIQJtb8UNmCvJ25UOqHWb9b/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>RASTR-GASMIG02-001_Matriz-de-Rastreabilidade.docx</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D341" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1_delTbo-PEeRpuGGGagv5p2SOF-ZNRos/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>RASTR-GASMIG02-001_Matriz-de-Rastreabilidade.md</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D342" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1s5eS3sxpXkZh0TY8Ws0nl6jo8CRWPWyi/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>RASTR-GASMIG02-002_Matriz-de-Rastreabilidade-OS002.docx</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D343" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1tfy9oNEOsThCKNb1YrvQq8Ll1jX9kYJO/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>RASTR-GASMIG02-002_Matriz-de-Rastreabilidade-OS002.md</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D344" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1WiIbZeuVyYE2ZPrnLjkoiqVH3_8Y3Igz/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>REQ-GASMIG02-001_Documento-de-Requisitos.docx</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D345" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/13duq0igfGKvJAHKh_sD9TN7WqTpuOfdn/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>REQ-GASMIG02-001_Documento-de-Requisitos.md</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D346" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1qU0dScZMsyE9b5u1RENM0M85uevSdmrL/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>REQ-GASMIG02-002_Documento-de-Requisitos-OS002.docx</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D347" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1_yN7yHPBc9iKilAlxd4pxj52G1_WoCHP/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>REQ-GASMIG02-002_Documento-de-Requisitos-OS002.md</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D348" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1tyw98Wg84EnhfdKkHSJw6IoGaXSZ6JgK/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>REV-GASMIG02-001_Registro-de-Verificacao-Tecnica.docx</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D349" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1biHfNjSf_g7hnUcjBATCG48aG7ARNvRL/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>REV-GASMIG02-001_Registro-de-Verificacao-Tecnica.md</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D350" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1uDopfyiOr-PKrdBbesatAYkF1YOgH1g6/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>TAE-GASMIG02-001_Termo-de-Encerramento-OS001.docx</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D351" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1mw7eJBj6HANyIYJ1MgxEnO59ML9sl5aa/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>TAE-GASMIG02-001_Termo-de-Encerramento-OS001.md</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D352" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/16Tvn5wYajcpGwNyPouZCvoJWXDedha5s/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>TAE-GASMIG02-002_Termo-de-Encerramento-OS002.docx</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D353" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1-zvT45vPsVTAwmcEzQVak8qKT4dnQWEr/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>TAE-GASMIG02-002_Termo-de-Encerramento-OS002.md</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D354" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Gvd3sqaF500esvT_KQXRRYQOKtSLBa1f/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>TAP-GASMIG02-001_Termo-de-Abertura.docx</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D355" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1WW3VNRafS44JkZiXK29Rm7bYI7NbP9rS/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>TAP-GASMIG02-001_Termo-de-Abertura.md</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D356" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1X37fcpWgIcSM5LirpbU23geQekmjCp_i/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>TAP-GASMIG02-002_Termo-de-Abertura-OS002.docx</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D357" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1cMUOhgzZzj6wwWIijFMDugRVZIl8aPvf/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>TAP-GASMIG02-002_Termo-de-Abertura-OS002.md</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D358" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1EDT02kT9MVQV0gWPgpmAcCbVHa8T5GH8/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>VV-GASMIG02-001_Plano-de-VV.docx</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D359" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/15t1yh5oMbpFZ47rREDx9kJPgS8oXyRmy/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>VV-GASMIG02-001_Plano-de-VV.md</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D360" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1u0GkYIZ3U_T3KbW9zDIyrX41XWlzafgu/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>VV-GASMIG02-002_Plano-de-VV-OS002.docx</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D361" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/18GgauiJykVy8AASSKtJcqkt2FR-6AuRv/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>VV-GASMIG02-002_Plano-de-VV-OS002.md</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D362" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1hDwgWy26ua7WcoidKXwkRKdPA3f8SgHB/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>ADAP-PROFARMA01-001_Registro-de-Adaptacao.docx</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D363" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1aRgkciq4Ed3iPJgEbe1jJnpkXKlF4Tma/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>ADAP-PROFARMA01-001_Registro-de-Adaptacao.md</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D364" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1qa1eP5ZefDj1uNO-X1akjz55I4ZqmCOn/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>ATA-PROFARMA01-001_Ata-de-Kickoff.docx</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D365" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1uNkVDge5WAgwLTCcUFZmBLlqKog16nmG/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>ATA-PROFARMA01-001_Ata-de-Kickoff.md</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D366" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1lUV0rrT2F--Db0coxhXjcOre7lWH4HOU/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>ATA-PROFARMA01-002_Ata-de-Aceite-Final.docx</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D367" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1odIVE62I5L7iqqLFUCACbHt3w2HRB8yR/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>ATA-PROFARMA01-002_Ata-de-Aceite-Final.md</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D368" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1fb6iusuVg05dDsai8VJhfW4ZxA-qpnxZ/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>CR-PROFARMA01-001_Registro-de-Change-Requests.docx</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D369" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1XWRRoeJ6NnvjCG3S0hlyPyxnMfkf9vM7/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>CR-PROFARMA01-001_Registro-de-Change-Requests.md</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D370" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1kgckhl0v57S7-e70hCKJB6Eo8eW2gT1y/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>CTQ-PROFARMA01-001_Cenarios-de-Teste-Homologacao.docx</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D371" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ts70FWbIasG3sf9qDBSw8cXldJfRJ7bY/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>CTQ-PROFARMA01-001_Cenarios-de-Teste-Homologacao.md</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D372" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/16ZD1X77Pqc4pDhauwVkg0ioDD6nVFAmy/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>GCO-PROFARMA01-001_Registro-de-Gerencia-de-Configuracao.docx</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D373" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ld1PXP0yafu0eW7nUNXN0iRCm1P7cskc/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>GCO-PROFARMA01-001_Registro-de-Gerencia-de-Configuracao.md</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D374" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Sa_Vs1t1DTIcQX0MLGesk4T6YVBc-Rlk/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>GDE-PROFARMA01-001_Registro-de-Analise-de-Decisao.docx</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D375" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1wU_hxVhwrX-XUT1OQmEKxw80Mz0T5Rat/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>GDE-PROFARMA01-001_Registro-de-Analise-de-Decisao.md</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D376" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Fn6AEOrG_9rfsHc5rb-55Ba6AJXD-oqJ/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>GEST-PROFARMA01_Planilha-de-Gestao-do-Projeto.xlsx</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>xlsx</t>
-        </is>
-      </c>
-      <c r="D377" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/12SEFOVCAA1jVQRgM1c1RDR_CL3KaW32_/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>GQA-PROFARMA01-001_Registro-de-GQA.docx</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D378" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1hefq-kmdiYVOIvc0RoWHcSVQDBbL8Fq4/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>GQA-PROFARMA01-001_Registro-de-GQA.md</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D379" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ejtinVxoovxalMob3EU5LzijUCO0eo0V/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>ITP-PROFARMA01-001_Estrategia-de-Integracao.docx</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D380" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1DKKcqAZK78dkV2UIRRSXHtELjnxdw4aj/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>ITP-PROFARMA01-001_Estrategia-de-Integracao.md</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D381" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1hbMF9jFqMlJF3soSLRNy6LTp11g408Pn/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>LI-PROFARMA01-001_Licoes-Aprendidas.docx</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D382" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1NMayhfr_e6Li-R0NEGoST5QATJgifMc7/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>LI-PROFARMA01-001_Licoes-Aprendidas.md</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D383" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1iG2LYXClAx5nZ4zuk_S74DvZ1Q0LMHQ_/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>MED-PROFARMA01-001_Registro-de-Medicao.docx</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D384" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1nmbiWfvYMAAa7Y5pO14VxaZgxEPQuKOn/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>MED-PROFARMA01-001_Registro-de-Medicao.md</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D385" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1QDJ9-TSu_9GDbyhDRN6ywUgTeuAJ4QiH/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>PCP-PROFARMA01-001_Documento-de-Design.docx</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D386" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1t0fD748MR_EBRMHsgQzVGLKRnJ4Zq7__/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>PCP-PROFARMA01-001_Documento-de-Design.md</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D387" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1xz3lOI7tT1T9MaUytvzP3u2djp_-VSll/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>PLA-PROFARMA01-001_Plano-de-Projeto.docx</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D388" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/189Kp-xA8BJ3SsO9NhxDyDOUtX3dADifK/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>PLA-PROFARMA01-001_Plano-de-Projeto.md</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D389" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1UiPpMmAewO-ZAlFVC7Wgy3mUVTqk8KTG/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>RAC-PROFARMA01-001_Relatorio-de-Acompanhamento.docx</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D390" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1HjCxyFwvC7Fxp4OXwxjqqL7OyYlSfI9x/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>RAC-PROFARMA01-001_Relatorio-de-Acompanhamento.md</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D391" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1WKuyyC2s6ukY52aDxjmqfD6w2L5l_GRn/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>RASTR-PROFARMA01-001_Matriz-de-Rastreabilidade.docx</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D392" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ep0JvVMNhdLVRwWXVMIyfLxurd7ReAyI/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>RASTR-PROFARMA01-001_Matriz-de-Rastreabilidade.md</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D393" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1TChhbQ3yhiT2-Q5VN8cbxtuO2C65slPV/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>REL-VV-PROFARMA01-001_Relatorio-de-Execucao-de-Testes.docx</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D394" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1KF8zj0lufb0VPg6riJwGhibojJJIopHM/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>REL-VV-PROFARMA01-001_Relatorio-de-Execucao-de-Testes.md</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D395" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1-GrCtAPUfBcRFM4tMJfIEAO-o_cvFqOt/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>REQ-PROFARMA01-001_Documento-de-Requisitos.docx</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D396" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/17OE2PW4XkEy3OnJlSb6rtsHHh9ouTFJE/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>REQ-PROFARMA01-001_Documento-de-Requisitos.md</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D397" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1T0waKCjFQoXryc5x292hRhOggesgV4Pt/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>REV-PROFARMA01-001_Registro-de-Revisao-Tecnica.docx</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D398" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1dHd-EpgVX2Mg2Wo5Y_uxB8KFH4qphhxM/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>REV-PROFARMA01-001_Registro-de-Revisao-Tecnica.md</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D399" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1oPm581spQso7WLZsNUHItMYAVQGqD6Qq/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>TAE-PROFARMA01-001_Termo-de-Encerramento.docx</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D400" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1k_UZ_jWRVmpHA1Iiysa7vKvUwQ1T8QED/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>TAE-PROFARMA01-001_Termo-de-Encerramento.md</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D401" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1G8wrZkaa7n3kidURBXK6tUzzupMHpeyb/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>TAP-PROFARMA01-001_Termo-de-Abertura.docx</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D402" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/13BKbRnLmlBDMBkioH54vOpmicKqlei8W/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>TAP-PROFARMA01-001_Termo-de-Abertura.md</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D403" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1EViPFMzb6dgDVBr-wLeSrGXIJB25-2v2/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>VV-PROFARMA01-001_Plano-de-VV.docx</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D404" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/15tRkpsMad47tD4gPdlLKImY5ipIadjxw/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>VV-PROFARMA01-001_Plano-de-VV.md</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D405" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1pFat-uajlAcSBqyMC8Xr5TIDMOz5Yqa1/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>05_capacidade</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>MAPA-CAP-001_Mapa-de-Capacidade-dos-Processos.docx</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D406" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1YaGYkBQnoCkiO6AygwtZCQKSxZkMIRNU/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>05_capacidade</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>MAPA-CAP-001_Mapa-de-Capacidade-dos-Processos.md</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D407" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Cf81NchDsh8A185sbhMAt1NJTCks3snY/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>05_capacidade</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.docx</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>docx</t>
-        </is>
-      </c>
-      <c r="D408" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/16fsO_4U6QBJxV0HSWpFJsHX-XQ4HhLhT/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>05_capacidade</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.md</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="D409" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1NHV3d4WHuUhUcTOtjtGi-uB1yR3BC6mL/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>05_capacidade</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.xlsx</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>xlsx</t>
-        </is>
-      </c>
-      <c r="D410" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/14kYNYwEsp3nawnEA9t25kWyYey51aYlu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1i87bnTiddeMILoHq3CBlyZ-WzPS5meEW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D410"/>
+  <autoFilter ref="A1:D261"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -9716,155 +6434,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId259"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D399" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId409"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MAPA-DRIVE_Indice-de-Links.xlsx
+++ b/MAPA-DRIVE_Indice-de-Links.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mapa de Links Drive" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapa de Links Drive'!$A$1:$D$261</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapa de Links Drive'!$A$1:$D$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D261"/>
+  <dimension ref="A1:D267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CR-AASPAP01-001_Change-Request.docx</t>
+          <t>ATA-AASPAP01-002_Ata-de-Acompanhamento-Fase-1.docx</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1p94Xtd_QSXghPgdDQiaj9m8JoArrHree/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1o5hMgR4SdNrl2fakLB59tI0JOtZWxlwD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CR-AASPAP01-002_Change-Request.docx</t>
+          <t>ATA-AASPAP01-003_Ata-de-Acompanhamento-Fase-2.docx</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1e495VArI_U_3TMW7KQc0p3GfqUiAek4a/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1L5XOH48-U99-Y1mdKjuNV_UCY_bZCxJo/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GCO-AASPAP01-001_Registro-de-Configuracao.docx</t>
+          <t>ATA-AASPAP01-004_Ata-de-Acompanhamento-Fase-3.docx</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Rl6GXnN1H9mRl0V6bSYw9Pl_D-0THH_O/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1KTLJHZC0eTeQ429HoZqPT5SoF27e_aMw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GDE-AASPAP01-001_Registro-de-Analise-de-Decisao.docx</t>
+          <t>ATA-AASPAP01-005_Ata-de-Acompanhamento-Fase-4.docx</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1sDGfP0m6WdyKS4MYzHLLZNNQCyus0xJw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1U8rsYKXxRluVYXT1UNe3h5RlWmJGvS6-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3033,17 +3033,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GEST-AASPAP01_Planilha-de-Gestao-do-Projeto.xlsx</t>
+          <t>CR-AASPAP01-001_Change-Request.docx</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZB2yOn7Pt1eviyaL1-XMCaiamiCql6gz/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1p94Xtd_QSXghPgdDQiaj9m8JoArrHree/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GQA-AASPAP01-001_Registro-de-GQA.docx</t>
+          <t>CR-AASPAP01-002_Change-Request.docx</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19WE56UNWv-aVGiPL24PzStXvX1NuplXF/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1e495VArI_U_3TMW7KQc0p3GfqUiAek4a/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ITP-AASPAP01-001_Estrategia-de-Integracao.docx</t>
+          <t>GCO-AASPAP01-001_Registro-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cSlw8Kqi3fPboNG2KDMoRuWYLii5s1Qm/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Rl6GXnN1H9mRl0V6bSYw9Pl_D-0THH_O/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MED-AASPAP01-001_Registro-de-Medicao.docx</t>
+          <t>GDE-AASPAP01-001_Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17jDdprZJdXPr-muQAYnQNXoMNU1VOSAV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1sDGfP0m6WdyKS4MYzHLLZNNQCyus0xJw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3121,17 +3121,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PCP-AASPAP01-001_Documento-de-Design.docx</t>
+          <t>GEST-AASPAP01_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MkxkyhMa5O4d9ee1JVYHNZV59BxiHU3m/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZB2yOn7Pt1eviyaL1-XMCaiamiCql6gz/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PLA-AASPAP01-001_Plano-de-Projeto.docx</t>
+          <t>GQA-AASPAP01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D7tchEQKaqeZMZ2vNNa0wgnXevI-Br8H/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19WE56UNWv-aVGiPL24PzStXvX1NuplXF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RAC-AASPAP01-001_Relatorio-de-Acompanhamento.docx</t>
+          <t>ITP-AASPAP01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/155bBfagbpaZdKxRSqXQzkmZSQkmCHNt0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1cSlw8Kqi3fPboNG2KDMoRuWYLii5s1Qm/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RASTR-AASPAP01-001_Matriz-de-Rastreabilidade.docx</t>
+          <t>MED-AASPAP01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nqVdGrDD5CJ_3zPB3IehiBEhuDKSxZlS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17jDdprZJdXPr-muQAYnQNXoMNU1VOSAV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>REL-VV-AASPAP01-001_Relatorio-de-Execucao-de-Testes.docx</t>
+          <t>MQ-AASPAP01-001_Definicao-de-Metas-de-Qualidade.docx</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TzIWFlAfEpqwWO0JIF3DACKPzPgC2sPV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1xsxRl8hMbuDqZIcyrSTe9niJJuYLldRn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>REQ-AASPAP01-001_Documento-de-Requisitos.docx</t>
+          <t>PCP-AASPAP01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1kV_N6w7TU5Cwe5SYWL3tcptlcr4oazYt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1MkxkyhMa5O4d9ee1JVYHNZV59BxiHU3m/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>REV-AASPAP01-001_Registro-de-Revisao-por-Pares.docx</t>
+          <t>PLA-AASPAP01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1b2XcTr_rrP1ntnEzllbB2gHNdFaEaLsQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D7tchEQKaqeZMZ2vNNa0wgnXevI-Br8H/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TAP-AASPAP01-001_Termo-de-Abertura.docx</t>
+          <t>RAC-AASPAP01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1vj9arb9bNdy4z2DLV7U8sEbBp4GuIMHw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/155bBfagbpaZdKxRSqXQzkmZSQkmCHNt0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VV-AASPAP01-001_Plano-de-VV.docx</t>
+          <t>RASTR-AASPAP01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3307,139 +3307,139 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11Vx-bMcQfovROo3RwVY7-dQClEVcFp1e/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nqVdGrDD5CJ_3zPB3IehiBEhuDKSxZlS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>andamentos_ApisParceiras.jpg</t>
+          <t>REL-VV-AASPAP01-001_Relatorio-de-Execucao-de-Testes.docx</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jpg</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1di53G9P1RLs2VtusPoTRJay3fOG7c1L2/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TzIWFlAfEpqwWO0JIF3DACKPzPgC2sPV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>andamentos_arquitetura.svg</t>
+          <t>REQ-AASPAP01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hwULBFas2YSOqC3BIi0dVbGelx-U-Mp0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1kV_N6w7TU5Cwe5SYWL3tcptlcr4oazYt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>andamentos_historicoPreservado.jpeg</t>
+          <t>REV-AASPAP01-001_Registro-de-Revisao-por-Pares.docx</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>jpeg</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Nx8OtLH1th3lVs3pRHd1yJjZ-l5jsR4s/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1b2XcTr_rrP1ntnEzllbB2gHNdFaEaLsQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>andamentos_historicoPreservado1.jpg</t>
+          <t>REV-AASPAP01-002_Registro-de-Revisao-por-Pares-por-Entrega.docx</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jpg</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1zXIyrAtYHinI0oETDvC-PQ0sgF4Z6Fjy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ijB8cHIMAWWH29ZHGjN2ByonolS_z-XE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>andamentos_historicoPreservado2.jpg</t>
+          <t>TAP-AASPAP01-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jpg</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1l8sW0voE8k-y6ew1dTbd5aePqlr5UffM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1vj9arb9bNdy4z2DLV7U8sEbBp4GuIMHw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
+          <t>04_registros/AASP_Andamento-Processuais</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>andamentos_retry_webhook.jpeg</t>
+          <t>VV-AASPAP01-001_Plano-de-VV.docx</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>jpeg</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15lXDLmdWW620DS2qE9-qwIEzvAgmpGlW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11Vx-bMcQfovROo3RwVY7-dQClEVcFp1e/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3451,17 +3451,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>devops_andamentos_branches.png</t>
+          <t>andamentos_ApisParceiras.jpg</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>jpg</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YaLDEwp8l6FoyFTaMTEWMmeLqbT6gfnx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1di53G9P1RLs2VtusPoTRJay3fOG7c1L2/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3473,17 +3473,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>devops_andamentos_commits.png</t>
+          <t>andamentos_arquitetura.svg</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fkX4bzm8iFGVFOtMtIK4rEtjZhF1bomY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hwULBFas2YSOqC3BIi0dVbGelx-U-Mp0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3495,17 +3495,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>devops_andamentos_estrutura.png</t>
+          <t>andamentos_historicoPreservado.jpeg</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>jpeg</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1w_Hj4o0YyA0oYRSE1_5d1VE67_JisEFY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Nx8OtLH1th3lVs3pRHd1yJjZ-l5jsR4s/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3517,17 +3517,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>devops_andamentos_pipeline_ci.png</t>
+          <t>andamentos_historicoPreservado1.jpg</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>jpg</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1p1VezDp1C0XYPSOjQk978cQmrvGVrTWo/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1zXIyrAtYHinI0oETDvC-PQ0sgF4Z6Fjy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3539,17 +3539,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>devops_andamentos_pipeline_cicd.png</t>
+          <t>andamentos_historicoPreservado2.jpg</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>jpg</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Zf1k0e36NnyOxq-zv6Rrz22N5tvM8x49/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1l8sW0voE8k-y6ew1dTbd5aePqlr5UffM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3561,17 +3561,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>devops_andamentos_pr_detail_1.png</t>
+          <t>andamentos_retry_webhook.jpeg</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>jpeg</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FSv2kmZbKNXOk5tjctohUFqHtn-BZ9bu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15lXDLmdWW620DS2qE9-qwIEzvAgmpGlW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>devops_andamentos_pr_detail_2.png</t>
+          <t>devops_andamentos_branches.png</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1oBhgj_wDBy_Ap5QoTy-HRRu7a62wsa6S/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YaLDEwp8l6FoyFTaMTEWMmeLqbT6gfnx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>devops_andamentos_prs.png</t>
+          <t>devops_andamentos_commits.png</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14Se4mDLpHgV5EjT8w7kd1TypMmOEmzMU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fkX4bzm8iFGVFOtMtIK4rEtjZhF1bomY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>devops_andamentos_tags.png</t>
+          <t>devops_andamentos_estrutura.png</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fGjCYwKyDczuhAJPkpaxCMdrrCi7BRc4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1w_Hj4o0YyA0oYRSE1_5d1VE67_JisEFY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>estrutura_andamentosProcessuais.png</t>
+          <t>devops_andamentos_pipeline_ci.png</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3659,139 +3659,139 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1BQ_7ZiscsMUDn84a_vBXcghhchm29hLs/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1p1VezDp1C0XYPSOjQk978cQmrvGVrTWo/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>00_INDICEAASPCNJ01_MapadeRegistros.docx</t>
+          <t>devops_andamentos_pipeline_cicd.png</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1kf3EdS_AsVImdD6P_03zCt-OF7_UHj6N/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Zf1k0e36NnyOxq-zv6Rrz22N5tvM8x49/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ADAP-AASPCNJ01-001_Registro-de-Adaptacao.docx</t>
+          <t>devops_andamentos_pr_detail_1.png</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14GFOTJj6jxDsV62h60zCqIgxnRW-DbWW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1FSv2kmZbKNXOk5tjctohUFqHtn-BZ9bu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ATA-AASPCNJ01-001_Ata-Alinhamento-Fluxo-CNJ.docx</t>
+          <t>devops_andamentos_pr_detail_2.png</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12sOcC6FDaP-3OdoM1_duAMNNcbgYsQvb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1oBhgj_wDBy_Ap5QoTy-HRRu7a62wsa6S/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CAP-AASPCNJ01-001_Registro-de-Capacitacao-da-Equipe.docx</t>
+          <t>devops_andamentos_prs.png</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11db2exVuX-huVhgL8azaDzByfMFQv_pb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14Se4mDLpHgV5EjT8w7kd1TypMmOEmzMU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CR-AASPCNJ01-001_Change-Request.docx</t>
+          <t>devops_andamentos_tags.png</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1J3XOn56R7ruWa8vhPAnVzI7r092DFLY-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fGjCYwKyDczuhAJPkpaxCMdrrCi7BRc4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>04_registros/AASP_CNJ</t>
+          <t>04_registros/AASP_Andamento-Processuais/evidencias</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>GCO-AASPCNJ01-001_Registro-de-Configuracao.docx</t>
+          <t>estrutura_andamentosProcessuais.png</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>png</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1IJozbK4BobNpyION4zPWa_s2auynxhv9/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1BQ_7ZiscsMUDn84a_vBXcghhchm29hLs/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GDE-AASPCNJ01-001_Registro-de-Analise-de-Decisao.docx</t>
+          <t>00_INDICEAASPCNJ01_MapadeRegistros.docx</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1EpobYWmsjCftVdxosshioK0mCuXVFlEq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1kf3EdS_AsVImdD6P_03zCt-OF7_UHj6N/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3825,17 +3825,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GEST-AASPCNJ01-001_Planilha-de-Gestao-do-Projeto.xlsx</t>
+          <t>ADAP-AASPCNJ01-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Vdng-5mBCjlXpajdZ6ScLD67c8e85qob/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14GFOTJj6jxDsV62h60zCqIgxnRW-DbWW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>GQA-AASPCNJ01-001_Registro-de-GQA.docx</t>
+          <t>ATA-AASPCNJ01-001_Ata-Alinhamento-Fluxo-CNJ.docx</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1AI6TXKQ5f6Oh5g6VmFgzTmXNQHEtLOlh/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/12sOcC6FDaP-3OdoM1_duAMNNcbgYsQvb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ITP-AASPCNJ01-001_Estrategia-de-Integracao.docx</t>
+          <t>CAP-AASPCNJ01-001_Registro-de-Capacitacao-da-Equipe.docx</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tobpnNoEQf5LarNnPEJAEJnt5BAZGrtQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11db2exVuX-huVhgL8azaDzByfMFQv_pb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MED-AASPCNJ01-001_Registro-de-Medicao.docx</t>
+          <t>CR-AASPCNJ01-001_Change-Request.docx</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ePiJ3ONIXZf2gN00FzXuyUCIXdrpezsx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1J3XOn56R7ruWa8vhPAnVzI7r092DFLY-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PCP-AASPCNJ01-001_Documento-de-Design.docx</t>
+          <t>GCO-AASPCNJ01-001_Registro-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ywDtDrM3zHptY2XfL6ut22ra3MEbuLTe/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1IJozbK4BobNpyION4zPWa_s2auynxhv9/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PLA-AASPCNJ01-001_Plano-de-Projeto.docx</t>
+          <t>GDE-AASPCNJ01-001_Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1y9zo8Fx1AewE2z9GVdmhsecKySyDoSf6/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1EpobYWmsjCftVdxosshioK0mCuXVFlEq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3957,17 +3957,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>RAC-AASPCNJ01-001_Relatorio-de-Acompanhamento.docx</t>
+          <t>GEST-AASPCNJ01-001_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1G_0Odyq4HbI3nfCyDh7-zZoXDgu_BiON/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Vdng-5mBCjlXpajdZ6ScLD67c8e85qob/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>RASTR-AASPCNJ01-001_Matriz-de-Rastreabilidade.docx</t>
+          <t>GQA-AASPCNJ01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1lfPyboZZ3hd-8g3IzjQRQciVYXCztgZw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1AI6TXKQ5f6Oh5g6VmFgzTmXNQHEtLOlh/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>REL-VV-AASPCNJ01-001_Relatorio-de-Execucao-de-Testes.docx</t>
+          <t>ITP-AASPCNJ01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1whC8gTS2Mz1CW7QajDlOMvfXNlxt5AP6/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tobpnNoEQf5LarNnPEJAEJnt5BAZGrtQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>REQ-AASPCNJ01-001_Documento-de-Requisitos.docx</t>
+          <t>MED-AASPCNJ01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1GDwHhtK1Nc-2AptWo8HIryVHeOF8hzj5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ePiJ3ONIXZf2gN00FzXuyUCIXdrpezsx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>REV-AASPCNJ01-001_Registro-de-Revisao-por-Pares.docx</t>
+          <t>PCP-AASPCNJ01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1PfM9kKAjFJofhtJn5xqgicqG-0-v3mA-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ywDtDrM3zHptY2XfL6ut22ra3MEbuLTe/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TAP-AASPCNJ01-001_Termo-de-Abertura.docx</t>
+          <t>PLA-AASPCNJ01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hKBUW2dTTfmd8PEs36tEuIQjsKjPAuRF/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1y9zo8Fx1AewE2z9GVdmhsecKySyDoSf6/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>VV-AASPCNJ01-001_Plano-de-VV.docx</t>
+          <t>RAC-AASPCNJ01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4099,19 +4099,19 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/199h316ZoZ43k7W_rnPpNq6GTBr502zuu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1G_0Odyq4HbI3nfCyDh7-zZoXDgu_BiON/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.docx</t>
+          <t>RASTR-AASPCNJ01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4121,19 +4121,19 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NaEJlUDHw0FE6fgH28gpifHft7ZLxUyL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1lfPyboZZ3hd-8g3IzjQRQciVYXCztgZw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.docx</t>
+          <t>REL-VV-AASPCNJ01-001_Relatorio-de-Execucao-de-Testes.docx</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4143,19 +4143,19 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LNzyoQkTM7oLgWtSCPY6VxNqt4JS_MzM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1whC8gTS2Mz1CW7QajDlOMvfXNlxt5AP6/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-001_Ata-de-Kickoff.docx</t>
+          <t>REQ-AASPCNJ01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4165,19 +4165,19 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pjAXblbrxR8Y6p5eq2BDYRBpiYlK3Ag_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1GDwHhtK1Nc-2AptWo8HIryVHeOF8hzj5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.docx</t>
+          <t>REV-AASPCNJ01-001_Registro-de-Revisao-por-Pares.docx</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4187,19 +4187,19 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cypxWHL-NU9CPnLV47N-bKnP0QrSIB17/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1PfM9kKAjFJofhtJn5xqgicqG-0-v3mA-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.docx</t>
+          <t>TAP-AASPCNJ01-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4209,19 +4209,19 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1m0odZUeHy212r9AQwyZ_sfwXzznT4oqJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hKBUW2dTTfmd8PEs36tEuIQjsKjPAuRF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/AASP_CNJ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.docx</t>
+          <t>VV-AASPCNJ01-001_Plano-de-VV.docx</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10Qo6yB8nqAQmzacMbuLZaVv1ZaX178Lt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/199h316ZoZ43k7W_rnPpNq6GTBr502zuu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.docx</t>
+          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1VmGwsZK4GLu_zpzmrHnD2XOChsiR1GZr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NaEJlUDHw0FE6fgH28gpifHft7ZLxUyL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.docx</t>
+          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ujgsYTHnAVE_J60APn-OqGSRaCTbfPHf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LNzyoQkTM7oLgWtSCPY6VxNqt4JS_MzM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.docx</t>
+          <t>ATA-FRUKI01-001_Ata-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bNAl7ljD0PhTyZEb-2ngdIbBzCpvNY2q/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pjAXblbrxR8Y6p5eq2BDYRBpiYlK3Ag_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ATAFRUKI01008_AtaKickoffPacoteFinal24.docx</t>
+          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.docx</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11alVpwlnsPjgd1_PO4OzMBXeJLRz6PXi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1cypxWHL-NU9CPnLV47N-bKnP0QrSIB17/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4331,17 +4331,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>AnaliseDecisao_FTFRUKI_TIMEWARE.xlsx</t>
+          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.docx</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19sYcZ40SHiEe7qUV7jau-3fruYrAzjWp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1m0odZUeHy212r9AQwyZ_sfwXzznT4oqJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.docx</t>
+          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.docx</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1z2TIuyQQTiU7fOKmK0kQfziTtE8NqiLc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/10Qo6yB8nqAQmzacMbuLZaVv1ZaX178Lt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>GCO-FRUKI01-001_Registro-de-Configuracao.docx</t>
+          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.docx</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fMcui7ebx_4af41JtRltlCCJzDWkd1eA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1VmGwsZK4GLu_zpzmrHnD2XOChsiR1GZr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GDE-FRUKI01-001_Registro-de-Decisao.docx</t>
+          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.docx</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1h8FKsNP59PnO8tzm2WEJ_vgsZYRSmjwX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ujgsYTHnAVE_J60APn-OqGSRaCTbfPHf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4419,17 +4419,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>GEST-FRUKI01-001_Planilha-de-Gestao-do-Projeto.xlsx</t>
+          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.docx</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RsktvVNbrH1f-RmcV3_AmIu3uJt9Q7sH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bNAl7ljD0PhTyZEb-2ngdIbBzCpvNY2q/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>GQA-FRUKI01-001_Registro-de-GQA.docx</t>
+          <t>ATAFRUKI01008_AtaKickoffPacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jmdev8ggRDsbM_CrkMQY_oKaImvKG4vM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11alVpwlnsPjgd1_PO4OzMBXeJLRz6PXi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4463,17 +4463,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.docx</t>
+          <t>AnaliseDecisao_FTFRUKI_TIMEWARE.xlsx</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19YCw05XWIRh-NaI5GWf1c-MF6m5AhIra/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19sYcZ40SHiEe7qUV7jau-3fruYrAzjWp/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.docx</t>
+          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.docx</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1A-6S0ZZmHteTzIjSNP46H2OJYgeI-Gc7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1z2TIuyQQTiU7fOKmK0kQfziTtE8NqiLc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LI-FRUKI01-001_Licoes-Aprendidas.docx</t>
+          <t>GCO-FRUKI01-001_Registro-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pXvWCErdbUdvvAcXV93935DeGW6bJ7xL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fMcui7ebx_4af41JtRltlCCJzDWkd1eA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MED-FRUKI01-001_Registro-de-Medicao.docx</t>
+          <t>GDE-FRUKI01-001_Registro-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D6gCK_SBP31WdmYGToQH2iCZV1RdzhWI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1h8FKsNP59PnO8tzm2WEJ_vgsZYRSmjwX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4551,17 +4551,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PCP-FRUKI01-001_Documento-de-Design.docx</t>
+          <t>GEST-FRUKI01-001_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ff6Ha1FH1T1XAJGnmdy2QvkrqXxCUg2s/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RsktvVNbrH1f-RmcV3_AmIu3uJt9Q7sH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.docx</t>
+          <t>GQA-FRUKI01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17KodAvypysQkbqocfQIrlE2q1dfRIUnY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jmdev8ggRDsbM_CrkMQY_oKaImvKG4vM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PLA-FRUKI01-001_Plano-de-Projeto.docx</t>
+          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1WEPaZNg7rxj29B48l_scz7x7CyLlvoSf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19YCw05XWIRh-NaI5GWf1c-MF6m5AhIra/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.docx</t>
+          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1d0l6IhtfbI9hE0UYxQm6nVq9grpjKnpn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1A-6S0ZZmHteTzIjSNP46H2OJYgeI-Gc7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.docx</t>
+          <t>LI-FRUKI01-001_Licoes-Aprendidas.docx</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_C3hZUp-7-2ldAa2BmIfZ3tMfa9WX0bd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pXvWCErdbUdvvAcXV93935DeGW6bJ7xL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.docx</t>
+          <t>MED-FRUKI01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SokajsndvgCtPAX7FyUpNp9mIDxQrVQf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D6gCK_SBP31WdmYGToQH2iCZV1RdzhWI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.docx</t>
+          <t>PCP-FRUKI01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1S4nR_PkZnGQrm6ppWv47ftgH2ptyG9xJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ff6Ha1FH1T1XAJGnmdy2QvkrqXxCUg2s/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>REQ-FRUKI01-001_Documento-de-Requisitos.docx</t>
+          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1mCQ9GroaEFEjulblg31P0Kdknw95w8LJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17KodAvypysQkbqocfQIrlE2q1dfRIUnY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.docx</t>
+          <t>PLA-FRUKI01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1GexOXykQE4rnKFPmeW1kVQac18vsnlnQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1WEPaZNg7rxj29B48l_scz7x7CyLlvoSf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TAE-FRUKI01-001_Termo-de-Encerramento.docx</t>
+          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JNvLtWIaqno7WXqzPfQwcK1bRE3UjCRv/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1d0l6IhtfbI9hE0UYxQm6nVq9grpjKnpn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.docx</t>
+          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D3T0RHrOPhOq08Edxc1fWW-cZ1uR-e2n/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_C3hZUp-7-2ldAa2BmIfZ3tMfa9WX0bd/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>TAP-FRUKI01-001_Termo-de-Abertura.docx</t>
+          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ehO_9gQoPrLS-Ykhxfnnsrn9KZ9o8zdH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SokajsndvgCtPAX7FyUpNp9mIDxQrVQf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.docx</t>
+          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UUmn_lYKBv8eG5UZBaLipFbSMdnYTxgU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1S4nR_PkZnGQrm6ppWv47ftgH2ptyG9xJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>VV-FRUKI01-001_Plano-VeV.docx</t>
+          <t>REQ-FRUKI01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1yCFY98oM8rlf44HUIeERib4_7jtYsKeU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1mCQ9GroaEFEjulblg31P0Kdknw95w8LJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.docx</t>
+          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4869,19 +4869,19 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1d_okleyBKoPtPW2zEy7300KiXoWL62oj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1GexOXykQE4rnKFPmeW1kVQac18vsnlnQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ADAP-GASMIG02-001_Registro-de-Adaptacao.docx</t>
+          <t>TAE-FRUKI01-001_Termo-de-Encerramento.docx</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4891,19 +4891,19 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uDnjyU3hDOdzbVZPUFA-1PGqXCsuDeS7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JNvLtWIaqno7WXqzPfQwcK1bRE3UjCRv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ADAP-GASMIG02-002_Registro-de-Adaptacao-OS002.docx</t>
+          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4913,19 +4913,19 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1oQshhvn5DIq1DoB3rybc8jEbP_OdEnfn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D3T0RHrOPhOq08Edxc1fWW-cZ1uR-e2n/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ATA-GASMIG02-001_Ata-de-Kickoff.docx</t>
+          <t>TAP-FRUKI01-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4935,19 +4935,19 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1XcstqfQTQC0cm8wZgfc9oLgjSknU6Ueq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ehO_9gQoPrLS-Ykhxfnnsrn9KZ9o8zdH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ATA-GASMIG02-002_Ata-de-Aceite-OS001.docx</t>
+          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4957,19 +4957,19 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CcRbEbIcDWeHO7sOznH_FcuK-uVVusM0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1UUmn_lYKBv8eG5UZBaLipFbSMdnYTxgU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ATA-GASMIG02-003_Apresentacao-Entrega-OS002.docx</t>
+          <t>VV-FRUKI01-001_Plano-VeV.docx</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4979,29 +4979,29 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YCW3PFHS2p1bh8O6VWyZ8y2NFoG6ZWFN/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1yCFY98oM8rlf44HUIeERib4_7jtYsKeU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>AnaliseDecisao_FTGASMIG_TIMEWARE.xlsx</t>
+          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1u5oCqJrnQuaPBUMqTNQvaukwxqZvsmQi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1d_okleyBKoPtPW2zEy7300KiXoWL62oj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>CAP-GASMIG02-001_Registro-de-Capacitacao-da-Equipe.docx</t>
+          <t>ADAP-GASMIG02-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ibleg7tRQDHfYp3ahRpAlbYjKetFDzzT/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1uDnjyU3hDOdzbVZPUFA-1PGqXCsuDeS7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>GCO-GASMIG02-001_Gerencia-de-Configuracao.docx</t>
+          <t>ADAP-GASMIG02-002_Registro-de-Adaptacao-OS002.docx</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1qpIzDVbsmVYkiXW9NNdciOuv5iovMNu4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1oQshhvn5DIq1DoB3rybc8jEbP_OdEnfn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>GDE-GASMIG02-001_Registro-de-Analise-de-Decisao.docx</t>
+          <t>ATA-GASMIG02-001_Ata-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1sqAtX-R1-EjASMtMCnp_fjiessTaSaQU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1XcstqfQTQC0cm8wZgfc9oLgjSknU6Ueq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5079,17 +5079,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>GEST-GASMIG02_Planilha-de-Gestao-do-Projeto.xlsx</t>
+          <t>ATA-GASMIG02-002_Ata-de-Aceite-OS001.docx</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1r_dSFP9AmEnj79FkmqU80OkuYWnwzfZS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CcRbEbIcDWeHO7sOznH_FcuK-uVVusM0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>GQA-GASMIG02-001_Registro-de-GQA.docx</t>
+          <t>ATA-GASMIG02-003_Apresentacao-Entrega-OS002.docx</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1V-T1g_9AKu9TLFPROMR0fA1gkyx180a-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YCW3PFHS2p1bh8O6VWyZ8y2NFoG6ZWFN/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5123,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ITP-GASMIG02-002_Estrategia-de-Integracao-OS002.docx</t>
+          <t>AnaliseDecisao_FTGASMIG_TIMEWARE.xlsx</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JIAbQHVpTSO3V0AKGnWyVwEs6zuTWX7R/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1u5oCqJrnQuaPBUMqTNQvaukwxqZvsmQi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>LI-GASMIG02-001_Licoes-Aprendidas.docx</t>
+          <t>CAP-GASMIG02-001_Registro-de-Capacitacao-da-Equipe.docx</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ra9yyJuVYa2tmQW0DKwbJgannxAI2W0E/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ibleg7tRQDHfYp3ahRpAlbYjKetFDzzT/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MED-GASMIG02-001_Registro-de-Medicao.docx</t>
+          <t>GCO-GASMIG02-001_Gerencia-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LtjN_WSjn_g1wQ_RRLe4Z4KP6Cnu-Ohx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1qpIzDVbsmVYkiXW9NNdciOuv5iovMNu4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PCP-GASMIG02-001_Documento-de-Design.docx</t>
+          <t>GDE-GASMIG02-001_Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YI-40O6IWGMB0C_R6ytpbxc2w1E7W4fF/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1sqAtX-R1-EjASMtMCnp_fjiessTaSaQU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5211,17 +5211,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PCP-GASMIG02-002_Documento-de-Design-OS002.docx</t>
+          <t>GEST-GASMIG02_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Q4M2R4uqiy81BP8L3HiQ_idRqmpMt8Cw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1r_dSFP9AmEnj79FkmqU80OkuYWnwzfZS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PLA-GASMIG02-001_Plano-de-Projeto.docx</t>
+          <t>GQA-GASMIG02-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZIwX-h0RDNJfhO5AXev2vqhYrGHOr2qf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1V-T1g_9AKu9TLFPROMR0fA1gkyx180a-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PLA-GASMIG02-002_Plano-de-Projeto-OS002.docx</t>
+          <t>ITP-GASMIG02-002_Estrategia-de-Integracao-OS002.docx</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jfUDk7bhCtOXUYDcBnpjOx8FARp2VqPH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JIAbQHVpTSO3V0AKGnWyVwEs6zuTWX7R/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>RAC-GASMIG02-001_Relatorio-de-Acompanhamento.docx</t>
+          <t>LI-GASMIG02-001_Licoes-Aprendidas.docx</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bAl8o8UPkTb1AHypGNvRxEJG8UYswpvS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ra9yyJuVYa2tmQW0DKwbJgannxAI2W0E/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>RASTR-GASMIG02-001_Matriz-de-Rastreabilidade.docx</t>
+          <t>MED-GASMIG02-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_delTbo-PEeRpuGGGagv5p2SOF-ZNRos/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LtjN_WSjn_g1wQ_RRLe4Z4KP6Cnu-Ohx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>RASTR-GASMIG02-002_Matriz-de-Rastreabilidade-OS002.docx</t>
+          <t>PCP-GASMIG02-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tfy9oNEOsThCKNb1YrvQq8Ll1jX9kYJO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YI-40O6IWGMB0C_R6ytpbxc2w1E7W4fF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>REQ-GASMIG02-001_Documento-de-Requisitos.docx</t>
+          <t>PCP-GASMIG02-002_Documento-de-Design-OS002.docx</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13duq0igfGKvJAHKh_sD9TN7WqTpuOfdn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Q4M2R4uqiy81BP8L3HiQ_idRqmpMt8Cw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>REQ-GASMIG02-002_Documento-de-Requisitos-OS002.docx</t>
+          <t>PLA-GASMIG02-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_yN7yHPBc9iKilAlxd4pxj52G1_WoCHP/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZIwX-h0RDNJfhO5AXev2vqhYrGHOr2qf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>REV-GASMIG02-001_Registro-de-Verificacao-Tecnica.docx</t>
+          <t>PLA-GASMIG02-002_Plano-de-Projeto-OS002.docx</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1biHfNjSf_g7hnUcjBATCG48aG7ARNvRL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jfUDk7bhCtOXUYDcBnpjOx8FARp2VqPH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>TAE-GASMIG02-001_Termo-de-Encerramento-OS001.docx</t>
+          <t>RAC-GASMIG02-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1mw7eJBj6HANyIYJ1MgxEnO59ML9sl5aa/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bAl8o8UPkTb1AHypGNvRxEJG8UYswpvS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>TAE-GASMIG02-002_Termo-de-Encerramento-OS002.docx</t>
+          <t>RASTR-GASMIG02-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1-zvT45vPsVTAwmcEzQVak8qKT4dnQWEr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_delTbo-PEeRpuGGGagv5p2SOF-ZNRos/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>TAP-GASMIG02-001_Termo-de-Abertura.docx</t>
+          <t>RASTR-GASMIG02-002_Matriz-de-Rastreabilidade-OS002.docx</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1WW3VNRafS44JkZiXK29Rm7bYI7NbP9rS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tfy9oNEOsThCKNb1YrvQq8Ll1jX9kYJO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>TAP-GASMIG02-002_Termo-de-Abertura-OS002.docx</t>
+          <t>REQ-GASMIG02-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cMUOhgzZzj6wwWIijFMDugRVZIl8aPvf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/13duq0igfGKvJAHKh_sD9TN7WqTpuOfdn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>VV-GASMIG02-001_Plano-de-VV.docx</t>
+          <t>REQ-GASMIG02-002_Documento-de-Requisitos-OS002.docx</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15t1yh5oMbpFZ47rREDx9kJPgS8oXyRmy/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_yN7yHPBc9iKilAlxd4pxj52G1_WoCHP/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>VV-GASMIG02-002_Plano-de-VV-OS002.docx</t>
+          <t>REV-GASMIG02-001_Registro-de-Verificacao-Tecnica.docx</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5529,19 +5529,19 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/18GgauiJykVy8AASSKtJcqkt2FR-6AuRv/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1biHfNjSf_g7hnUcjBATCG48aG7ARNvRL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>ADAP-PROFARMA01-001_Registro-de-Adaptacao.docx</t>
+          <t>TAE-GASMIG02-001_Termo-de-Encerramento-OS001.docx</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5551,19 +5551,19 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1aRgkciq4Ed3iPJgEbe1jJnpkXKlF4Tma/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1mw7eJBj6HANyIYJ1MgxEnO59ML9sl5aa/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ATA-PROFARMA01-001_Ata-de-Kickoff.docx</t>
+          <t>TAE-GASMIG02-002_Termo-de-Encerramento-OS002.docx</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5573,19 +5573,19 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uNkVDge5WAgwLTCcUFZmBLlqKog16nmG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-zvT45vPsVTAwmcEzQVak8qKT4dnQWEr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ATA-PROFARMA01-002_Ata-de-Aceite-Final.docx</t>
+          <t>TAP-GASMIG02-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5595,41 +5595,41 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1odIVE62I5L7iqqLFUCACbHt3w2HRB8yR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1WW3VNRafS44JkZiXK29Rm7bYI7NbP9rS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Analise-Decisao_PROFARMA_TIMEWARE.xlsx</t>
+          <t>TAP-GASMIG02-002_Termo-de-Abertura-OS002.docx</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1iS1LRiviBLZgmxymc7Hfq7szzjUGkHjK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1cMUOhgzZzj6wwWIijFMDugRVZIl8aPvf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>CR-PROFARMA01-001_Registro-de-Change-Requests.docx</t>
+          <t>VV-GASMIG02-001_Plano-de-VV.docx</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5639,19 +5639,19 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1XWRRoeJ6NnvjCG3S0hlyPyxnMfkf9vM7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15t1yh5oMbpFZ47rREDx9kJPgS8oXyRmy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+          <t>04_registros/FTGASMIG_Governanca-APIs/GASMIG02_Fundacao-Tecnologica</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>CTQ-PROFARMA01-001_Cenarios-de-Teste-Homologacao.docx</t>
+          <t>VV-GASMIG02-002_Plano-de-VV-OS002.docx</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ts70FWbIasG3sf9qDBSw8cXldJfRJ7bY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18GgauiJykVy8AASSKtJcqkt2FR-6AuRv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EV-AzureDevOps-PROFARMA01-001.docx</t>
+          <t>ADAP-PROFARMA01-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1K3LjcxoNE5lRsuUe0IIkCtwreoj3Bizv/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1aRgkciq4Ed3iPJgEbe1jJnpkXKlF4Tma/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EV-Jira-PROFARMA01-001.docx</t>
+          <t>ATA-PROFARMA01-001_Ata-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ftGwgagbTkMohz_ZpKcLT0Z1_cPq_4A9/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1uNkVDge5WAgwLTCcUFZmBLlqKog16nmG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EV-Swagger-PROFARMA01-001.docx</t>
+          <t>ATA-PROFARMA01-002_Ata-de-Aceite-Final.docx</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17hu5hEzQctuc6OaDun7ki1pn1f-fp7cL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1odIVE62I5L7iqqLFUCACbHt3w2HRB8yR/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5739,17 +5739,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>GCO-PROFARMA01-001_Registro-de-Gerencia-de-Configuracao.docx</t>
+          <t>Analise-Decisao_PROFARMA_TIMEWARE.xlsx</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ld1PXP0yafu0eW7nUNXN0iRCm1P7cskc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1iS1LRiviBLZgmxymc7Hfq7szzjUGkHjK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>GDE-PROFARMA01-001_Registro-de-Analise-de-Decisao.docx</t>
+          <t>CR-PROFARMA01-001_Registro-de-Change-Requests.docx</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1wU_hxVhwrX-XUT1OQmEKxw80Mz0T5Rat/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1XWRRoeJ6NnvjCG3S0hlyPyxnMfkf9vM7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5783,17 +5783,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>GEST-PROFARMA01_Planilha-de-Gestao-do-Projeto.xlsx</t>
+          <t>CTQ-PROFARMA01-001_Cenarios-de-Teste-Homologacao.docx</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12SEFOVCAA1jVQRgM1c1RDR_CL3KaW32_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ts70FWbIasG3sf9qDBSw8cXldJfRJ7bY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>GQA-PROFARMA01-001_Registro-de-GQA.docx</t>
+          <t>EV-AzureDevOps-PROFARMA01-001.docx</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hefq-kmdiYVOIvc0RoWHcSVQDBbL8Fq4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1K3LjcxoNE5lRsuUe0IIkCtwreoj3Bizv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ITP-PROFARMA01-001_Estrategia-de-Integracao.docx</t>
+          <t>EV-Jira-PROFARMA01-001.docx</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DKKcqAZK78dkV2UIRRSXHtELjnxdw4aj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ftGwgagbTkMohz_ZpKcLT0Z1_cPq_4A9/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>LI-PROFARMA01-001_Licoes-Aprendidas.docx</t>
+          <t>EV-Swagger-PROFARMA01-001.docx</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NMayhfr_e6Li-R0NEGoST5QATJgifMc7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17hu5hEzQctuc6OaDun7ki1pn1f-fp7cL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>MED-PROFARMA01-001_Registro-de-Medicao.docx</t>
+          <t>GCO-PROFARMA01-001_Registro-de-Gerencia-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nmbiWfvYMAAa7Y5pO14VxaZgxEPQuKOn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ld1PXP0yafu0eW7nUNXN0iRCm1P7cskc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PCP-PROFARMA01-001_Documento-de-Design.docx</t>
+          <t>GDE-PROFARMA01-001_Registro-de-Analise-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1t0fD748MR_EBRMHsgQzVGLKRnJ4Zq7__/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1wU_hxVhwrX-XUT1OQmEKxw80Mz0T5Rat/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5915,17 +5915,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PLA-PROFARMA01-001_Plano-de-Projeto.docx</t>
+          <t>GEST-PROFARMA01_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/189Kp-xA8BJ3SsO9NhxDyDOUtX3dADifK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/12SEFOVCAA1jVQRgM1c1RDR_CL3KaW32_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>RAC-PROFARMA01-001_Relatorio-de-Acompanhamento.docx</t>
+          <t>GQA-PROFARMA01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HjCxyFwvC7Fxp4OXwxjqqL7OyYlSfI9x/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hefq-kmdiYVOIvc0RoWHcSVQDBbL8Fq4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>RASTR-PROFARMA01-001_Matriz-de-Rastreabilidade.docx</t>
+          <t>ITP-PROFARMA01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ep0JvVMNhdLVRwWXVMIyfLxurd7ReAyI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1DKKcqAZK78dkV2UIRRSXHtELjnxdw4aj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>REL-VV-PROFARMA01-001_Relatorio-de-Execucao-de-Testes.docx</t>
+          <t>LI-PROFARMA01-001_Licoes-Aprendidas.docx</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1KF8zj0lufb0VPg6riJwGhibojJJIopHM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NMayhfr_e6Li-R0NEGoST5QATJgifMc7/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>REQ-PROFARMA01-001_Documento-de-Requisitos.docx</t>
+          <t>MED-PROFARMA01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17OE2PW4XkEy3OnJlSb6rtsHHh9ouTFJE/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nmbiWfvYMAAa7Y5pO14VxaZgxEPQuKOn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>REV-PROFARMA01-001_Registro-de-Revisao-Tecnica.docx</t>
+          <t>PCP-PROFARMA01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dHd-EpgVX2Mg2Wo5Y_uxB8KFH4qphhxM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1t0fD748MR_EBRMHsgQzVGLKRnJ4Zq7__/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>TAE-PROFARMA01-001_Termo-de-Encerramento.docx</t>
+          <t>PLA-PROFARMA01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1k_UZ_jWRVmpHA1Iiysa7vKvUwQ1T8QED/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/189Kp-xA8BJ3SsO9NhxDyDOUtX3dADifK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>TAP-PROFARMA01-001_Termo-de-Abertura.docx</t>
+          <t>RAC-PROFARMA01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/13BKbRnLmlBDMBkioH54vOpmicKqlei8W/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1HjCxyFwvC7Fxp4OXwxjqqL7OyYlSfI9x/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>VV-PROFARMA01-001_Plano-de-VV.docx</t>
+          <t>RASTR-PROFARMA01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6101,19 +6101,19 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15tRkpsMad47tD4gPdlLKImY5ipIadjxw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ep0JvVMNhdLVRwWXVMIyfLxurd7ReAyI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>05_capacidade</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>MAPA-CAP-001_Mapa-de-Capacidade-dos-Processos.docx</t>
+          <t>REL-VV-PROFARMA01-001_Relatorio-de-Execucao-de-Testes.docx</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6123,19 +6123,19 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17csazhVOlhhgaMN-DCmoQEUiJsfrN1Il/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1KF8zj0lufb0VPg6riJwGhibojJJIopHM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>05_capacidade</t>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.docx</t>
+          <t>REQ-PROFARMA01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6145,34 +6145,166 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1j98CQbhiUr74uV7VenwJcEhnLmLupxhe/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17OE2PW4XkEy3OnJlSb6rtsHHh9ouTFJE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>REV-PROFARMA01-001_Registro-de-Revisao-Tecnica.docx</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1dHd-EpgVX2Mg2Wo5Y_uxB8KFH4qphhxM/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>TAE-PROFARMA01-001_Termo-de-Encerramento.docx</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1k_UZ_jWRVmpHA1Iiysa7vKvUwQ1T8QED/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>TAP-PROFARMA01-001_Termo-de-Abertura.docx</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/13BKbRnLmlBDMBkioH54vOpmicKqlei8W/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>04_registros/PROFARMA_Cadastro-de-Clientes</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>VV-PROFARMA01-001_Plano-de-VV.docx</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/15tRkpsMad47tD4gPdlLKImY5ipIadjxw/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
           <t>05_capacidade</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>MAPA-CAP-001_Mapa-de-Capacidade-dos-Processos.docx</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/17csazhVOlhhgaMN-DCmoQEUiJsfrN1Il/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>05_capacidade</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.docx</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1j98CQbhiUr74uV7VenwJcEhnLmLupxhe/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>05_capacidade</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
         <is>
           <t>MAPA-ORG-001_Matriz-de-Papeis-e-Responsabilidades.xlsx</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C267" t="inlineStr">
         <is>
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1i87bnTiddeMILoHq3CBlyZ-WzPS5meEW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D261"/>
+  <autoFilter ref="A1:D267"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -6434,6 +6566,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId259"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId266"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MAPA-DRIVE_Indice-de-Links.xlsx
+++ b/MAPA-DRIVE_Indice-de-Links.xlsx
@@ -4238,770 +4238,770 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/00_Comum</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.docx</t>
+          <t>GCO-FRUKI01-001_Registro-de-Configuracao.md</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NaEJlUDHw0FE6fgH28gpifHft7ZLxUyL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1yZ7iuUvSlwsgPoGBWgXxDjKNTofdWRAu/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/00_Comum</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.docx</t>
+          <t>GDE-FRUKI01-001_Registro-de-Decisao.md</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LNzyoQkTM7oLgWtSCPY6VxNqt4JS_MzM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hcn4AishYVOXgTA-qq--wQXfa5rN2J7j/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/00_Comum</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-001_Ata-de-Kickoff.docx</t>
+          <t>GQA-FRUKI01-001_Registro-de-GQA.md</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pjAXblbrxR8Y6p5eq2BDYRBpiYlK3Ag_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Xhrg8NS3j_pN1Bv_z1Qo3009f_xVYYJx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/00_Comum</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.docx</t>
+          <t>LI-FRUKI01-001_Licoes-Aprendidas.md</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cypxWHL-NU9CPnLV47N-bKnP0QrSIB17/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1A_N6OJ8TlDnicQrSrnNfBOqLFzHl93cF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/00_Comum</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.docx</t>
+          <t>MED-FRUKI01-001_Registro-de-Medicao.md</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1m0odZUeHy212r9AQwyZ_sfwXzznT4oqJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1oQr_iKEzIYoU1ETYOAfRLqKmzOYWrE6P/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/00_Comum</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.docx</t>
+          <t>RAC-FRUKI01-002_Planilha-de-Gestao-do-Projeto.xlsx</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10Qo6yB8nqAQmzacMbuLZaVv1ZaX178Lt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZwQgdrMLk96Yo2EyAtPobbt2i_FyGhxe/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.docx</t>
+          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.md</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1VmGwsZK4GLu_zpzmrHnD2XOChsiR1GZr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1g-INZLVI4w9mctAzk6OGTBdLW39j5J-O/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.docx</t>
+          <t>ATA-FRUKI01-001_Ata-de-Kickoff.md</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ujgsYTHnAVE_J60APn-OqGSRaCTbfPHf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SIsT8G2rPxBsPHS_a34NVOkfIczIAbEO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.docx</t>
+          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.md</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bNAl7ljD0PhTyZEb-2ngdIbBzCpvNY2q/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JCWhoRHCOa43L1rL1y9xhz2bzFiioUnK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ATAFRUKI01008_AtaKickoffPacoteFinal24.docx</t>
+          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.md</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11alVpwlnsPjgd1_PO4OzMBXeJLRz6PXi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1i2TY8dz01qak1BldOVjMBL1BjH02Lnuv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>AnaliseDecisao_FTFRUKI_TIMEWARE.xlsx</t>
+          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.md</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19sYcZ40SHiEe7qUV7jau-3fruYrAzjWp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11y80hz07nL5InEITjRl2F_pOMiDhlHKf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.docx</t>
+          <t>PCP-FRUKI01-001_Documento-de-Design.md</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1z2TIuyQQTiU7fOKmK0kQfziTtE8NqiLc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Lv68QFqybPvcG03VHmdEaL6dnBac8lSg/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>GCO-FRUKI01-001_Registro-de-Configuracao.docx</t>
+          <t>PLA-FRUKI01-001_Plano-de-Projeto.md</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fMcui7ebx_4af41JtRltlCCJzDWkd1eA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nRlcB-Y-88Uwxc_7bC2AdBAF0kzWBaQv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>GDE-FRUKI01-001_Registro-de-Decisao.docx</t>
+          <t>RAC-FRUKI01-002_Relatorio-de-Acompanhamento-Pacote1.md</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1h8FKsNP59PnO8tzm2WEJ_vgsZYRSmjwX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1H6OwCNBXOpeXunhW1zRuov7QJ0ujUR2B/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>GEST-FRUKI01-001_Planilha-de-Gestao-do-Projeto.xlsx</t>
+          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.md</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RsktvVNbrH1f-RmcV3_AmIu3uJt9Q7sH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RlKVc6M0_sBlK9SoGVfJTxjGooTxQu5-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>GQA-FRUKI01-001_Registro-de-GQA.docx</t>
+          <t>REQ-FRUKI01-001_Documento-de-Requisitos.md</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jmdev8ggRDsbM_CrkMQY_oKaImvKG4vM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jsj6iEmqHQeFIV_2mbnVLU2yGk_aZSrG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.docx</t>
+          <t>TAE-FRUKI01-001_Termo-de-Encerramento.md</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19YCw05XWIRh-NaI5GWf1c-MF6m5AhIra/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1eUVKAwQOSziboYim_LkDwdl-CRRKAkTE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.docx</t>
+          <t>TAP-FRUKI01-001_Termo-de-Abertura.md</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1A-6S0ZZmHteTzIjSNP46H2OJYgeI-Gc7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1lyGciE7qckPltxEtVNXcwC2BbewYy8n8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase1</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LI-FRUKI01-001_Licoes-Aprendidas.docx</t>
+          <t>VV-FRUKI01-001_Plano-VeV.md</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pXvWCErdbUdvvAcXV93935DeGW6bJ7xL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pa1Kv-CVgiDKp6O15HsH2wS1Sj6w6rl2/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MED-FRUKI01-001_Registro-de-Medicao.docx</t>
+          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D6gCK_SBP31WdmYGToQH2iCZV1RdzhWI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1gUQ1M-ZbVfLD2JDMMRy5dF-HwbZGqGT5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PCP-FRUKI01-001_Documento-de-Design.docx</t>
+          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.md</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ff6Ha1FH1T1XAJGnmdy2QvkrqXxCUg2s/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-aeqT0BAQN8q9aiSFDprKncgUGv35Tbw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.docx</t>
+          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.md</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17KodAvypysQkbqocfQIrlE2q1dfRIUnY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/16-FiineTnD7qs-K0efjHI8oveh067Pjb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PLA-FRUKI01-001_Plano-de-Projeto.docx</t>
+          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.md</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1WEPaZNg7rxj29B48l_scz7x7CyLlvoSf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pDeNymn8eEw1bg7neASDrMpjaHtKKF3m/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.docx</t>
+          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.md</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1d0l6IhtfbI9hE0UYxQm6nVq9grpjKnpn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tfZWSE26gCYWH3-cALxoyp66y9FEXp-R/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.docx</t>
+          <t>ATA-FRUKI01-008_Ata-Kickoff-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_C3hZUp-7-2ldAa2BmIfZ3tMfa9WX0bd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1W-eIgotNpxwMJEQ3NO9CEQwVqcRKvOrq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.docx</t>
+          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.md</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SokajsndvgCtPAX7FyUpNp9mIDxQrVQf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17fNk1TFIvfWh4C2O_pOGytMA5Gj9xgrr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.docx</t>
+          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1S4nR_PkZnGQrm6ppWv47ftgH2ptyG9xJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1b7z0ytGUrMuvUxixgK9g_YtzJOIAFlaD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>REQ-FRUKI01-001_Documento-de-Requisitos.docx</t>
+          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1mCQ9GroaEFEjulblg31P0Kdknw95w8LJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17pKjVVEK0WOH8TP4tQrYY-1SEOD87_gn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.docx</t>
+          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1GexOXykQE4rnKFPmeW1kVQac18vsnlnQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11HJg1b3_ko_YRr18_io0PeJKdqbBS6cz/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>TAE-FRUKI01-001_Termo-de-Encerramento.docx</t>
+          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.md</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JNvLtWIaqno7WXqzPfQwcK1bRE3UjCRv/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tJKc9cSokMjVl6ZUEGziBPortQ0w9vHs/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.docx</t>
+          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D3T0RHrOPhOq08Edxc1fWW-cZ1uR-e2n/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1r2v_XLLzm37ySMynrN3AyLOGj1IHdnoW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>TAP-FRUKI01-001_Termo-de-Abertura.docx</t>
+          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ehO_9gQoPrLS-Ykhxfnnsrn9KZ9o8zdH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Fb7MpfzPfNKM--4N94Tx49pUGvWBnKab/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.docx</t>
+          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UUmn_lYKBv8eG5UZBaLipFbSMdnYTxgU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1qGo80blY7kzlFuXtUUCrkV6K427xB6SK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>VV-FRUKI01-001_Plano-VeV.docx</t>
+          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1yCFY98oM8rlf44HUIeERib4_7jtYsKeU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ngjegtxERo_jJObFfcYsUfNPw9yuC9PV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas</t>
+          <t>04_registros/FTFRUKI_SuperApp-Forca-de-Vendas/Fase2</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.docx</t>
+          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.md</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>md</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1d_okleyBKoPtPW2zEy7300KiXoWL62oj/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1WcBf_hl4Unrs6FsG4AHhcJ-NuAoEG1s5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>

--- a/MAPA-DRIVE_Indice-de-Links.xlsx
+++ b/MAPA-DRIVE_Indice-de-Links.xlsx
@@ -4243,17 +4243,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GCO-FRUKI01-001_Registro-de-Configuracao.md</t>
+          <t>GCO-FRUKI01-001_Registro-de-Configuracao.docx</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1yZ7iuUvSlwsgPoGBWgXxDjKNTofdWRAu/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pNtMiuOiFIaHQPJgi6eVfUg5n09WLqBP/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4265,17 +4265,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GDE-FRUKI01-001_Registro-de-Decisao.md</t>
+          <t>GDE-FRUKI01-001_Registro-de-Decisao.docx</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hcn4AishYVOXgTA-qq--wQXfa5rN2J7j/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1zmsr5YyHjrNpwEp90By_W7S1GnElYmw8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4287,17 +4287,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>GQA-FRUKI01-001_Registro-de-GQA.md</t>
+          <t>GQA-FRUKI01-001_Registro-de-GQA.docx</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Xhrg8NS3j_pN1Bv_z1Qo3009f_xVYYJx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hmfL9793lOZ1GYNpydSIg3qi8_6Mw_Rg/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4309,17 +4309,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LI-FRUKI01-001_Licoes-Aprendidas.md</t>
+          <t>LI-FRUKI01-001_Licoes-Aprendidas.docx</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1A_N6OJ8TlDnicQrSrnNfBOqLFzHl93cF/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17Qt_1yhKepTzL_g9JFOPU5J1Q2UF-BCX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4331,17 +4331,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MED-FRUKI01-001_Registro-de-Medicao.md</t>
+          <t>MED-FRUKI01-001_Registro-de-Medicao.docx</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1oQr_iKEzIYoU1ETYOAfRLqKmzOYWrE6P/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14EdqCHT1X2JpRNN_NZ3C8Ews0ON8xu1P/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZwQgdrMLk96Yo2EyAtPobbt2i_FyGhxe/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17ieOzpbIyysqF4xnATVsvILE3L3juD4Z/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4375,17 +4375,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.md</t>
+          <t>ADAP-FRUKI01-001_Registro-de-Adaptacao.docx</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1g-INZLVI4w9mctAzk6OGTBdLW39j5J-O/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1efYcrr-1Tiw6JyKjakckma78t0SmY43G/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4397,17 +4397,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-001_Ata-de-Kickoff.md</t>
+          <t>ATA-FRUKI01-001_Ata-de-Kickoff.docx</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SIsT8G2rPxBsPHS_a34NVOkfIczIAbEO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Ry0TUfXQPFqDBUkeeUNOk5vb3pDwIlVS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4419,17 +4419,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.md</t>
+          <t>ATA-FRUKI01-002_Ata-Levantamento-Metas.docx</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JCWhoRHCOa43L1rL1y9xhz2bzFiioUnK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1PnWtrFi4hLIWraOqhBVWpbOkJXFUMI9O/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4441,17 +4441,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.md</t>
+          <t>ATA-FRUKI01-007_Ata-Piloto-Pacote1.docx</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1i2TY8dz01qak1BldOVjMBL1BjH02Lnuv/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19h2hAuaXqPLMEIRQXXPIepH4F7aGuJqz/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4463,17 +4463,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.md</t>
+          <t>ITP-FRUKI01-001_Estrategia-de-Integracao.docx</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11y80hz07nL5InEITjRl2F_pOMiDhlHKf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1vPddrPn96WUUiXuR-EYuaZqNwsD8kg4H/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4485,17 +4485,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PCP-FRUKI01-001_Documento-de-Design.md</t>
+          <t>PCP-FRUKI01-001_Documento-de-Design.docx</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Lv68QFqybPvcG03VHmdEaL6dnBac8lSg/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1DhU-ouU4se-N_zNSd5WL1VHcuWwv7abA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4507,17 +4507,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PLA-FRUKI01-001_Plano-de-Projeto.md</t>
+          <t>PLA-FRUKI01-001_Plano-de-Projeto.docx</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nRlcB-Y-88Uwxc_7bC2AdBAF0kzWBaQv/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18AHtQjHJ04e1unAbEuXyuSufSVAxy9np/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4529,17 +4529,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RAC-FRUKI01-002_Relatorio-de-Acompanhamento-Pacote1.md</t>
+          <t>RAC-FRUKI01-002_Relatorio-de-Acompanhamento-Pacote1.docx</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1H6OwCNBXOpeXunhW1zRuov7QJ0ujUR2B/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1387oUWKKn_H3kKKKjDprHWcfJcHeunJy/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4551,17 +4551,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.md</t>
+          <t>RASTR-FRUKI01-001_Matriz-de-Rastreabilidade.docx</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RlKVc6M0_sBlK9SoGVfJTxjGooTxQu5-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/10vzbMMnDEc6da_gk6WMvbc_SoIkjaVPr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4573,17 +4573,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>REQ-FRUKI01-001_Documento-de-Requisitos.md</t>
+          <t>REQ-FRUKI01-001_Documento-de-Requisitos.docx</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jsj6iEmqHQeFIV_2mbnVLU2yGk_aZSrG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17zmKJI3e67wnxKzzzhVPhCZ3IxXBIFWU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4595,17 +4595,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TAE-FRUKI01-001_Termo-de-Encerramento.md</t>
+          <t>TAE-FRUKI01-001_Termo-de-Encerramento.docx</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1eUVKAwQOSziboYim_LkDwdl-CRRKAkTE/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1eI5-xDVUYZm1JfdD7jFDTmfgShwVcK16/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TAP-FRUKI01-001_Termo-de-Abertura.md</t>
+          <t>TAP-FRUKI01-001_Termo-de-Abertura.docx</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1lyGciE7qckPltxEtVNXcwC2BbewYy8n8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hroxBim8Y34nc02GxAH8o551-e38E49o/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4639,17 +4639,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>VV-FRUKI01-001_Plano-VeV.md</t>
+          <t>VV-FRUKI01-001_Plano-VeV.docx</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pa1Kv-CVgiDKp6O15HsH2wS1Sj6w6rl2/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15zwR3REjPc7plvrG3q3zeJKrpJCFi-BX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4661,17 +4661,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.md</t>
+          <t>ADAP-FRUKI01-002_Registro-de-Adaptacao-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gUQ1M-ZbVfLD2JDMMRy5dF-HwbZGqGT5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1VMC6fRaDDblj024RkZaO_kRBPI5-AWb2/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4683,17 +4683,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.md</t>
+          <t>ATA-FRUKI01-003_Ata-de-Aceite-Final.docx</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1-aeqT0BAQN8q9aiSFDprKncgUGv35Tbw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1JsjKR7P6hEv9Atyfx_kxA95bQG3uvdgI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4705,17 +4705,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.md</t>
+          <t>ATA-FRUKI01-004_Ata-Validacao-Sprint1-NaoAlocados.docx</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16-FiineTnD7qs-K0efjHI8oveh067Pjb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-gn_pkcbdNRCSzLHi75m8fgkkw2ILrev/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4727,17 +4727,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.md</t>
+          <t>ATA-FRUKI01-005_Ata-Validacao-Sprint2-RegraDeOuro.docx</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pDeNymn8eEw1bg7neASDrMpjaHtKKF3m/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1gUsmWDj66IvWi1jdTBUwx1_jOV3qBMcr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4749,17 +4749,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.md</t>
+          <t>ATA-FRUKI01-006_Ata-Validacao-Sprint3-PDV.docx</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tfZWSE26gCYWH3-cALxoyp66y9FEXp-R/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ksGRCQp2uOce8XzQ6JUwXrY5Jm6gypth/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4771,17 +4771,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ATA-FRUKI01-008_Ata-Kickoff-PacoteFinal24.md</t>
+          <t>ATA-FRUKI01-008_Ata-Kickoff-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1W-eIgotNpxwMJEQ3NO9CEQwVqcRKvOrq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1AxV06s10xmWtcppFZdspU8YgwA0kK3zo/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4793,17 +4793,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.md</t>
+          <t>CR-FRUKI01-001_Solicitacao-de-Mudanca-RegraDeOuro.docx</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17fNk1TFIvfWh4C2O_pOGytMA5Gj9xgrr/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1lES6gbWkdIs_lGMYzw0Oinv_mhKMd9vv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4815,17 +4815,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.md</t>
+          <t>ITP-FRUKI01-002_Estrategia-de-Integracao-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1b7z0ytGUrMuvUxixgK9g_YtzJOIAFlaD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1x6oQSghPGUoW4ALmte-BAWOesdL7LOej/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4837,17 +4837,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.md</t>
+          <t>PCP-FRUKI01-002_Documento-de-Design-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17pKjVVEK0WOH8TP4tQrYY-1SEOD87_gn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/12JPCWQwCPOeAqhPQlD2RhqgWlhF7RCi_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4859,17 +4859,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.md</t>
+          <t>PLA-FRUKI01-002_Plano-de-Projeto-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11HJg1b3_ko_YRr18_io0PeJKdqbBS6cz/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1X7aqRJ1cFWaFFDY2-PIZOr0LZY3aYPUs/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4881,17 +4881,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.md</t>
+          <t>RAC-FRUKI01-001_Relatorio-de-Acompanhamento.docx</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tJKc9cSokMjVl6ZUEGziBPortQ0w9vHs/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1wCqToBV70Od2cMUBDpQdRHprknhcf03v/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4903,17 +4903,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.md</t>
+          <t>RASTR-FRUKI01-002_Matriz-de-Rastreabilidade-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1r2v_XLLzm37ySMynrN3AyLOGj1IHdnoW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/16oO8wnQlq4M88T-Twa2PvUaJOT4PdNvN/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4925,17 +4925,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.md</t>
+          <t>REQ-FRUKI01-002_Documento-de-Requisitos-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Fb7MpfzPfNKM--4N94Tx49pUGvWBnKab/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SLfbHTNWFb_AEyvA6NY1PZH2-yaCEQaQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4947,17 +4947,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.md</t>
+          <t>TAE-FRUKI01-002_Termo-de-Encerramento-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1qGo80blY7kzlFuXtUUCrkV6K427xB6SK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1F3XBLU-UzqieEn0RGs0fVDI5DUrGsYIf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4969,17 +4969,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.md</t>
+          <t>TAP-FRUKI01-002_Termo-de-Abertura-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ngjegtxERo_jJObFfcYsUfNPw9yuC9PV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1wHC3EjPGW68mXZ48j8CHpEgv0AYir6vt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -4991,17 +4991,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.md</t>
+          <t>VV-FRUKI01-002_Plano-VeV-PacoteFinal24.docx</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1WcBf_hl4Unrs6FsG4AHhcJ-NuAoEG1s5/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1lvrkJPwro6_uYQ5o_5Lmy58Y0nv0mrwd/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
